--- a/data/human/adult/validation/Scenarios/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B08C5B4-4D05-4BB3-8C48-745C58EF3914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A12A9F-0610-4DEF-B683-7650FB4E905C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27180" yWindow="5040" windowWidth="27555" windowHeight="24945" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28410" yWindow="4725" windowWidth="27555" windowHeight="24945" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="206">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -865,34 +865,6 @@
     <t>musch2008relation</t>
   </si>
   <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 27, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.25, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 10, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 16, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 27, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.25, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 10, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 16, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } }
-  }}
-}</t>
-  </si>
-  <si>
     <t>Learning Objectives:
  - Recognize mild ARDS
  - Recognize hypventilation (rate too low and patient not triggering additional breaths)
@@ -910,15 +882,7 @@
 </t>
   </si>
   <si>
-    <t>Increase FiO2.  Patient transport has ended.
-Recommended Actions:
- - Consider PC-CMV to liberate inspiratory volume and flow
- - Monitor for excessive tidal volume
-Ventilator settings are updated to:
- - FiO2: 0.4 -&gt; 0.5
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.567    | NA          | 27           | NA  | 1.25    | 16      | 10            | 0.5 |</t>
+    <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 1, "Unit": "min" }}}}</t>
   </si>
   <si>
     <t>Increase PEEP.
@@ -929,10 +893,64 @@
  - PEEP: 5 -&gt; 10 cmH2O
 | Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
 | ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.567    | NA          | 27           | NA  | 1.25    | 16      | 10            | 0.4 |</t>
+| VC-CMV | 0.567    | NA          | 27           | NA  | 1.25    | 16      | 15            | 0.4 |</t>
   </si>
   <si>
-    <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 1, "Unit": "min" }}}}</t>
+    <t>Increase FiO2.  Patient transport has ended.
+Recommended Actions:
+ - Consider PC-CMV to liberate inspiratory volume and flow
+ - Monitor for excessive tidal volume
+Ventilator settings are updated to:
+ - FiO2: 0.4 -&gt; 0.5
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.567    | NA          | 27           | NA  | 1.25    | 16      | 15            | 0.5 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 27, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.25, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 15, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 16, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 27, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.25, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 15, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 16, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.27 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.27 }}}]
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.57 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.57 }}}]
+  }}
+}</t>
   </si>
 </sst>
 </file>
@@ -1730,14 +1748,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>153</v>
+        <v>204</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -2034,14 +2052,14 @@
         <v>2</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>154</v>
+        <v>205</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
       <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H27" s="9"/>
     </row>
@@ -2324,14 +2342,14 @@
         <v>3</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C40" s="26"/>
       <c r="D40" s="26"/>
       <c r="E40" s="26"/>
       <c r="F40" s="27"/>
       <c r="G40" s="9" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H40" s="10"/>
     </row>
@@ -2542,7 +2560,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C50" s="26"/>
       <c r="D50" s="26"/>
@@ -2970,7 +2988,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
@@ -3346,7 +3364,7 @@
         <v>2</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C33" s="19"/>
       <c r="D33" s="19"/>
@@ -3708,7 +3726,7 @@
         <v>3</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C49" s="19"/>
       <c r="D49" s="19"/>
@@ -4331,7 +4349,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
@@ -9741,7 +9759,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
@@ -24281,7 +24299,7 @@
         <v>3</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C45" s="19"/>
       <c r="D45" s="19"/>
@@ -31848,7 +31866,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
@@ -32116,7 +32134,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
@@ -32360,7 +32378,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C39" s="19"/>
       <c r="D39" s="19"/>
@@ -32816,7 +32834,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
@@ -33108,7 +33126,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
@@ -33376,7 +33394,7 @@
         <v>3</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C41" s="19"/>
       <c r="D41" s="19"/>
@@ -33744,7 +33762,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
@@ -34084,7 +34102,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
@@ -34352,7 +34370,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C42" s="19"/>
       <c r="D42" s="19"/>
@@ -34719,7 +34737,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
@@ -35075,7 +35093,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
@@ -35343,7 +35361,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C43" s="19"/>
       <c r="D43" s="19"/>

--- a/data/human/adult/validation/Scenarios/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A12A9F-0610-4DEF-B683-7650FB4E905C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E02C90-5889-4F58-9C9B-6F9DA626A4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28410" yWindow="4725" windowWidth="27555" windowHeight="24945" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-3750" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="214">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -353,16 +353,6 @@
   }</t>
   </si>
   <si>
-    <t xml:space="preserve">    { "PatientAction": { "ChronicObstructivePulmonaryDiseaseExacerbation":
-      {
-        "BronchitisSeverity": { "Scalar0To1": { "Value": 0.8 }},
-        "EmphysemaSeverity": [ 
-          { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.4 }}},
-          { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.4 }}}]
-      }}
-    }</t>
-  </si>
-  <si>
     <t>Rinsp</t>
   </si>
   <si>
@@ -373,9 +363,6 @@
   </si>
   <si>
     <t>RespiratoryCompliance</t>
-  </si>
-  <si>
-    <t>HR; Sinus Tachycardia</t>
   </si>
   <si>
     <t>BP</t>
@@ -391,9 +378,6 @@
   </si>
   <si>
     <t>SpO2</t>
-  </si>
-  <si>
-    <t>etCO2</t>
   </si>
   <si>
     <t>P/F</t>
@@ -702,27 +686,6 @@
   { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
   "Mode": "AssistedControl", 
   "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 24, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.25, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 16, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 500, "Unit": "mL" } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>Ventilator settings are:
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.5    | NA          | 24           | NA  | 1.25    | 16       | 5            | 0.50 |</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
   "Flow": { "ScalarVolumePerTime": { "Value": 50, "Unit": "L/min" } },
   "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
   "InspiratoryPeriod": { "ScalarTime": { "Value": 0.504, "Unit": "s" } },
@@ -767,13 +730,6 @@
       { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}}]
   }}
 }</t>
-  </si>
-  <si>
-    <t>Ventilator settings are:
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.567    | NA          | 27           | NA  | 1.25    | 16      | 5            | 0.4 |</t>
   </si>
   <si>
     <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
@@ -882,9 +838,6 @@
 </t>
   </si>
   <si>
-    <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 1, "Unit": "min" }}}}</t>
-  </si>
-  <si>
     <t>Increase PEEP.
 Learning Objectives:
  - Recognize improvement due to change in vent settings
@@ -951,6 +904,77 @@
       { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.57 }}}]
   }}
 }</t>
+  </si>
+  <si>
+    <t>van1991effects, officer1998measurement</t>
+  </si>
+  <si>
+    <t>van1991effects</t>
+  </si>
+  <si>
+    <t>farah2009can</t>
+  </si>
+  <si>
+    <t>torres1989ventilation</t>
+  </si>
+  <si>
+    <t>Rinsp for mild COPD</t>
+  </si>
+  <si>
+    <t>Rexp for mild COPD</t>
+  </si>
+  <si>
+    <t>C for mild COPD</t>
+  </si>
+  <si>
+    <t>VD/VT for mild COPD</t>
+  </si>
+  <si>
+    <t>QS/QT for mild COPD</t>
+  </si>
+  <si>
+    <t>Ventilator settings are (VT Target = 6.9 mL/kg (ideal)):
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.567    | NA          | 27           | NA  | 1.25    | 16      | 5            | 0.4 |</t>
+  </si>
+  <si>
+    <t>Ventilator settings are (VT Target = 7.3 mL/kg (ideal)):
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.516    | NA          | 25.6          | NA  | 1.21    | 12       | 5            | 0.28 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 25.6, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.28 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.21, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 12, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 516, "Unit": "mL" } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    { "PatientAction": { "ChronicObstructivePulmonaryDiseaseExacerbation":
+      {
+        "BronchitisSeverity": { "Scalar0To1": { "Value": 0.8 }},
+        "EmphysemaSeverity": [ 
+          { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.3 }}},
+          { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.3 }}}]
+      }}
+    }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario1.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario2.json"} }</t>
   </si>
 </sst>
 </file>
@@ -1144,6 +1168,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1161,12 +1191,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1550,7 +1574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ55"/>
+  <dimension ref="A1:AMJ56"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="12" customWidth="1"/>
@@ -1566,44 +1590,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="23"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
       <c r="AMG1" s="14"/>
       <c r="AMH1" s="14"/>
       <c r="AMI1" s="14"/>
       <c r="AMJ1" s="14"/>
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23" t="s">
+      <c r="A2" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="23"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+        <v>106</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
       <c r="AMG2" s="14"/>
       <c r="AMH2" s="14"/>
       <c r="AMI2" s="14"/>
@@ -1613,13 +1637,13 @@
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
@@ -1654,72 +1678,72 @@
       <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21" t="s">
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="21"/>
+      <c r="H5" s="23"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="25" t="s">
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="H8" s="25"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1748,14 +1772,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -1794,14 +1818,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -1810,7 +1834,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
@@ -1862,10 +1886,10 @@
         <v>567</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -1874,7 +1898,7 @@
         <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>50</v>
@@ -1886,10 +1910,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -1898,7 +1922,7 @@
         <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>50</v>
@@ -1910,10 +1934,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -1922,7 +1946,7 @@
         <v>32</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>49</v>
@@ -1934,10 +1958,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -1946,7 +1970,7 @@
         <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>34</v>
@@ -1958,10 +1982,10 @@
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -1970,7 +1994,7 @@
         <v>32</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>34</v>
@@ -1982,10 +2006,10 @@
         <v>0.2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -2000,16 +2024,16 @@
         <v>39</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="F24" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -2017,13 +2041,13 @@
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
       <c r="G25" s="1" t="s">
         <v>7</v>
       </c>
@@ -2036,118 +2060,108 @@
         <v>2</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>52</v>
+        <v>212</v>
       </c>
       <c r="C26" s="19"/>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
       <c r="F26" s="19"/>
-      <c r="G26" s="9" t="s">
-        <v>157</v>
-      </c>
+      <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8" ht="119.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ht="68.650000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>2</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>205</v>
+        <v>52</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
       <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
-        <v>198</v>
+        <v>154</v>
       </c>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="119.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>2</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
       <c r="F28" s="19"/>
-      <c r="G28" s="9"/>
+      <c r="G28" s="9" t="s">
+        <v>192</v>
+      </c>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>2</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C30" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F29" s="6" t="s">
+      <c r="F30" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="15" t="s">
+      <c r="H30" s="15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="2">
-        <v>567</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H30" s="10"/>
     </row>
     <row r="31" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E31" s="2">
-        <v>12</v>
+        <v>567</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>189</v>
+        <v>166</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -2156,7 +2170,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>50</v>
@@ -2168,10 +2182,10 @@
         <v>12</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -2180,22 +2194,22 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E33" s="2">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -2204,22 +2218,22 @@
         <v>32</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>174</v>
+        <v>99</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E34" s="2">
-        <v>0.56999999999999995</v>
+        <v>35</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -2228,7 +2242,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>34</v>
@@ -2237,13 +2251,13 @@
         <v>35</v>
       </c>
       <c r="E35" s="2">
-        <v>0.3</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>193</v>
+        <v>167</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>186</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -2252,46 +2266,46 @@
         <v>32</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>42</v>
+        <v>169</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>188</v>
+        <v>35</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.3</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="H36" s="10"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="2">
-        <v>1</v>
+        <v>172</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>139</v>
+        <v>175</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -2300,7 +2314,7 @@
         <v>48</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>55</v>
@@ -2312,156 +2326,156 @@
         <v>1</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="H38" s="10"/>
     </row>
-    <row r="39" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="2">
+        <v>1</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="H39" s="10"/>
+    </row>
+    <row r="40" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="20" t="s">
+      <c r="B40" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
-      <c r="G39" s="1" t="s">
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H39" s="15" t="s">
+      <c r="H40" s="15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="213.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="8">
-        <v>3</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="C40" s="26"/>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="H40" s="10"/>
-    </row>
-    <row r="41" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" ht="213.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="8">
         <v>3</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="9"/>
+        <v>195</v>
+      </c>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="9" t="s">
+        <v>193</v>
+      </c>
       <c r="H41" s="10"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
+    <row r="42" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="8">
+        <v>3</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="10"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B43" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C43" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D43" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F43" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H42" s="15" t="s">
+      <c r="H43" s="15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E43" s="2">
-        <v>567</v>
-      </c>
-      <c r="F43" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>49</v>
+        <v>83</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="E44" s="2">
-        <v>2</v>
+        <v>567</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="G44" s="13" t="s">
-        <v>99</v>
+        <v>188</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>195</v>
+        <v>56</v>
       </c>
       <c r="E45" s="2">
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>104</v>
+        <v>167</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="H45" s="10"/>
     </row>
@@ -2470,31 +2484,31 @@
         <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>56</v>
+        <v>189</v>
       </c>
       <c r="E46" s="2">
         <v>2</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>39</v>
@@ -2506,10 +2520,10 @@
         <v>2</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>179</v>
+        <v>103</v>
       </c>
       <c r="H47" s="10"/>
     </row>
@@ -2518,144 +2532,144 @@
         <v>32</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E48" s="2">
         <v>2</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H48" s="10"/>
     </row>
-    <row r="49" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="1" t="s">
+    <row r="49" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E49" s="2">
+        <v>2</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H49" s="10"/>
+    </row>
+    <row r="50" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B49" s="20" t="s">
+      <c r="B50" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="1" t="s">
+      <c r="C50" s="22"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H49" s="15" t="s">
+      <c r="H50" s="15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="216.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="8">
-        <v>4</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="9" t="s">
-        <v>201</v>
-      </c>
-      <c r="H50" s="10"/>
-    </row>
-    <row r="51" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" ht="216.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="8">
         <v>4</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="9"/>
+        <v>196</v>
+      </c>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="21"/>
+      <c r="G51" s="9" t="s">
+        <v>194</v>
+      </c>
       <c r="H51" s="10"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A52" s="6" t="s">
+    <row r="52" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="8">
+        <v>4</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="10"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B53" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C53" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D53" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F53" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G53" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H52" s="15" t="s">
+      <c r="H53" s="15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E53" s="2">
-        <v>567</v>
-      </c>
-      <c r="F53" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="E54" s="2">
-        <v>3</v>
+        <v>567</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="H54" s="10"/>
     </row>
@@ -2664,30 +2678,54 @@
         <v>37</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>56</v>
+        <v>189</v>
       </c>
       <c r="E55" s="2">
         <v>3</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H55" s="10"/>
     </row>
+    <row r="56" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E56" s="2">
+        <v>3</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H56" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="B49:F49"/>
+  <mergeCells count="32">
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B52:F52"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
@@ -2708,14 +2746,15 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B40:F40"/>
     <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B40:F40"/>
     <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B39:F39"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2728,7 +2767,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMJ62"/>
+  <dimension ref="A1:AMJ43"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="12" customWidth="1"/>
@@ -2736,7 +2775,7 @@
     <col min="3" max="3" width="15" style="12" customWidth="1"/>
     <col min="4" max="4" width="25" style="12" customWidth="1"/>
     <col min="5" max="5" width="35.5703125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="26.7109375" style="12" customWidth="1"/>
+    <col min="6" max="6" width="41.85546875" style="12" customWidth="1"/>
     <col min="7" max="7" width="83.85546875" style="12" customWidth="1"/>
     <col min="8" max="8" width="33.85546875" style="16" customWidth="1"/>
     <col min="9" max="1024" width="11.5703125" style="12"/>
@@ -2744,42 +2783,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="23"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
       <c r="AMI1" s="14"/>
       <c r="AMJ1" s="14"/>
     </row>
     <row r="2" spans="1:1024" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="23"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+        <v>107</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
       <c r="AMI2" s="14"/>
       <c r="AMJ2" s="14"/>
     </row>
@@ -2787,13 +2826,13 @@
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
@@ -2828,12 +2867,12 @@
       <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21" t="s">
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="21"/>
+      <c r="H5" s="23"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -2846,60 +2885,60 @@
         <v>17</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="25" t="s">
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="H8" s="25"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -2928,14 +2967,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -2972,14 +3011,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>162</v>
+        <v>210</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -2988,7 +3027,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
@@ -3025,25 +3064,25 @@
     </row>
     <row r="18" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E18" s="2">
-        <v>18</v>
+        <v>516</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>97</v>
+        <v>166</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -3052,7 +3091,7 @@
         <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>50</v>
@@ -3061,13 +3100,13 @@
         <v>35</v>
       </c>
       <c r="E19" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>151</v>
+        <v>199</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>98</v>
+        <v>203</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -3076,22 +3115,22 @@
         <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E20" s="2">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -3100,446 +3139,414 @@
         <v>32</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E21" s="2">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>101</v>
+        <v>167</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>205</v>
       </c>
       <c r="H21" s="10"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>46</v>
+        <v>168</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E22" s="2">
-        <v>150</v>
+        <v>0.25</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>102</v>
+        <v>201</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>206</v>
       </c>
       <c r="H22" s="10"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>47</v>
+        <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E23" s="2">
-        <v>83</v>
+        <v>0.12</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>102</v>
+        <v>207</v>
       </c>
       <c r="H23" s="10"/>
     </row>
-    <row r="24" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="2">
-        <v>7.28</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="10"/>
+    <row r="24" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="25" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E25" s="2">
-        <v>56</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H25" s="10"/>
+    <row r="25" spans="1:8" ht="68.650000000000006" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="8">
+        <v>2</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
     </row>
-    <row r="26" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="2">
-        <v>141</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H26" s="10"/>
+    <row r="26" spans="1:8" ht="161.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="8">
+        <v>2</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="H26" s="9"/>
     </row>
-    <row r="27" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="2">
-        <v>0.99</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>106</v>
-      </c>
+    <row r="27" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="8">
+        <v>2</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="9"/>
       <c r="H27" s="10"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E28" s="2">
-        <v>38</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>107</v>
-      </c>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="8">
+        <v>2</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="9"/>
       <c r="H28" s="10"/>
     </row>
-    <row r="29" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="2" t="s">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="2">
+        <v>516</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="H30" s="10"/>
+    </row>
+    <row r="31" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" s="2">
-        <v>282</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H29" s="10"/>
+      <c r="B31" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H31" s="10"/>
     </row>
-    <row r="30" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="161.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="8">
-        <v>2</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="H31" s="9"/>
-    </row>
-    <row r="32" spans="1:8" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="8">
-        <v>2</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="9"/>
+    <row r="32" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>97</v>
+      </c>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="8">
-        <v>2</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="9"/>
+    <row r="33" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>136</v>
+      </c>
       <c r="H33" s="10"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G34" s="1" t="s">
+    <row r="34" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="H34" s="10"/>
+    </row>
+    <row r="35" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="15" t="s">
+      <c r="H35" s="15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E35" s="2">
-        <v>25</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G35" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="H35" s="10"/>
-    </row>
-    <row r="36" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E36" s="2">
-        <v>25</v>
-      </c>
-      <c r="F36" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G36" s="13" t="s">
-        <v>98</v>
+    <row r="36" spans="1:8" ht="189" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>3</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="9" t="s">
+        <v>157</v>
       </c>
       <c r="H36" s="10"/>
     </row>
-    <row r="37" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="2">
-        <v>53</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G37" s="13" t="s">
-        <v>99</v>
-      </c>
+    <row r="37" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <v>3</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="9"/>
       <c r="H37" s="10"/>
     </row>
-    <row r="38" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E38" s="2">
-        <v>99</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H38" s="10"/>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E39" s="2">
-        <v>145</v>
+        <v>516</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
       <c r="H39" s="10"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E40" s="2">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>102</v>
+        <v>148</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>96</v>
       </c>
       <c r="H40" s="10"/>
     </row>
@@ -3548,509 +3555,75 @@
         <v>32</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E41" s="2">
-        <v>7.19</v>
+        <v>2</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>103</v>
+        <v>148</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>97</v>
       </c>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E42" s="2">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>104</v>
+        <v>148</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>136</v>
       </c>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="E43" s="2">
+        <v>2</v>
+      </c>
+      <c r="F43" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="F43" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>105</v>
+      <c r="G43" s="13" t="s">
+        <v>137</v>
       </c>
       <c r="H43" s="10"/>
     </row>
-    <row r="44" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E44" s="2">
-        <v>0.99</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H44" s="10"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E45" s="2">
-        <v>56</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H45" s="10"/>
-    </row>
-    <row r="46" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E46" s="2">
-        <v>296</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H46" s="10"/>
-    </row>
-    <row r="47" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B47" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H47" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="189" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="8">
-        <v>3</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="H48" s="10"/>
-    </row>
-    <row r="49" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="8">
-        <v>3</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="9"/>
-      <c r="H49" s="10"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H50" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E51" s="2">
-        <v>14</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G51" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="H51" s="10"/>
-    </row>
-    <row r="52" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E52" s="2">
-        <v>14</v>
-      </c>
-      <c r="F52" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G52" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="H52" s="10"/>
-    </row>
-    <row r="53" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E53" s="2">
-        <v>61</v>
-      </c>
-      <c r="F53" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G53" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="H53" s="10"/>
-    </row>
-    <row r="54" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E54" s="2">
-        <v>103</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H54" s="10"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A55" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E55" s="2">
-        <v>144</v>
-      </c>
-      <c r="F55" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H55" s="10"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E56" s="2">
-        <v>91</v>
-      </c>
-      <c r="F56" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H56" s="10"/>
-    </row>
-    <row r="57" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E57" s="2">
-        <v>7.22</v>
-      </c>
-      <c r="F57" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H57" s="10"/>
-    </row>
-    <row r="58" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E58" s="2">
-        <v>65</v>
-      </c>
-      <c r="F58" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H58" s="10"/>
-    </row>
-    <row r="59" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E59" s="2">
-        <v>151</v>
-      </c>
-      <c r="F59" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H59" s="10"/>
-    </row>
-    <row r="60" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E60" s="2">
-        <v>0.99</v>
-      </c>
-      <c r="F60" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H60" s="10"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E61" s="2">
-        <v>68</v>
-      </c>
-      <c r="F61" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H61" s="10"/>
-    </row>
-    <row r="62" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E62" s="2">
-        <v>302</v>
-      </c>
-      <c r="F62" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H62" s="10"/>
-    </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
@@ -4072,13 +3645,14 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B25:F25"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4107,52 +3681,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="23"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="23"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
@@ -4187,12 +3761,12 @@
       <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21" t="s">
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="21"/>
+      <c r="H5" s="23"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -4205,60 +3779,60 @@
         <v>17</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="25" t="s">
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="H8" s="25"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -4287,14 +3861,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -4333,14 +3907,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -4349,7 +3923,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
@@ -4406,7 +3980,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -4430,7 +4004,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H19" s="10"/>
       <c r="I19" s="14"/>
@@ -5470,7 +5044,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H20" s="10"/>
       <c r="I20" s="14"/>
@@ -6510,7 +6084,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -6534,7 +6108,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -6558,7 +6132,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -6582,7 +6156,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -6606,7 +6180,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H25" s="10"/>
     </row>
@@ -6630,7 +6204,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H26" s="10"/>
     </row>
@@ -6654,7 +6228,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -6662,13 +6236,13 @@
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
       <c r="G28" s="1" t="s">
         <v>7</v>
       </c>
@@ -7697,7 +7271,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
@@ -9759,7 +9333,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
@@ -11848,7 +11422,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H33" s="10"/>
       <c r="I33" s="14"/>
@@ -12888,7 +12462,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H34" s="10"/>
       <c r="I34" s="14"/>
@@ -13928,7 +13502,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H35" s="10"/>
       <c r="I35" s="14"/>
@@ -14968,7 +14542,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H36" s="10"/>
       <c r="I36" s="14"/>
@@ -16008,7 +15582,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H37" s="10"/>
       <c r="I37" s="14"/>
@@ -17048,7 +16622,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H38" s="10"/>
       <c r="I38" s="14"/>
@@ -18088,7 +17662,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H39" s="10"/>
       <c r="I39" s="14"/>
@@ -19128,7 +18702,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H40" s="10"/>
       <c r="I40" s="14"/>
@@ -20168,7 +19742,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H41" s="10"/>
       <c r="I41" s="14"/>
@@ -21208,7 +20782,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H42" s="10"/>
       <c r="I42" s="14"/>
@@ -22232,13 +21806,13 @@
       <c r="A43" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
       <c r="G43" s="1" t="s">
         <v>7</v>
       </c>
@@ -23267,14 +22841,14 @@
         <v>3</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C44" s="19"/>
       <c r="D44" s="19"/>
       <c r="E44" s="19"/>
       <c r="F44" s="19"/>
       <c r="G44" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H44" s="10"/>
       <c r="I44" s="14"/>
@@ -24299,7 +23873,7 @@
         <v>3</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C45" s="19"/>
       <c r="D45" s="19"/>
@@ -26386,7 +25960,7 @@
         <v>36</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H47" s="10"/>
       <c r="I47" s="14"/>
@@ -27426,7 +27000,7 @@
         <v>36</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H48" s="10"/>
       <c r="I48" s="14"/>
@@ -28466,7 +28040,7 @@
         <v>36</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H49" s="10"/>
       <c r="I49" s="14"/>
@@ -29506,7 +29080,7 @@
         <v>36</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H50" s="10"/>
       <c r="I50" s="14"/>
@@ -30546,7 +30120,7 @@
         <v>36</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H51" s="10"/>
       <c r="I51" s="14"/>
@@ -31624,52 +31198,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="23"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="23"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="F2" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
@@ -31704,12 +31278,12 @@
       <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21" t="s">
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="21"/>
+      <c r="H5" s="23"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -31722,60 +31296,60 @@
         <v>17</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="25" t="s">
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="H8" s="25"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -31804,14 +31378,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -31850,14 +31424,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -31866,7 +31440,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
@@ -31923,7 +31497,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -31947,7 +31521,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -31971,7 +31545,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -31995,7 +31569,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -32019,7 +31593,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -32043,7 +31617,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -32067,7 +31641,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -32091,7 +31665,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H25" s="10"/>
     </row>
@@ -32099,13 +31673,13 @@
       <c r="A26" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
       <c r="G26" s="1" t="s">
         <v>7</v>
       </c>
@@ -32118,14 +31692,14 @@
         <v>2</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
       <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -32134,7 +31708,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
@@ -32176,7 +31750,7 @@
         <v>32</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>49</v>
@@ -32191,7 +31765,7 @@
         <v>36</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -32215,7 +31789,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -32239,7 +31813,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -32263,7 +31837,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -32287,7 +31861,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -32311,7 +31885,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -32335,7 +31909,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -32343,13 +31917,13 @@
       <c r="A37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="20" t="s">
+      <c r="B37" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
       <c r="G37" s="1" t="s">
         <v>7</v>
       </c>
@@ -32369,7 +31943,7 @@
       <c r="E38" s="19"/>
       <c r="F38" s="19"/>
       <c r="G38" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -32378,7 +31952,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C39" s="19"/>
       <c r="D39" s="19"/>
@@ -32433,7 +32007,7 @@
         <v>36</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -32457,7 +32031,7 @@
         <v>36</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H42" s="10"/>
     </row>
@@ -32481,7 +32055,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H43" s="10"/>
     </row>
@@ -32505,7 +32079,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -32529,7 +32103,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H45" s="10"/>
     </row>
@@ -32590,52 +32164,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="23"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="23"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="F2" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
@@ -32670,12 +32244,12 @@
       <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21" t="s">
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="21"/>
+      <c r="H5" s="23"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -32688,60 +32262,60 @@
         <v>17</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="25" t="s">
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="H8" s="25"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -32770,14 +32344,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -32793,7 +32367,7 @@
       <c r="E13" s="19"/>
       <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>27</v>
@@ -32818,14 +32392,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -32834,7 +32408,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
@@ -32891,7 +32465,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -32915,7 +32489,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -32939,7 +32513,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -32963,7 +32537,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -32987,7 +32561,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -33011,7 +32585,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -33035,7 +32609,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -33059,7 +32633,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H25" s="10"/>
     </row>
@@ -33091,13 +32665,13 @@
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
       <c r="G27" s="1" t="s">
         <v>7</v>
       </c>
@@ -33117,7 +32691,7 @@
       <c r="E28" s="19"/>
       <c r="F28" s="19"/>
       <c r="G28" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -33126,7 +32700,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C29" s="19"/>
       <c r="D29" s="19"/>
@@ -33183,7 +32757,7 @@
         <v>36</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -33207,7 +32781,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -33231,7 +32805,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -33255,7 +32829,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -33279,7 +32853,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -33303,7 +32877,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H36" s="18"/>
     </row>
@@ -33327,7 +32901,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -33351,7 +32925,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -33359,13 +32933,13 @@
       <c r="A39" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B39" s="20" t="s">
+      <c r="B39" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="20"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
       <c r="G39" s="1" t="s">
         <v>7</v>
       </c>
@@ -33385,7 +32959,7 @@
       <c r="E40" s="19"/>
       <c r="F40" s="19"/>
       <c r="G40" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H40" s="10"/>
     </row>
@@ -33394,7 +32968,7 @@
         <v>3</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C41" s="19"/>
       <c r="D41" s="19"/>
@@ -33449,7 +33023,7 @@
         <v>36</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H43" s="10"/>
     </row>
@@ -33473,7 +33047,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -33534,52 +33108,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="23"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="23"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F2" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
@@ -33614,12 +33188,12 @@
       <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21" t="s">
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="21"/>
+      <c r="H5" s="23"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -33632,60 +33206,60 @@
         <v>17</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="25" t="s">
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="H8" s="25"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -33714,14 +33288,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -33746,14 +33320,14 @@
         <v>1</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -33762,7 +33336,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
@@ -33819,7 +33393,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H17" s="18"/>
     </row>
@@ -33843,7 +33417,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H18" s="18"/>
     </row>
@@ -33867,7 +33441,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -33891,7 +33465,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -33915,7 +33489,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -33939,7 +33513,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -33963,7 +33537,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -33987,7 +33561,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -34011,7 +33585,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H25" s="10"/>
     </row>
@@ -34035,7 +33609,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H26" s="10"/>
     </row>
@@ -34059,7 +33633,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -34067,13 +33641,13 @@
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
       <c r="G28" s="1" t="s">
         <v>7</v>
       </c>
@@ -34093,7 +33667,7 @@
       <c r="E29" s="19"/>
       <c r="F29" s="19"/>
       <c r="G29" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="H29" s="10"/>
     </row>
@@ -34102,7 +33676,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
@@ -34159,7 +33733,7 @@
         <v>36</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H32" s="18"/>
     </row>
@@ -34183,7 +33757,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H33" s="18"/>
     </row>
@@ -34207,7 +33781,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -34231,7 +33805,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -34255,7 +33829,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -34279,7 +33853,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -34303,7 +33877,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -34327,7 +33901,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H39" s="18"/>
     </row>
@@ -34335,13 +33909,13 @@
       <c r="A40" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
       <c r="G40" s="1" t="s">
         <v>7</v>
       </c>
@@ -34361,7 +33935,7 @@
       <c r="E41" s="19"/>
       <c r="F41" s="19"/>
       <c r="G41" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -34370,7 +33944,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C42" s="19"/>
       <c r="D42" s="19"/>
@@ -34425,7 +33999,7 @@
         <v>36</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -34449,7 +34023,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H45" s="10"/>
     </row>
@@ -34509,52 +34083,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="23"/>
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="23"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="F2" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
@@ -34589,12 +34163,12 @@
       <c r="D5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21" t="s">
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="21"/>
+      <c r="H5" s="23"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -34607,60 +34181,60 @@
         <v>17</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
-      <c r="G6" s="25" t="s">
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="25"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
-      <c r="G7" s="25" t="s">
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="25"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="H8" s="25"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="25" t="s">
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="25"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -34689,14 +34263,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -34721,14 +34295,14 @@
         <v>1</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -34737,7 +34311,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
@@ -34794,7 +34368,7 @@
         <v>36</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H17" s="18"/>
     </row>
@@ -34818,7 +34392,7 @@
         <v>36</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H18" s="18"/>
     </row>
@@ -34842,7 +34416,7 @@
         <v>36</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -34866,7 +34440,7 @@
         <v>36</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -34890,7 +34464,7 @@
         <v>36</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -34914,7 +34488,7 @@
         <v>36</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -34938,7 +34512,7 @@
         <v>36</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -34962,7 +34536,7 @@
         <v>36</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -34986,7 +34560,7 @@
         <v>36</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H25" s="10"/>
     </row>
@@ -35010,7 +34584,7 @@
         <v>36</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H26" s="10"/>
     </row>
@@ -35034,7 +34608,7 @@
         <v>36</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -35042,13 +34616,13 @@
       <c r="A28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
       <c r="G28" s="1" t="s">
         <v>7</v>
       </c>
@@ -35077,14 +34651,14 @@
         <v>2</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C30" s="19"/>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
       <c r="F30" s="19"/>
       <c r="G30" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -35093,7 +34667,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="19"/>
@@ -35150,7 +34724,7 @@
         <v>36</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H33" s="18"/>
     </row>
@@ -35174,7 +34748,7 @@
         <v>36</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H34" s="18"/>
     </row>
@@ -35198,7 +34772,7 @@
         <v>36</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -35222,7 +34796,7 @@
         <v>36</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -35246,7 +34820,7 @@
         <v>36</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -35270,7 +34844,7 @@
         <v>36</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -35294,7 +34868,7 @@
         <v>36</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H39" s="10"/>
     </row>
@@ -35318,7 +34892,7 @@
         <v>36</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="H40" s="18"/>
     </row>
@@ -35326,13 +34900,13 @@
       <c r="A41" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="20" t="s">
+      <c r="B41" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
       <c r="G41" s="1" t="s">
         <v>7</v>
       </c>
@@ -35352,7 +34926,7 @@
       <c r="E42" s="19"/>
       <c r="F42" s="19"/>
       <c r="G42" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="H42" s="10"/>
     </row>
@@ -35361,7 +34935,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="C43" s="19"/>
       <c r="D43" s="19"/>
@@ -35416,7 +34990,7 @@
         <v>36</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H45" s="10"/>
     </row>
@@ -35440,7 +35014,7 @@
         <v>36</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H46" s="10"/>
     </row>

--- a/data/human/adult/validation/Scenarios/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E02C90-5889-4F58-9C9B-6F9DA626A4A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF3A1B9C-4670-4070-B41A-00287DCF3158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3750" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27060" yWindow="2865" windowWidth="29130" windowHeight="27735" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="214">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -838,56 +838,6 @@
 </t>
   </si>
   <si>
-    <t>Increase PEEP.
-Learning Objectives:
- - Recognize improvement due to change in vent settings
- - Consider changing mode to address work shifting
-Ventilator settings are updated to:
- - PEEP: 5 -&gt; 10 cmH2O
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.567    | NA          | 27           | NA  | 1.25    | 16      | 15            | 0.4 |</t>
-  </si>
-  <si>
-    <t>Increase FiO2.  Patient transport has ended.
-Recommended Actions:
- - Consider PC-CMV to liberate inspiratory volume and flow
- - Monitor for excessive tidal volume
-Ventilator settings are updated to:
- - FiO2: 0.4 -&gt; 0.5
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.567    | NA          | 27           | NA  | 1.25    | 16      | 15            | 0.5 |</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 27, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.25, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 15, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 16, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 27, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.25, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 15, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 16, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } }
-  }}
-}</t>
-  </si>
-  <si>
     <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
   {
     "Severity": [ 
@@ -975,6 +925,56 @@
   </si>
   <si>
     <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario2.json"} }</t>
+  </si>
+  <si>
+    <t>Increase PEEP.
+Learning Objectives:
+ - Recognize improvement due to change in vent settings
+ - Consider changing mode to address work shifting
+Ventilator settings are updated to:
+ - PEEP: 5 -&gt; 10 cmH2O
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.567    | NA          | 27           | NA  | 1.25    | 16      | 10            | 0.4 |</t>
+  </si>
+  <si>
+    <t>Increase FiO2.  Patient transport has ended.
+Recommended Actions:
+ - Consider PC-CMV to liberate inspiratory volume and flow
+ - Monitor for excessive tidal volume
+Ventilator settings are updated to:
+ - FiO2: 0.4 -&gt; 0.5
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.567    | NA          | 27           | NA  | 1.25    | 16      | 5            | 0.5 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 27, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.25, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 10, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 16, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 27, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 1.25, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 16, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } }
+  }}
+}</t>
   </si>
 </sst>
 </file>
@@ -1574,7 +1574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ56"/>
+  <dimension ref="A1:AMJ57"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="12" customWidth="1"/>
@@ -1772,7 +1772,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
@@ -1825,7 +1825,7 @@
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -2060,7 +2060,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C26" s="19"/>
       <c r="D26" s="19"/>
@@ -2090,7 +2090,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C28" s="19"/>
       <c r="D28" s="19"/>
@@ -2380,14 +2380,14 @@
         <v>3</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="20"/>
       <c r="E41" s="20"/>
       <c r="F41" s="21"/>
       <c r="G41" s="9" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -2457,25 +2457,25 @@
     </row>
     <row r="45" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>99</v>
+        <v>38</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>56</v>
+        <v>189</v>
       </c>
       <c r="E45" s="2">
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>98</v>
+        <v>190</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="H45" s="10"/>
     </row>
@@ -2484,192 +2484,192 @@
         <v>37</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>189</v>
+        <v>56</v>
       </c>
       <c r="E46" s="2">
         <v>2</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>40</v>
+        <v>169</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>56</v>
+        <v>189</v>
       </c>
       <c r="E47" s="2">
         <v>2</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>188</v>
+        <v>148</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="H47" s="10"/>
     </row>
-    <row r="48" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E48" s="2">
-        <v>2</v>
-      </c>
-      <c r="F48" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="H48" s="10"/>
+    <row r="48" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H48" s="15" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="49" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E49" s="2">
-        <v>2</v>
-      </c>
-      <c r="F49" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>170</v>
+    <row r="49" spans="1:8" ht="216.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="8">
+        <v>4</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="9" t="s">
+        <v>210</v>
       </c>
       <c r="H49" s="10"/>
     </row>
     <row r="50" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B50" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C50" s="22"/>
-      <c r="D50" s="22"/>
-      <c r="E50" s="22"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="1" t="s">
+      <c r="A50" s="8">
+        <v>4</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="10"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G51" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H50" s="15" t="s">
+      <c r="H51" s="15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="216.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="8">
-        <v>4</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="21"/>
-      <c r="G51" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="H51" s="10"/>
-    </row>
-    <row r="52" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="8">
-        <v>4</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="9"/>
+    <row r="52" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52" s="2">
+        <v>567</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>171</v>
+      </c>
       <c r="H52" s="10"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A53" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H53" s="15" t="s">
-        <v>8</v>
-      </c>
+    <row r="53" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E53" s="2">
+        <v>3</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="E54" s="2">
-        <v>567</v>
+        <v>3</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="H54" s="10"/>
     </row>
@@ -2678,31 +2678,31 @@
         <v>37</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>39</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>189</v>
+        <v>56</v>
       </c>
       <c r="E55" s="2">
         <v>3</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>39</v>
@@ -2717,15 +2717,39 @@
         <v>188</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>103</v>
+        <v>173</v>
       </c>
       <c r="H56" s="10"/>
+    </row>
+    <row r="57" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57" s="2">
+        <v>3</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H57" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B49:F49"/>
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B52:F52"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
@@ -3011,14 +3035,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -3103,10 +3127,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>199</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>203</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -3127,10 +3151,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="G20" s="13" t="s">
         <v>200</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>204</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -3154,7 +3178,7 @@
         <v>167</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -3175,10 +3199,10 @@
         <v>0.25</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -3199,10 +3223,10 @@
         <v>0.12</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -3229,7 +3253,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
@@ -3243,7 +3267,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C26" s="19"/>
       <c r="D26" s="19"/>

--- a/data/human/adult/validation/Scenarios/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB3B9CB-DAC2-406C-AAAA-DD3A08BD3173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC7FC2A-3718-4016-A032-676F46F87FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28380" yWindow="1725" windowWidth="28875" windowHeight="28080" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25845" yWindow="2550" windowWidth="32595" windowHeight="26535" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1337" uniqueCount="206">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -540,21 +540,10 @@
     <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario2.json"} }</t>
   </si>
   <si>
-    <t xml:space="preserve">Learning Objectives:
- - Recognize worsening ARDS (moderate)
- - Adjust vent settings for safety
-Recommended Actions:
- - Increase FiO2 to 0.5
-</t>
-  </si>
-  <si>
     <t>VT (measured)</t>
   </si>
   <si>
     <t xml:space="preserve">A 22 year-old soldier was involved in a motor vehicle crash with rollover and ejection from the vehicle.  He suffered multiple rib fractures, a right femur fracture, multiple lacerations and pulmonary contusion.  He underwent internal fixation of the femur fracture, received 4 units of whole blood, had a chest tube placed for a small hemothorax and returned from the operating room on mechanical ventilation. The patient is sedated and is not currently triggering the ventilator.  Intraoperatively 3 L of crystalloids were administered. The patient is 6'2" tall, weighs 200 lbs and has no known comorbidities or allergies.  Chest radiograph demonstrates bi-basilar early consolidation, presence of the chest tube and pulmonary contusion. </t>
-  </si>
-  <si>
-    <t>A 62 year-old contractor developed pneumonia while working on a water purification system. He has 90- pack year history of cigarette smoking (2 packs per day x 45 years), has type II diabetes and primary hypertension managed with oral medications. He uses a rescue inhaler (albuterol) and is on a maintenance inhaled corticosteroid. His pre-deployment FEV-1 is 65% of predicted. The patient is 5'9" tall, weighs 210 lbs and has no known allergies. Chest radiograph demonstrates left-lower lobe consolidation, haziness in the right lower lobe, flattened diaphragms and hyperinflation in the upper lung fields. Heart rate is normal sinus rhythm and occasional PVC's. Patient is sedated and not triggering ventilator.</t>
   </si>
   <si>
     <t xml:space="preserve">    { "PatientAction": { "ChronicObstructivePulmonaryDiseaseExacerbation":
@@ -618,82 +607,11 @@
     <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario4.json"} }</t>
   </si>
   <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 59, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 10, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -2.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>Patient transport continues.
-Learning Objectives:
- - Recognize need to increase PEEP to keep on PEEP matrix
-Recommended Actions:
- - Increase PEEP to 10 to keep on PEEP matrix
-Ventilator settings are updated to:
- - FiO2: 0.4 -&gt; 0.5
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.567    | NA          | 59          | NA  | 0.6    | 20      | 5            | 0.5 |</t>
-  </si>
-  <si>
-    <t>Patient transport continues.
-Learning Objectives:
- - Recognize improvement due to change in vent settings
- - Consider changing mode to address work shifting
-Recommended Actions:
- - Consider PC-CMV to liberate inspiratory volume and flow and reduce work shifting
- - Monitor for excessive tidal volume
-Ventilator settings are updated to:
- - PEEP: 5 -&gt; 10 cmH2O
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.567    | NA          | 59         | NA  | 0.6    | 20      | 10            | 0.5 |</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 59, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -2.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
     <t>Ventilator settings are (VT Target = 6.9 mL/kg (ideal)):
 &lt;br /&gt;
 | Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
 | ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
 | VC-CMV | 0.567    | NA          | 59          | NA  | 0.6    | 20      | 5            | 0.4 |</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 59, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -2.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
   </si>
   <si>
     <t xml:space="preserve">    { "PatientAction": { "ChronicObstructivePulmonaryDiseaseExacerbation":
@@ -704,24 +622,6 @@
           { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}}]
       }}
     }</t>
-  </si>
-  <si>
-    <t>Learning Objectives:
- - Assess baseline status
-Recommended Actions:
- - Suspect dynamic airflow obstruction (high minute ventilation requirement but high SpO2 and low Pplat)
-&lt;br /&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Twenty minutes into the transport the patient is slightly agitated and is making inspiratory efforts that are not in sync with the ventilator.
-Learning Objectives:
- - Recognize increased airway resistance (PIP much higher than Pplat)
- - Recognize autoPEEP
- - Recognize failed trigger efforts due to autoPEEP (examine expiratory flow waveform)
-Recommended Actions:
- - Check airway patency (secretions?) suction ETT
- - Check breath sounds (wheezing?) - suspect bronchospasm and consider bronchodilator
-</t>
   </si>
   <si>
     <t>Patient suctioned and albuterol administered.
@@ -756,13 +656,6 @@
 &lt;br /&gt;</t>
   </si>
   <si>
-    <t>Learning Objectives:
- - Recognize mild ARDS
-Recommended Actions:
- - Increase RR to 23 to get acceptable pH
-&lt;br /&gt;</t>
-  </si>
-  <si>
     <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
   {
     "Severity": [ 
@@ -777,28 +670,6 @@
     "Severity": [ 
       { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.25 }}},
       { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.25 }}}]
-  }}
-}</t>
-  </si>
-  <si>
-    <t>Ventilator settings are (VT Target = 8.9 mL/kg (ideal)):
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.630    | NA          | 55          | NA  | 0.6    | 20       | 5            | 0.32 |</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 55, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.32 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 630, "Unit": "mL" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -2.0, "Unit": "cmH2O"  } }
   }}
 }</t>
   </si>
@@ -865,6 +736,53 @@
 | VC-CMV | 0.34   | NA          | 51           | NA  | 0.41  | 20       | 12            | 1.00 |</t>
   </si>
   <si>
+    <t>Ventilator settings are (VT Target = 6.9 mL/kg (ideal)):
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.488    | NA          | 52          | NA  | 0.6    | 20      | 5            | 0.4 |</t>
+  </si>
+  <si>
+    <t>Ventilator settings are (VT Target = 6.6 mL/kg (ideal)):
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.376    | NA          | 42          | NA  | 0.6    | 20      | 5            | 0.4 |</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "PneumoniaExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.4 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.4 }}}]
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.91 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.91 }}}]
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 59, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } },
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
     <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
   { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
   "Mode": "AssistedControl", 
@@ -875,16 +793,9 @@
   "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 12, "Unit": "cmH2O" } },
   "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
   "TidalVolume": { "ScalarVolume": { "Value": 340, "Unit": "mL" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -2.0, "Unit": "cmH2O"  } }
+   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
-  </si>
-  <si>
-    <t>Ventilator settings are (VT Target = 6.9 mL/kg (ideal)):
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.488    | NA          | 52          | NA  | 0.6    | 20      | 5            | 0.4 |</t>
   </si>
   <si>
     <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
@@ -897,16 +808,9 @@
   "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
   "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
   "TidalVolume": { "ScalarVolume": { "Value": 488, "Unit": "mL" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -2.0, "Unit": "cmH2O"  } }
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
-  </si>
-  <si>
-    <t>Ventilator settings are (VT Target = 6.6 mL/kg (ideal)):
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.376    | NA          | 42          | NA  | 0.6    | 20      | 5            | 0.4 |</t>
   </si>
   <si>
     <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
@@ -919,25 +823,7 @@
   "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
   "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
   "TidalVolume": { "ScalarVolume": { "Value": 376, "Unit": "mL" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -2.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "PatientAction": { "PneumoniaExacerbation":
-  {
-    "Severity": [ 
-      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.4 }}},
-      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.4 }}}]
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
-  {
-    "Severity": [ 
-      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.91 }}},
-      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.91 }}}]
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
   </si>
@@ -948,10 +834,10 @@
   "InspirationWaveform": "Square",
   "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.6 } },
   "InspiratoryPeriod": { "ScalarTime": { "Value": 1.2, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 22, "Unit": "cmH2O" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 18.5, "Unit": "cmH2O" } },
   "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
   "RespirationRate": { "ScalarFrequency": { "Value": 10, "Unit": "1/min" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -2.0, "Unit": "cmH2O"  } }
+   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
   </si>
@@ -961,7 +847,15 @@
 &lt;br /&gt;
 | Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
 | ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| PC-CMV | NA     | 22          | NA           | NA  | 1.2    | 10       | 8            | 0.60 |</t>
+| PC-CMV | NA     | 18.5          | NA           | NA  | 1.2    | 10       | 8            | 0.60 |</t>
+  </si>
+  <si>
+    <t>&lt;br /&gt;
+Ventilator settings are (delivered VT of 460 ml):
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| PC-CMV | NA     | 15          | NA           | NA  | 1.3    | 10       | 5            | 0.40 |</t>
   </si>
   <si>
     <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
@@ -970,20 +864,131 @@
   "InspirationWaveform": "Square",
   "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
   "InspiratoryPeriod": { "ScalarTime": { "Value": 1.3, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 18, "Unit": "cmH2O" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 15, "Unit": "cmH2O" } },
   "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
   "RespirationRate": { "ScalarFrequency": { "Value": 10, "Unit": "1/min" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -2.0, "Unit": "cmH2O"  } }
+   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
   </si>
   <si>
-    <t>&lt;br /&gt;
-Ventilator settings are (delivered VT of 460 ml):
+    <t>Learning Objectives:
+ - Recognize mild ARDS
+ - Recognize acceptable ventilator settings
+Recommended Actions:
+ - None
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Objectives:
+ - Recognize worsening ARDS (moderate)
+ - Adjust vent settings for safety
+Recommended Actions:
+ - Increase FiO2 to 0.5
+ - Decrease VT to 490 mL to get acceptable DP
+</t>
+  </si>
+  <si>
+    <t>A 62 year-old contractor developed pneumonia while working on a water purification system. He has 90- pack year history of cigarette smoking (2 packs per day x 45 years), has type II diabetes and primary hypertension managed with oral medications. He uses a rescue inhaler (albuterol) and is on a maintenance inhaled corticosteroid. His pre-deployment FEV-1 is 43% of predicted. The patient is 5'9" tall, weighs 210 lbs and has no known allergies. Chest radiograph demonstrates left-lower lobe consolidation, haziness in the right lower lobe, flattened diaphragms and hyperinflation in the upper lung fields. Heart rate is normal sinus rhythm and occasional PVC's. Patient is sedated and not triggering ventilator.</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Assess baseline status
+ - Recognize presence of autoPEEP (from flow waveform)
+ - Suspect obstructive lung disease (high minute ventilation requirement but high SpO2 and low Pplat)
+Recommended Actions:
+ - None
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>Twenty minutes into the transport the patient is slightly agitated and is making inspiratory efforts that are not in sync with the ventilator.
+Learning Objectives:
+ - Recognize increased airway resistance (PIP much higher than Pplat)
+ - Recognize autoPEEP (from flow waveform)
+ - Recognize failed trigger efforts due to autoPEEP (examine expiratory flow waveform)
+Recommended Actions:
+ - Goal shifts to Comfort (improve synchrony) due to failed trigger efforts
+ - Check airway patency (secretions?) suction ETT
+ - Check breath sounds (wheezing?) - suspect bronchospasm and consider bronchodilator</t>
+  </si>
+  <si>
+    <t>Patient transport has ended. 
+Learning Objectives:
+ - Recognize improvement due to change in vent settings
+ - Consider changing mode to address work shifting
+Recommended Actions:
+ - None
+Ventilator settings are updated to:
+ - PEEP: 5 -&gt; 10 cmH2O
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.567    | NA          | 50         | NA  | 0.6    | 20      | 10            | 0.5 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 50, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 10, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } },
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 50, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 490, "Unit": "mL" } },
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>Patient transport continues.
+Learning Objectives:
+ - Recognize need to increase PEEP to keep on PEEP matrix
+Recommended Actions:
+ - Increase PEEP to 10 to keep on PEEP matrix
+Ventilator settings are updated to:
+ - FiO2: 0.4 -&gt; 0.5
+ - VT: 567 -&gt; 490 mL
+ - Flow: 59 -&gt; 50 L/min
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.490    | NA          | 50          | NA  | 0.6    | 20      | 5            | 0.5 |</t>
+  </si>
+  <si>
+    <t>Ventilator settings are (VT Target = 8.9 mL/kg (ideal)):
 &lt;br /&gt;
 | Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
 | ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| PC-CMV | NA     | 18          | NA           | NA  | 1.3    | 10       | 5            | 0.40 |</t>
+| VC-CMV | 0.630    | NA          | 55          | NA  | 0.6    | 18       | 5            | 0.4 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 55, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 18, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 630, "Unit": "mL" } },
+   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
   </si>
 </sst>
 </file>
@@ -1221,6 +1226,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1229,9 +1237,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1642,7 +1647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ57"/>
+  <dimension ref="A1:AMJ54"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="12" customWidth="1"/>
@@ -1692,7 +1697,7 @@
         <v>81</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -1723,11 +1728,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -1805,13 +1810,13 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1823,13 +1828,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>23</v>
@@ -1839,15 +1844,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>181</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -1855,13 +1860,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>25</v>
@@ -1871,13 +1876,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -1885,15 +1890,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>168</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="20"/>
+      <c r="B15" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="9" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -1901,13 +1906,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -1957,7 +1962,7 @@
         <v>113</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -2109,13 +2114,13 @@
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="1" t="s">
         <v>7</v>
       </c>
@@ -2127,13 +2132,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -2141,13 +2146,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
         <v>110</v>
       </c>
@@ -2157,15 +2162,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="9" t="s">
-        <v>143</v>
+        <v>196</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -2173,13 +2178,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
@@ -2229,7 +2234,7 @@
         <v>113</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -2377,235 +2382,219 @@
       </c>
       <c r="H37" s="10"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
+    <row r="38" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H38" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="263.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <v>3</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="21"/>
+      <c r="G39" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="H39" s="10"/>
+    </row>
+    <row r="40" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="8">
+        <v>3</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="10"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H41" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="B42" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" s="2">
+        <v>490</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H42" s="10"/>
+    </row>
+    <row r="43" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E38" s="2">
-        <v>1</v>
-      </c>
-      <c r="F38" s="11" t="s">
+      <c r="E43" s="2">
+        <v>2</v>
+      </c>
+      <c r="F43" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="G38" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="H38" s="10"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E39" s="2">
-        <v>1</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="H39" s="10"/>
-    </row>
-    <row r="40" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="21"/>
-      <c r="G40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H40" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="225.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="8">
-        <v>3</v>
-      </c>
-      <c r="B41" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="H41" s="10"/>
-    </row>
-    <row r="42" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="8">
-        <v>3</v>
-      </c>
-      <c r="B42" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="9"/>
-      <c r="H42" s="10"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>8</v>
-      </c>
+      <c r="G43" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="E44" s="2">
-        <v>567</v>
+        <v>2</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="H44" s="10"/>
     </row>
-    <row r="45" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E45" s="2">
-        <v>2</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H45" s="10"/>
-    </row>
-    <row r="46" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E46" s="2">
-        <v>2</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>80</v>
+    <row r="45" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H45" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="260.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="8">
+        <v>4</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="9" t="s">
+        <v>200</v>
       </c>
       <c r="H46" s="10"/>
     </row>
-    <row r="47" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E47" s="2">
-        <v>2</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>117</v>
-      </c>
+    <row r="47" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="8">
+        <v>4</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="9"/>
       <c r="H47" s="10"/>
     </row>
-    <row r="48" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B48" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C48" s="21"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="21"/>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>29</v>
+      </c>
       <c r="G48" s="1" t="s">
         <v>7</v>
       </c>
@@ -2613,83 +2602,99 @@
         <v>8</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="260.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="8">
-        <v>4</v>
-      </c>
-      <c r="B49" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="9" t="s">
-        <v>167</v>
+    <row r="49" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="2">
+        <v>490</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>143</v>
       </c>
       <c r="H49" s="10"/>
     </row>
-    <row r="50" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="8">
-        <v>4</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="9"/>
+    <row r="50" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E50" s="2">
+        <v>3</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>76</v>
+      </c>
       <c r="H50" s="10"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A51" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H51" s="15" t="s">
-        <v>8</v>
-      </c>
+    <row r="51" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E51" s="2">
+        <v>3</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H51" s="10"/>
     </row>
     <row r="52" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E52" s="2">
-        <v>567</v>
+        <v>3</v>
       </c>
       <c r="F52" s="11" t="s">
         <v>134</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>144</v>
+        <v>80</v>
       </c>
       <c r="H52" s="10"/>
     </row>
@@ -2698,10 +2703,10 @@
         <v>30</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>47</v>
@@ -2710,114 +2715,58 @@
         <v>3</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="G53" s="13" t="s">
-        <v>76</v>
+        <v>134</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="E54" s="2">
         <v>3</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="H54" s="10"/>
-    </row>
-    <row r="55" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E55" s="2">
-        <v>3</v>
-      </c>
-      <c r="F55" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H55" s="10"/>
-    </row>
-    <row r="56" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E56" s="2">
-        <v>3</v>
-      </c>
-      <c r="F56" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H56" s="10"/>
-    </row>
-    <row r="57" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E57" s="2">
-        <v>3</v>
-      </c>
-      <c r="F57" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H57" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
-    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
@@ -2831,22 +2780,6 @@
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B27:F27"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2865,9 +2798,9 @@
     <col min="1" max="1" width="24.85546875" style="12" customWidth="1"/>
     <col min="2" max="2" width="36.28515625" style="12" customWidth="1"/>
     <col min="3" max="3" width="15" style="12" customWidth="1"/>
-    <col min="4" max="4" width="25" style="12" customWidth="1"/>
-    <col min="5" max="5" width="35.5703125" style="12" customWidth="1"/>
-    <col min="6" max="6" width="41.85546875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.5703125" style="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="83.85546875" style="12" customWidth="1"/>
     <col min="8" max="8" width="33.85546875" style="16" customWidth="1"/>
     <col min="9" max="1024" width="11.5703125" style="12"/>
@@ -2907,7 +2840,7 @@
         <v>82</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>146</v>
+        <v>197</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -2936,11 +2869,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -3024,13 +2957,13 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -3042,31 +2975,31 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:1024" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1024" ht="179.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -3074,13 +3007,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10"/>
     </row>
@@ -3088,13 +3021,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -3102,15 +3035,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="B15" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -3118,13 +3051,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
@@ -3174,7 +3107,7 @@
         <v>113</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -3198,7 +3131,7 @@
         <v>137</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -3222,7 +3155,7 @@
         <v>138</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -3246,7 +3179,7 @@
         <v>114</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -3270,7 +3203,7 @@
         <v>139</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -3294,7 +3227,7 @@
         <v>140</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -3302,13 +3235,13 @@
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
       <c r="G24" s="1" t="s">
         <v>7</v>
       </c>
@@ -3320,13 +3253,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -3334,15 +3267,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="B26" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="H26" s="9"/>
     </row>
@@ -3364,13 +3297,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="9"/>
       <c r="H28" s="10"/>
     </row>
@@ -3420,7 +3353,7 @@
         <v>113</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -3524,13 +3457,13 @@
       <c r="A35" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
       <c r="G35" s="1" t="s">
         <v>7</v>
       </c>
@@ -3542,15 +3475,15 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
       <c r="G36" s="9" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -3558,13 +3491,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
       <c r="G37" s="9"/>
       <c r="H37" s="10"/>
     </row>
@@ -3614,7 +3547,7 @@
         <v>113</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H39" s="10"/>
     </row>
@@ -3716,26 +3649,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B36:F36"/>
@@ -3745,6 +3658,26 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3803,7 +3736,7 @@
         <v>83</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -3830,11 +3763,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -3918,13 +3851,13 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -3939,10 +3872,10 @@
       <c r="B11" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="21"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -3952,15 +3885,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -3968,13 +3901,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10" t="s">
         <v>25</v>
@@ -3984,13 +3917,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -3998,15 +3931,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="B15" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -4014,13 +3947,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
@@ -4070,7 +4003,7 @@
         <v>113</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -4222,13 +4155,13 @@
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="1" t="s">
         <v>7</v>
       </c>
@@ -5256,13 +5189,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="B26" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -5270,15 +5203,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="14"/>
@@ -6302,15 +6235,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="B28" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="9" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="14"/>
@@ -7334,13 +7267,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
       <c r="H29" s="10"/>
       <c r="I29" s="14"/>
       <c r="J29" s="14"/>
@@ -9421,7 +9354,7 @@
         <v>113</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -9445,7 +9378,7 @@
         <v>113</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -9469,7 +9402,7 @@
         <v>113</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -9493,7 +9426,7 @@
         <v>114</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -9517,7 +9450,7 @@
         <v>114</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -9541,7 +9474,7 @@
         <v>114</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -9556,7 +9489,7 @@
         <v>36</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E37" s="2">
         <v>100</v>
@@ -9565,7 +9498,7 @@
         <v>121</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -9573,13 +9506,13 @@
       <c r="A38" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
       <c r="G38" s="1" t="s">
         <v>7</v>
       </c>
@@ -10607,15 +10540,15 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
+      <c r="B39" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
       <c r="G39" s="9" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="H39" s="10"/>
       <c r="I39" s="14"/>
@@ -11639,13 +11572,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
       <c r="G40" s="9"/>
       <c r="H40" s="10"/>
       <c r="I40" s="14"/>
@@ -13727,7 +13660,7 @@
         <v>113</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H42" s="10"/>
     </row>
@@ -13757,25 +13690,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B39:F39"/>
@@ -13786,6 +13700,25 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -13871,11 +13804,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -13959,13 +13892,13 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -13977,13 +13910,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -13993,13 +13926,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>90</v>
       </c>
@@ -14009,13 +13942,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10" t="s">
         <v>25</v>
@@ -14025,13 +13958,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -14039,15 +13972,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="20"/>
+      <c r="B15" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="9" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -14055,13 +13988,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
@@ -14111,7 +14044,7 @@
         <v>113</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -14263,13 +14196,13 @@
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="1" t="s">
         <v>7</v>
       </c>
@@ -14281,13 +14214,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="B26" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -14295,13 +14228,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
         <v>91</v>
       </c>
@@ -14311,15 +14244,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="9" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -14369,7 +14302,7 @@
         <v>113</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -14521,13 +14454,13 @@
       <c r="A37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="21"/>
-      <c r="D37" s="21"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
       <c r="G37" s="1" t="s">
         <v>7</v>
       </c>
@@ -14539,13 +14472,13 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
       <c r="G38" s="9" t="s">
         <v>92</v>
       </c>
@@ -14555,13 +14488,13 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
       <c r="G39" s="9"/>
       <c r="H39" s="10"/>
     </row>
@@ -14611,7 +14544,7 @@
         <v>113</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -14761,25 +14694,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B39:F39"/>
@@ -14789,6 +14703,25 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -14874,11 +14807,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -14962,13 +14895,13 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -14980,13 +14913,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -14996,13 +14929,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>99</v>
       </c>
@@ -15012,13 +14945,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>93</v>
       </c>
@@ -15030,13 +14963,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -15044,15 +14977,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="20"/>
+      <c r="B15" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="9" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -15060,15 +14993,15 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="H16" s="10"/>
     </row>
@@ -15118,7 +15051,7 @@
         <v>113</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -15270,13 +15203,13 @@
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="1" t="s">
         <v>7</v>
       </c>
@@ -15288,13 +15221,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>163</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="B26" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -15302,13 +15235,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
         <v>94</v>
       </c>
@@ -15318,15 +15251,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="9" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -15376,7 +15309,7 @@
         <v>113</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -15480,13 +15413,13 @@
       <c r="A35" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
       <c r="G35" s="1" t="s">
         <v>7</v>
       </c>
@@ -15498,13 +15431,13 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
       <c r="G36" s="9" t="s">
         <v>95</v>
       </c>
@@ -15514,13 +15447,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
       <c r="G37" s="9"/>
       <c r="H37" s="10"/>
     </row>
@@ -15570,7 +15503,7 @@
         <v>113</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H39" s="10"/>
     </row>
@@ -15672,25 +15605,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B37:F37"/>
@@ -15700,6 +15614,25 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -15785,11 +15718,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -15873,13 +15806,13 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -15891,13 +15824,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -15907,15 +15840,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -15923,13 +15856,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>63</v>
       </c>
@@ -15940,14 +15873,14 @@
         <v>1</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="20"/>
+        <v>191</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="21"/>
       <c r="G14" s="9" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -15955,15 +15888,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -16013,7 +15946,7 @@
         <v>113</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H17" s="10"/>
     </row>
@@ -16165,13 +16098,13 @@
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
       <c r="G24" s="1" t="s">
         <v>7</v>
       </c>
@@ -16183,13 +16116,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="B25" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -16197,13 +16130,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9" t="s">
         <v>100</v>
       </c>
@@ -16213,15 +16146,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -16271,7 +16204,7 @@
         <v>113</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H29" s="10"/>
     </row>
@@ -16375,13 +16308,13 @@
       <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
       <c r="G34" s="1" t="s">
         <v>7</v>
       </c>
@@ -16393,13 +16326,13 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
       <c r="G35" s="9" t="s">
         <v>96</v>
       </c>
@@ -16409,13 +16342,13 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
       <c r="G36" s="9"/>
       <c r="H36" s="10"/>
     </row>
@@ -16459,13 +16392,13 @@
         <v>32</v>
       </c>
       <c r="E38" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>113</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -16567,12 +16500,19 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="E5:F9"/>
@@ -16581,19 +16521,12 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -16679,11 +16612,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -16767,13 +16700,13 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -16785,13 +16718,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -16801,13 +16734,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
         <v>98</v>
       </c>
@@ -16817,13 +16750,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>63</v>
       </c>
@@ -16833,15 +16766,15 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="B14" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -16849,15 +16782,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -16907,7 +16840,7 @@
         <v>113</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H17" s="10"/>
     </row>
@@ -17059,13 +16992,13 @@
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
       <c r="G24" s="1" t="s">
         <v>7</v>
       </c>
@@ -17077,13 +17010,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="B25" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -17091,13 +17024,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9" t="s">
         <v>101</v>
       </c>
@@ -17107,15 +17040,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -17165,7 +17098,7 @@
         <v>113</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H29" s="10"/>
     </row>
@@ -17269,13 +17202,13 @@
       <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="21"/>
-      <c r="D34" s="21"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="21"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
       <c r="G34" s="1" t="s">
         <v>7</v>
       </c>
@@ -17287,13 +17220,13 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
       <c r="G35" s="9" t="s">
         <v>97</v>
       </c>
@@ -17303,13 +17236,13 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
       <c r="G36" s="9"/>
       <c r="H36" s="10"/>
     </row>
@@ -17359,7 +17292,7 @@
         <v>113</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -17461,12 +17394,19 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="E5:F9"/>
@@ -17475,19 +17415,12 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC7FC2A-3718-4016-A032-676F46F87FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F22D9965-3786-46E4-87EF-F1CEE93E8EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25845" yWindow="2550" windowWidth="32595" windowHeight="26535" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -969,23 +969,23 @@
 | VC-CMV | 0.490    | NA          | 50          | NA  | 0.6    | 20      | 5            | 0.5 |</t>
   </si>
   <si>
-    <t>Ventilator settings are (VT Target = 8.9 mL/kg (ideal)):
+    <t>Ventilator settings are:
 &lt;br /&gt;
 | Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
 | ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.630    | NA          | 55          | NA  | 0.6    | 18       | 5            | 0.4 |</t>
+| VC-CMV | 0.600    | NA          | 64          | NA  | 0.6    | 18       | 5            | 0.4 |</t>
   </si>
   <si>
     <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
   { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
   "Mode": "AssistedControl", 
   "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 55, "Unit": "L/min" } },
+  "Flow": { "ScalarVolumePerTime": { "Value": 64, "Unit": "L/min" } },
   "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
   "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
   "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
   "RespirationRate": { "ScalarFrequency": { "Value": 18, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 630, "Unit": "mL" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 600, "Unit": "mL" } },
    "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
@@ -1226,9 +1226,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1237,6 +1234,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1728,11 +1728,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -1810,13 +1810,13 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -1828,13 +1828,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>23</v>
@@ -1844,13 +1844,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
         <v>195</v>
       </c>
@@ -1860,13 +1860,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>25</v>
@@ -1876,13 +1876,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -1890,13 +1890,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="21"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20"/>
       <c r="G15" s="9" t="s">
         <v>163</v>
       </c>
@@ -1906,13 +1906,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -2114,13 +2114,13 @@
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
       <c r="G25" s="1" t="s">
         <v>7</v>
       </c>
@@ -2132,13 +2132,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -2146,13 +2146,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
         <v>110</v>
       </c>
@@ -2162,13 +2162,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
         <v>196</v>
       </c>
@@ -2178,13 +2178,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
@@ -2386,13 +2386,13 @@
       <c r="A38" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
       <c r="G38" s="1" t="s">
         <v>7</v>
       </c>
@@ -2404,13 +2404,13 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="20"/>
-      <c r="F39" s="21"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="20"/>
       <c r="G39" s="9" t="s">
         <v>203</v>
       </c>
@@ -2420,13 +2420,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
       <c r="G40" s="9"/>
       <c r="H40" s="10"/>
     </row>
@@ -2532,13 +2532,13 @@
       <c r="A45" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
       <c r="G45" s="1" t="s">
         <v>7</v>
       </c>
@@ -2550,13 +2550,13 @@
       <c r="A46" s="8">
         <v>4</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="21"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="20"/>
       <c r="G46" s="9" t="s">
         <v>200</v>
       </c>
@@ -2566,13 +2566,13 @@
       <c r="A47" s="8">
         <v>4</v>
       </c>
-      <c r="B47" s="19" t="s">
+      <c r="B47" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
       <c r="G47" s="9"/>
       <c r="H47" s="10"/>
     </row>
@@ -2748,22 +2748,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="B46:F46"/>
     <mergeCell ref="B47:F47"/>
@@ -2780,6 +2764,22 @@
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B27:F27"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2869,11 +2869,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -2957,13 +2957,13 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -2975,13 +2975,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -2991,13 +2991,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
         <v>198</v>
       </c>
@@ -3007,13 +3007,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10"/>
     </row>
@@ -3021,13 +3021,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -3035,13 +3035,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
       <c r="G15" s="9" t="s">
         <v>204</v>
       </c>
@@ -3051,13 +3051,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
@@ -3101,7 +3101,7 @@
         <v>32</v>
       </c>
       <c r="E18" s="2">
-        <v>516</v>
+        <v>600</v>
       </c>
       <c r="F18" s="11" t="s">
         <v>113</v>
@@ -3235,13 +3235,13 @@
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="1" t="s">
         <v>7</v>
       </c>
@@ -3253,13 +3253,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -3267,13 +3267,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
         <v>199</v>
       </c>
@@ -3297,13 +3297,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9"/>
       <c r="H28" s="10"/>
     </row>
@@ -3347,7 +3347,7 @@
         <v>32</v>
       </c>
       <c r="E30" s="2">
-        <v>516</v>
+        <v>600</v>
       </c>
       <c r="F30" s="11" t="s">
         <v>113</v>
@@ -3457,13 +3457,13 @@
       <c r="A35" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
       <c r="G35" s="1" t="s">
         <v>7</v>
       </c>
@@ -3475,13 +3475,13 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
       <c r="G36" s="9" t="s">
         <v>165</v>
       </c>
@@ -3491,13 +3491,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
       <c r="G37" s="9"/>
       <c r="H37" s="10"/>
     </row>
@@ -3541,7 +3541,7 @@
         <v>32</v>
       </c>
       <c r="E39" s="2">
-        <v>516</v>
+        <v>600</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>113</v>
@@ -3649,6 +3649,26 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B36:F36"/>
@@ -3658,26 +3678,6 @@
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3763,11 +3763,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -3851,13 +3851,13 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -3872,10 +3872,10 @@
       <c r="B11" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="21"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="20"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -3885,13 +3885,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
         <v>169</v>
       </c>
@@ -3901,13 +3901,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10" t="s">
         <v>25</v>
@@ -3917,13 +3917,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -3931,13 +3931,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
       <c r="G15" s="9" t="s">
         <v>180</v>
       </c>
@@ -3947,13 +3947,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
@@ -4155,13 +4155,13 @@
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
       <c r="G25" s="1" t="s">
         <v>7</v>
       </c>
@@ -5189,13 +5189,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -5203,13 +5203,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
         <v>167</v>
       </c>
@@ -6235,13 +6235,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
         <v>168</v>
       </c>
@@ -7267,13 +7267,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="H29" s="10"/>
       <c r="I29" s="14"/>
       <c r="J29" s="14"/>
@@ -9506,13 +9506,13 @@
       <c r="A38" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
       <c r="G38" s="1" t="s">
         <v>7</v>
       </c>
@@ -10540,13 +10540,13 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
       <c r="G39" s="9" t="s">
         <v>182</v>
       </c>
@@ -11572,13 +11572,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
       <c r="G40" s="9"/>
       <c r="H40" s="10"/>
       <c r="I40" s="14"/>
@@ -13690,6 +13690,25 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B39:F39"/>
@@ -13700,25 +13719,6 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -13804,11 +13804,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -13892,13 +13892,13 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -13910,13 +13910,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -13926,13 +13926,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
         <v>90</v>
       </c>
@@ -13942,13 +13942,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10" t="s">
         <v>25</v>
@@ -13958,13 +13958,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -13972,13 +13972,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="21"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20"/>
       <c r="G15" s="9" t="s">
         <v>183</v>
       </c>
@@ -13988,13 +13988,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
@@ -14196,13 +14196,13 @@
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
       <c r="G25" s="1" t="s">
         <v>7</v>
       </c>
@@ -14214,13 +14214,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -14228,13 +14228,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
         <v>91</v>
       </c>
@@ -14244,13 +14244,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
         <v>172</v>
       </c>
@@ -14454,13 +14454,13 @@
       <c r="A37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="21"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21"/>
       <c r="G37" s="1" t="s">
         <v>7</v>
       </c>
@@ -14472,13 +14472,13 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
       <c r="G38" s="9" t="s">
         <v>92</v>
       </c>
@@ -14488,13 +14488,13 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
       <c r="G39" s="9"/>
       <c r="H39" s="10"/>
     </row>
@@ -14694,6 +14694,25 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B39:F39"/>
@@ -14703,25 +14722,6 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -14807,11 +14807,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -14895,13 +14895,13 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -14913,13 +14913,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -14929,13 +14929,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
         <v>99</v>
       </c>
@@ -14945,13 +14945,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9" t="s">
         <v>93</v>
       </c>
@@ -14963,13 +14963,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -14977,13 +14977,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="21"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20"/>
       <c r="G15" s="9" t="s">
         <v>184</v>
       </c>
@@ -14993,13 +14993,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9" t="s">
         <v>173</v>
       </c>
@@ -15203,13 +15203,13 @@
       <c r="A25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
       <c r="G25" s="1" t="s">
         <v>7</v>
       </c>
@@ -15221,13 +15221,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -15235,13 +15235,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
         <v>94</v>
       </c>
@@ -15251,13 +15251,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
         <v>174</v>
       </c>
@@ -15413,13 +15413,13 @@
       <c r="A35" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
       <c r="G35" s="1" t="s">
         <v>7</v>
       </c>
@@ -15431,13 +15431,13 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
       <c r="G36" s="9" t="s">
         <v>95</v>
       </c>
@@ -15447,13 +15447,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
       <c r="G37" s="9"/>
       <c r="H37" s="10"/>
     </row>
@@ -15605,6 +15605,25 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B37:F37"/>
@@ -15614,25 +15633,6 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -15718,11 +15718,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -15806,13 +15806,13 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -15824,13 +15824,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -15840,13 +15840,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
         <v>177</v>
       </c>
@@ -15856,13 +15856,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9" t="s">
         <v>63</v>
       </c>
@@ -15875,10 +15875,10 @@
       <c r="B14" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="21"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="20"/>
       <c r="G14" s="9" t="s">
         <v>192</v>
       </c>
@@ -15888,13 +15888,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
       <c r="G15" s="9" t="s">
         <v>176</v>
       </c>
@@ -16098,13 +16098,13 @@
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="1" t="s">
         <v>7</v>
       </c>
@@ -16116,13 +16116,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -16130,13 +16130,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
         <v>100</v>
       </c>
@@ -16146,13 +16146,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
         <v>175</v>
       </c>
@@ -16308,13 +16308,13 @@
       <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
       <c r="G34" s="1" t="s">
         <v>7</v>
       </c>
@@ -16326,13 +16326,13 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
       <c r="G35" s="9" t="s">
         <v>96</v>
       </c>
@@ -16342,13 +16342,13 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
       <c r="G36" s="9"/>
       <c r="H36" s="10"/>
     </row>
@@ -16500,6 +16500,25 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B15:F15"/>
@@ -16508,25 +16527,6 @@
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -16612,11 +16612,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>9</v>
@@ -16700,13 +16700,13 @@
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
@@ -16718,13 +16718,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>23</v>
@@ -16734,13 +16734,13 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
         <v>98</v>
       </c>
@@ -16750,13 +16750,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9" t="s">
         <v>63</v>
       </c>
@@ -16766,13 +16766,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9" t="s">
         <v>193</v>
       </c>
@@ -16782,13 +16782,13 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
       <c r="G15" s="9" t="s">
         <v>178</v>
       </c>
@@ -16992,13 +16992,13 @@
       <c r="A24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="1" t="s">
         <v>7</v>
       </c>
@@ -17010,13 +17010,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -17024,13 +17024,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
         <v>101</v>
       </c>
@@ -17040,13 +17040,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
         <v>179</v>
       </c>
@@ -17202,13 +17202,13 @@
       <c r="A34" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="21"/>
       <c r="G34" s="1" t="s">
         <v>7</v>
       </c>
@@ -17220,13 +17220,13 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="19" t="s">
+      <c r="B35" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
       <c r="G35" s="9" t="s">
         <v>97</v>
       </c>
@@ -17236,13 +17236,13 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="19" t="s">
+      <c r="B36" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
       <c r="G36" s="9"/>
       <c r="H36" s="10"/>
     </row>
@@ -17394,6 +17394,25 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B36:F36"/>
@@ -17402,25 +17421,6 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA5D927-C61B-40FD-B240-EDA65E753481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD3E49A1-ED82-40F1-98C2-04E714393CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29115" yWindow="5490" windowWidth="26880" windowHeight="24210" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6825" yWindow="3030" windowWidth="21600" windowHeight="12645" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="217">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>Description</t>
-  </si>
-  <si>
-    <t>Scenario1</t>
   </si>
   <si>
     <t>Segment</t>
@@ -199,9 +196,6 @@
   </si>
   <si>
     <t>Moderate COPD with Subsequent Bronchospasm</t>
-  </si>
-  <si>
-    <t>Scenario2</t>
   </si>
   <si>
     <t xml:space="preserve">    {
@@ -221,13 +215,7 @@
     <t>Mild TBI with worsening ARDS</t>
   </si>
   <si>
-    <t>Scenario3</t>
-  </si>
-  <si>
     <t>Mild ARDS with Tension Pneumothorax</t>
-  </si>
-  <si>
-    <t>Scenario4</t>
   </si>
   <si>
     <t>{ "PatientAction": {
@@ -241,16 +229,10 @@
     <t>Moderate ARDS with Right Mainstem Intubation</t>
   </si>
   <si>
-    <t>Scenario5</t>
-  </si>
-  <si>
     <t>{ "PatientAction": { "Intubation": { "Type": "RightMainstem" } } }</t>
   </si>
   <si>
     <t>Hypoxemic Respiratory Failure - Pneumonia</t>
-  </si>
-  <si>
-    <t>Scenario6</t>
   </si>
   <si>
     <t xml:space="preserve">After intubation he is on mechanical ventilation and remains sedated with a RASS of -2. </t>
@@ -272,9 +254,6 @@
   </si>
   <si>
     <t>Hypoxemic Respiratory Failure Plugged ETT</t>
-  </si>
-  <si>
-    <t>Scenario7</t>
   </si>
   <si>
     <t>A 25 year-old soldier was injured following an IED detonation while dismounted. He suffered a traumatic amputation of the right lower extremity below the knee, multiple puncture wounds from fragments in the left lower extremity and lost consciousness at the scene. A tourniquet was applied and the hemorrhage mitigated.  Both eardrums were ruptured and his GCS was 12.  He underwent a massive transfusion, received 10 units of whole blood, crystalloid infusions and platelets. In the operating room primary control of hemorrhage was achieved and the lower extremity amputation addressed using standard techniques. The patient arrived from the operating room on mechanical ventilation. He was sedated and is not currently triggering the ventilator. The patient is 5'9" tall, weighs 170 lbs and has no known comorbidities or allergies.</t>
@@ -1289,9 +1268,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1300,6 +1276,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1749,18 +1728,16 @@
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B2" s="24"/>
-      <c r="C2" s="24" t="s">
-        <v>4</v>
-      </c>
+      <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -1771,53 +1748,53 @@
     </row>
     <row r="3" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
       <c r="G3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="E5" s="22"/>
       <c r="F5" s="22"/>
       <c r="G5" s="22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="22"/>
     </row>
@@ -1829,7 +1806,7 @@
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
       <c r="G6" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6" s="26"/>
     </row>
@@ -1841,7 +1818,7 @@
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
       <c r="G7" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" s="26"/>
     </row>
@@ -1853,7 +1830,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -1865,57 +1842,57 @@
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
       <c r="G9" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="B11" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:1024" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -1923,29 +1900,29 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="B13" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="B14" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -1953,15 +1930,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>177</v>
-      </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="21"/>
+      <c r="B15" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20"/>
       <c r="G15" s="9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -1969,239 +1946,239 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="B16" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="G17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2">
         <v>567</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2">
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2">
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2">
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E22" s="2">
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E23" s="2">
         <v>0.2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
       <c r="G25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H25" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>197</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -2209,15 +2186,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="B27" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="H27" s="9"/>
     </row>
@@ -2225,15 +2202,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -2241,13 +2218,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="B29" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
@@ -2255,239 +2232,239 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
+      <c r="B30" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="C31" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H31" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H31" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E32" s="2">
         <v>567</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E33" s="2">
         <v>12</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E34" s="2">
         <v>12</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E35" s="2">
         <v>35</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E36" s="2">
         <v>0.56999999999999995</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E37" s="2">
         <v>0.3</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
       <c r="G39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H39" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H39" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
+      <c r="B40" s="18" t="s">
+        <v>198</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
@@ -2495,15 +2472,15 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="21"/>
+      <c r="B41" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="20"/>
       <c r="G41" s="9" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -2511,145 +2488,145 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
+      <c r="B42" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
       <c r="G42" s="9"/>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="C43" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H43" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E44" s="2">
         <v>490</v>
       </c>
       <c r="F44" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E45" s="2">
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H45" s="10"/>
     </row>
     <row r="46" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D46" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E46" s="2">
         <v>2</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B47" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
       <c r="G47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H47" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H47" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="260.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="8">
         <v>4</v>
       </c>
-      <c r="B48" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="21"/>
+      <c r="B48" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="20"/>
       <c r="G48" s="9" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="H48" s="10"/>
     </row>
@@ -2657,206 +2634,188 @@
       <c r="A49" s="8">
         <v>4</v>
       </c>
-      <c r="B49" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
+      <c r="B49" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
       <c r="G49" s="9"/>
       <c r="H49" s="10"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="C50" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="F50" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H50" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H50" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E51" s="2">
         <v>490</v>
       </c>
       <c r="F51" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="G51" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="H51" s="10"/>
     </row>
     <row r="52" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E52" s="2">
         <v>3</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="D53" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E53" s="2">
         <v>3</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H53" s="10"/>
     </row>
     <row r="54" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E54" s="2">
         <v>3</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E55" s="2">
         <v>3</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H55" s="10"/>
     </row>
     <row r="56" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="D56" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E56" s="2">
         <v>3</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H56" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B49:F49"/>
@@ -2873,6 +2832,24 @@
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B29:F29"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2922,18 +2899,16 @@
     </row>
     <row r="2" spans="1:1024" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="24"/>
-      <c r="C2" s="24" t="s">
-        <v>51</v>
-      </c>
+      <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -2942,71 +2917,71 @@
     </row>
     <row r="3" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
       <c r="G3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="E5" s="22"/>
       <c r="F5" s="22"/>
       <c r="G5" s="22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="22"/>
     </row>
     <row r="6" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
       <c r="G6" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6" s="26"/>
     </row>
@@ -3018,7 +2993,7 @@
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
       <c r="G7" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" s="26"/>
     </row>
@@ -3030,7 +3005,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -3042,57 +3017,57 @@
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
       <c r="G9" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="B11" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:1024" ht="179.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -3100,13 +3075,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="B13" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10"/>
     </row>
@@ -3114,13 +3089,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="B14" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -3128,15 +3103,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="B15" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
       <c r="G15" s="9" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -3144,215 +3119,215 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="B16" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="G17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2">
         <v>600</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2">
         <v>24</v>
       </c>
       <c r="F19" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G19" s="13" t="s">
         <v>135</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>142</v>
       </c>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2">
         <v>36</v>
       </c>
       <c r="F20" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="13" t="s">
         <v>136</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>143</v>
       </c>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2">
         <v>68</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E22" s="2">
         <v>0.49</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E23" s="2">
         <v>0.19</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="B25" s="18" t="s">
+        <v>199</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -3360,15 +3335,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="H26" s="9"/>
     </row>
@@ -3377,7 +3352,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" s="29"/>
       <c r="D27" s="29"/>
@@ -3390,13 +3365,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
@@ -3404,191 +3379,191 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="B29" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="9"/>
       <c r="H29" s="10"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="C30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H30" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" s="2">
         <v>600</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="E34" s="2">
         <v>1</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="E35" s="2">
         <v>1</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
       <c r="G36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H36" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
+      <c r="B37" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
     </row>
@@ -3597,14 +3572,14 @@
         <v>3</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="21"/>
+        <v>50</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="20"/>
       <c r="G38" s="9" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -3612,164 +3587,184 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
+      <c r="B39" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
       <c r="G39" s="9"/>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H40" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H40" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E41" s="2">
         <v>600</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E42" s="2">
         <v>2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E43" s="2">
         <v>2</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E44" s="2">
         <v>2</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="E45" s="2">
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H45" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B38:F38"/>
@@ -3781,26 +3776,6 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3848,89 +3823,87 @@
     </row>
     <row r="2" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B2" s="24"/>
-      <c r="C2" s="24" t="s">
-        <v>54</v>
-      </c>
+      <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
       <c r="G3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="E5" s="22"/>
       <c r="F5" s="22"/>
       <c r="G5" s="22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="22"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
       <c r="G6" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6" s="26"/>
     </row>
@@ -3942,7 +3915,7 @@
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
       <c r="G7" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" s="26"/>
     </row>
@@ -3954,7 +3927,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -3966,26 +3939,26 @@
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
       <c r="G9" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
@@ -3993,30 +3966,30 @@
         <v>1</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="21"/>
+        <v>21</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="20"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="147.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -4024,29 +3997,29 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="B13" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="B14" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -4054,15 +4027,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="B15" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
       <c r="G15" s="9" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -4070,226 +4043,226 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="B16" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="G17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2">
         <v>420</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2">
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2">
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2">
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E22" s="2">
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E23" s="2">
         <v>0.2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
       <c r="G25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H25" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>8</v>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14"/>
@@ -5312,13 +5285,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -5326,15 +5299,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="B27" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="14"/>
@@ -6358,15 +6331,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="14"/>
@@ -7390,13 +7363,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="B29" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
@@ -7404,13 +7377,13 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
+      <c r="B30" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
       <c r="H30" s="10"/>
       <c r="I30" s="14"/>
       <c r="J30" s="14"/>
@@ -8431,28 +8404,28 @@
     </row>
     <row r="31" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="C31" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="F31" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H31" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H31" s="15" t="s">
-        <v>8</v>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14"/>
@@ -9473,188 +9446,188 @@
     </row>
     <row r="32" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E32" s="2">
         <v>420</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E33" s="2">
         <v>12</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E34" s="2">
         <v>12</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E35" s="2">
         <v>33</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E36" s="2">
         <v>0.65</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E37" s="2">
         <v>0.4</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E38" s="2">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
       <c r="G39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H39" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H39" s="15" t="s">
-        <v>8</v>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14"/>
@@ -10677,13 +10650,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>211</v>
-      </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
+      <c r="B40" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
@@ -10691,15 +10664,15 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
+      <c r="B41" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
       <c r="G41" s="9" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="H41" s="10"/>
       <c r="I41" s="14"/>
@@ -11723,13 +11696,13 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
+      <c r="B42" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
       <c r="G42" s="9"/>
       <c r="H42" s="10"/>
       <c r="I42" s="14"/>
@@ -12751,28 +12724,28 @@
     </row>
     <row r="43" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="C43" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H43" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>8</v>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14"/>
@@ -13793,54 +13766,73 @@
     </row>
     <row r="44" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E44" s="2">
         <v>340</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E45" s="2">
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H45" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B41:F41"/>
@@ -13853,25 +13845,6 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -13919,89 +13892,87 @@
     </row>
     <row r="2" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B2" s="24"/>
-      <c r="C2" s="24" t="s">
-        <v>56</v>
-      </c>
+      <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
       <c r="G3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="E5" s="22"/>
       <c r="F5" s="22"/>
       <c r="G5" s="22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="22"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
       <c r="G6" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6" s="26"/>
     </row>
@@ -14013,7 +13984,7 @@
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
       <c r="G7" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" s="26"/>
     </row>
@@ -14025,7 +13996,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -14037,57 +14008,57 @@
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
       <c r="G9" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="B11" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -14095,29 +14066,29 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="B13" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="B14" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -14125,15 +14096,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="21"/>
+      <c r="B15" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20"/>
       <c r="G15" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -14141,239 +14112,239 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="B16" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="G17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2">
         <v>500</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2">
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2">
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2">
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E22" s="2">
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E23" s="2">
         <v>0.2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
       <c r="G25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H25" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -14381,15 +14352,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="B27" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -14397,13 +14368,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
@@ -14411,241 +14382,241 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="B29" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="9" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="H29" s="10"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="C30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H30" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" s="2">
         <v>500</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E34" s="2">
         <v>1</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E35" s="2">
         <v>1</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="E36" s="2">
         <v>1</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="E37" s="2">
         <v>1</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B38" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
       <c r="G38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H38" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H38" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
+      <c r="B39" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
     </row>
@@ -14653,15 +14624,15 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
+      <c r="B40" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
       <c r="G40" s="9" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H40" s="10"/>
     </row>
@@ -14669,228 +14640,247 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
+      <c r="B41" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
       <c r="G41" s="9"/>
       <c r="H41" s="10" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
+      <c r="B42" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
       <c r="G42" s="9"/>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="C43" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D43" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F43" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H43" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E44" s="2">
         <v>500</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E45" s="2">
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H45" s="10"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E46" s="2">
         <v>2</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H46" s="10"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E47" s="2">
         <v>2</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H47" s="10"/>
     </row>
     <row r="48" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E48" s="2">
         <v>2</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H48" s="10"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D49" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E49" s="2">
         <v>2</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H49" s="10"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="E50" s="2">
         <v>2</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H50" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B42:F42"/>
@@ -14903,25 +14893,6 @@
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -14969,89 +14940,87 @@
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B2" s="24"/>
-      <c r="C2" s="24" t="s">
-        <v>59</v>
-      </c>
+      <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
       <c r="G3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="E5" s="22"/>
       <c r="F5" s="22"/>
       <c r="G5" s="22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="22"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
       <c r="G6" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6" s="26"/>
     </row>
@@ -15063,7 +15032,7 @@
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
       <c r="G7" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" s="26"/>
     </row>
@@ -15075,7 +15044,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -15087,57 +15056,57 @@
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
       <c r="G9" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="B11" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -15145,31 +15114,31 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>24</v>
-      </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="B14" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -15177,15 +15146,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="21"/>
+      <c r="B15" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20"/>
       <c r="G15" s="9" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -15193,241 +15162,241 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="B16" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="H16" s="10"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="F17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="G17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H17" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2">
         <v>376</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2">
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2">
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2">
         <v>35</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E22" s="2">
         <v>0.56999999999999995</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E23" s="2">
         <v>0.3</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H24" s="10"/>
     </row>
     <row r="25" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
       <c r="G25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H25" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -15435,15 +15404,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="B27" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -15451,13 +15420,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
@@ -15465,193 +15434,193 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="B29" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="9" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="H29" s="10"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="C30" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="F30" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H30" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H30" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" s="2">
         <v>376</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H33" s="10"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="E34" s="2">
         <v>1</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H34" s="10"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="E35" s="2">
         <v>1</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H35" s="10"/>
     </row>
     <row r="36" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
       <c r="G36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H36" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="19" t="s">
-        <v>217</v>
-      </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
+      <c r="B37" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
     </row>
@@ -15659,15 +15628,15 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
+      <c r="B38" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
       <c r="G38" s="9" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -15675,164 +15644,183 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
+      <c r="B39" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
       <c r="G39" s="9"/>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="F40" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H40" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H40" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E41" s="2">
         <v>376</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E42" s="2">
         <v>2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H42" s="10"/>
     </row>
     <row r="43" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E43" s="2">
         <v>2</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="D44" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E44" s="2">
         <v>2</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="E45" s="2">
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H45" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B39:F39"/>
@@ -15844,25 +15832,6 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -15910,89 +15879,87 @@
     </row>
     <row r="2" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B2" s="24"/>
-      <c r="C2" s="24" t="s">
-        <v>62</v>
-      </c>
+      <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
       <c r="G3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="E5" s="22"/>
       <c r="F5" s="22"/>
       <c r="G5" s="22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="22"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
       <c r="G6" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6" s="26"/>
     </row>
@@ -16004,7 +15971,7 @@
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
       <c r="G7" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" s="26"/>
     </row>
@@ -16016,7 +15983,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -16028,57 +15995,57 @@
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
       <c r="G9" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="B11" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -16086,15 +16053,15 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="B13" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H13" s="10"/>
     </row>
@@ -16103,14 +16070,14 @@
         <v>1</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="21"/>
+        <v>192</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="20"/>
       <c r="G14" s="9" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -16118,241 +16085,241 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="B15" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
       <c r="G15" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="G16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2">
         <v>520</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2">
         <v>12</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2">
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2">
         <v>35</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E21" s="2">
         <v>0.56999999999999995</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E22" s="2">
         <v>0.3</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="B25" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -16360,15 +16327,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H26" s="10"/>
     </row>
@@ -16376,13 +16343,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="B27" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
@@ -16390,145 +16357,145 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="18" t="s">
+        <v>189</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="C29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H29" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H30" s="10"/>
     </row>
     <row r="31" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E31" s="2">
         <v>1</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
       <c r="G33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H33" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="8">
         <v>3</v>
       </c>
-      <c r="B34" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
+      <c r="B34" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
     </row>
@@ -16536,15 +16503,15 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
+      <c r="B35" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
       <c r="G35" s="9" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -16552,116 +16519,135 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
+      <c r="B36" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
       <c r="G36" s="9"/>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="C37" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H37" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E38" s="2">
         <v>520</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E39" s="2">
         <v>2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E40" s="2">
         <v>2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H40" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B15:F15"/>
@@ -16672,25 +16658,6 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -16738,89 +16705,87 @@
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B2" s="24"/>
-      <c r="C2" s="24" t="s">
-        <v>68</v>
-      </c>
+      <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
       <c r="G3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>13</v>
       </c>
       <c r="E5" s="22"/>
       <c r="F5" s="22"/>
       <c r="G5" s="22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H5" s="22"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
       <c r="G6" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H6" s="26"/>
     </row>
@@ -16832,7 +16797,7 @@
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
       <c r="G7" s="26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" s="26"/>
     </row>
@@ -16844,7 +16809,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -16856,57 +16821,57 @@
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
       <c r="G9" s="26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" s="26"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="B11" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -16914,15 +16879,15 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="B13" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H13" s="10"/>
     </row>
@@ -16930,15 +16895,15 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="B14" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -16946,241 +16911,241 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="B15" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
       <c r="G15" s="9" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="G16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H16" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2">
         <v>460</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2">
         <v>12</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H18" s="10"/>
     </row>
     <row r="19" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="2">
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="H19" s="10"/>
     </row>
     <row r="20" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2">
         <v>40</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H20" s="10"/>
     </row>
     <row r="21" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E21" s="2">
         <v>0.54</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H21" s="10"/>
     </row>
     <row r="22" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="E22" s="2">
         <v>0.2</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="H22" s="10"/>
     </row>
     <row r="23" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="B25" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -17188,15 +17153,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="H26" s="10"/>
     </row>
@@ -17204,13 +17169,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="B27" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
@@ -17218,145 +17183,145 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H28" s="10"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="C29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="F29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F29" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H29" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H29" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E30" s="2">
         <v>1</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H30" s="10"/>
     </row>
     <row r="31" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E31" s="2">
         <v>1</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E32" s="2">
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H32" s="10"/>
     </row>
     <row r="33" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
+        <v>4</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
       <c r="G33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H33" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H33" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="8">
         <v>3</v>
       </c>
-      <c r="B34" s="19" t="s">
-        <v>223</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
+      <c r="B34" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
     </row>
@@ -17364,15 +17329,15 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
+      <c r="B35" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
       <c r="G35" s="9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -17380,116 +17345,135 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
+      <c r="B36" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
       <c r="G36" s="9"/>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="C37" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="D37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="F37" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F37" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="G37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H37" s="15" t="s">
         <v>7</v>
-      </c>
-      <c r="H37" s="15" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E38" s="2">
         <v>460</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E39" s="2">
         <v>2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E40" s="2">
         <v>2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H40" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B36:F36"/>
@@ -17500,25 +17484,6 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD3E49A1-ED82-40F1-98C2-04E714393CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BFE21B-C3AF-4926-9633-0B8D4F08B8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6825" yWindow="3030" windowWidth="21600" windowHeight="12645" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29580" yWindow="780" windowWidth="43200" windowHeight="23445" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -256,18 +256,6 @@
     <t>Hypoxemic Respiratory Failure Plugged ETT</t>
   </si>
   <si>
-    <t>A 25 year-old soldier was injured following an IED detonation while dismounted. He suffered a traumatic amputation of the right lower extremity below the knee, multiple puncture wounds from fragments in the left lower extremity and lost consciousness at the scene. A tourniquet was applied and the hemorrhage mitigated.  Both eardrums were ruptured and his GCS was 12.  He underwent a massive transfusion, received 10 units of whole blood, crystalloid infusions and platelets. In the operating room primary control of hemorrhage was achieved and the lower extremity amputation addressed using standard techniques. The patient arrived from the operating room on mechanical ventilation. He was sedated and is not currently triggering the ventilator. The patient is 5'9" tall, weighs 170 lbs and has no known comorbidities or allergies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A 28 year old sailor suffered a crush injury during the transfer of supplies from a fork lift.  She suffered an open book pelvic fracture, ruptured bladder and splenic laceration.  She required a massive transfusion and intraoperative open reduction and internal fixation of the pelvic fracture.  The spleen was removed and the bladder repaired.  Blood loss was estimated at 2.5 L. The sailor is 5'5" and weighs 138 lbs.  </t>
-  </si>
-  <si>
-    <t>A 23 year old soldier suffered developed shortness of breath, substernal chest pain and a productive cough following burn pit exposure. He was started on broad spectrum antibiotics and steroids for a suspected respiratory tract infection.  Initial chest x-ray demonstrated some minor hilar infiltrates. On day 5 of his antibiotic course he developed worsening dyspnea, was febrile to 39.5 degC, a breathing frequency of 32 bpm and his SpO2 was 91%. He was placed on high flow nasal cannula at 50% and 40 L/min.  After 12 hours he was intubated.  The soldier is 6'3" and weighs 215 lbs.  Suctioning reveals thick, tenacious, brownish-yellow secretions.  Therapeutic bronchoscopy is performed and 15-20 ml secretions removed and sent for culture and sensitivity. Initial gram stain suggests acinetobacter baumanni. Antibiotics are changed to a carbapenem. He is scheduled for CCATT to definitive care in the morning.</t>
-  </si>
-  <si>
-    <t>A 54-year-old, Black contractor was injured in a motor vehicle accident sustaining multiple rib fractures and pulmonary contusion. He lost consciousness at the scene, sustained a complex jaw fracture, near transection of the tongue with significant blood loss and noted to have blood in the trachea at intubation.  His initial chest x-ray demonstrated right middle lobe consolidation and some evidence of hyperinflation.  The patient has a smoking history of 2 packs per day for 35 years and has primary hypertension managed with drug therapy.   He is 5'8" and weighs 235 lbs.  Suctioning reveals a moderate amount of old blood. Gram stain of secretions shows no bacteria. He is scheduled for CCATT to definitive care that night.</t>
-  </si>
-  <si>
     <t>{ "PatientAction": {
       "AirwayObstruction": {
         "Severity": {
@@ -494,9 +482,6 @@
   </si>
   <si>
     <t>VT (measured)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A 22 year-old soldier was involved in a motor vehicle crash with rollover and ejection from the vehicle.  He suffered multiple rib fractures, a right femur fracture, multiple lacerations and pulmonary contusion.  He underwent internal fixation of the femur fracture, received 4 units of whole blood, had a chest tube placed for a small hemothorax and returned from the operating room on mechanical ventilation. The patient is sedated and is not currently triggering the ventilator.  Intraoperatively 3 L of crystalloids were administered. The patient is 6'2" tall, weighs 200 lbs and has no known comorbidities or allergies.  Chest radiograph demonstrates bi-basilar early consolidation, presence of the chest tube and pulmonary contusion. </t>
   </si>
   <si>
     <t xml:space="preserve">    { "PatientAction": { "ChronicObstructivePulmonaryDiseaseExacerbation":
@@ -571,9 +556,6 @@
 Recommended Actions:
  - Goal shifts to Comfort (imprive synchrony) due to cycle dyssychrony
  - Consider switching mode to PC-CSV (ie Pressure Support)</t>
-  </si>
-  <si>
-    <t>A 25 year-old active duty Marine was involved in a training accident where a Humvee was wrecked. She has a mild traumatic brain injury, flail chest and pulmonary contusions. The patient is 5'7" tall, weighs 170 lbs and has no known allergies. She is sedated and not triggering the ventilator.</t>
   </si>
   <si>
     <t>The patient is loaded in the aircraft for transport to SAMMC. Halfway through the flight the ventilator starts alarming high inspiratory pressure. The SpO2 falls while PIP and Pplat increase.  Heart rate decreases, and blood pressure remains constant. The patient is now triggering the ventilator at a much higher rate.
@@ -774,9 +756,6 @@
 </t>
   </si>
   <si>
-    <t>A 62 year-old contractor developed pneumonia while working on a water purification system. He has 90- pack year history of cigarette smoking (2 packs per day x 45 years), has type II diabetes and primary hypertension managed with oral medications. He uses a rescue inhaler (albuterol) and is on a maintenance inhaled corticosteroid. His pre-deployment FEV-1 is 43% of predicted. The patient is 5'9" tall, weighs 210 lbs and has no known allergies. Chest radiograph demonstrates left-lower lobe consolidation, haziness in the right lower lobe, flattened diaphragms and hyperinflation in the upper lung fields. Heart rate is normal sinus rhythm and occasional PVC's. Patient is sedated and not triggering ventilator.</t>
-  </si>
-  <si>
     <t>Learning Objectives:
  - Assess baseline status
  - Recognize presence of autoPEEP (from flow waveform)
@@ -1031,6 +1010,27 @@
   </si>
   <si>
     <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario7-InsultsOutcome.json"} }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 22 year-old soldier was involved in a motor vehicle crash with rollover and ejection from the vehicle.  He suffered multiple rib fractures, a right femur fracture, multiple lacerations and pulmonary contusion.  He underwent internal fixation of the femur fracture, received 4 units of whole blood, had a chest tube placed for a small hemothorax and returned from the operating room on mechanical ventilation. The patient is sedated and is not currently triggering the ventilator.  Intraoperatively 3 L of crystalloids were administered. The patient is 6'2'' tall, weighs 200 lbs and has no known comorbidities or allergies.  Chest radiograph demonstrates bi-basilar early consolidation, presence of the chest tube and pulmonary contusion. </t>
+  </si>
+  <si>
+    <t>A 62 year-old contractor developed pneumonia while working on a water purification system. He has 90- pack year history of cigarette smoking (2 packs per day x 45 years), has type II diabetes and primary hypertension managed with oral medications. He uses a rescue inhaler (albuterol) and is on a maintenance inhaled corticosteroid. His pre-deployment FEV-1 is 43% of predicted. The patient is 5'9'' tall, weighs 210 lbs and has no known allergies. Chest radiograph demonstrates left-lower lobe consolidation, haziness in the right lower lobe, flattened diaphragms and hyperinflation in the upper lung fields. Heart rate is normal sinus rhythm and occasional PVC's. Patient is sedated and not triggering ventilator.</t>
+  </si>
+  <si>
+    <t>A 25 year-old active duty Marine was involved in a training accident where a Humvee was wrecked. She has a mild traumatic brain injury, flail chest and pulmonary contusions. The patient is 5'7'' tall, weighs 170 lbs and has no known allergies. She is sedated and not triggering the ventilator.</t>
+  </si>
+  <si>
+    <t>A 25 year-old soldier was injured following an IED detonation while dismounted. He suffered a traumatic amputation of the right lower extremity below the knee, multiple puncture wounds from fragments in the left lower extremity and lost consciousness at the scene. A tourniquet was applied and the hemorrhage mitigated.  Both eardrums were ruptured and his GCS was 12.  He underwent a massive transfusion, received 10 units of whole blood, crystalloid infusions and platelets. In the operating room primary control of hemorrhage was achieved and the lower extremity amputation addressed using standard techniques. The patient arrived from the operating room on mechanical ventilation. He was sedated and is not currently triggering the ventilator. The patient is 5'9'' tall, weighs 170 lbs and has no known comorbidities or allergies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 28 year old sailor suffered a crush injury during the transfer of supplies from a fork lift.  She suffered an open book pelvic fracture, ruptured bladder and splenic laceration.  She required a massive transfusion and intraoperative open reduction and internal fixation of the pelvic fracture.  The spleen was removed and the bladder repaired.  Blood loss was estimated at 2.5 L. The sailor is 5'5'' and weighs 138 lbs.  </t>
+  </si>
+  <si>
+    <t>A 23 year old soldier suffered developed shortness of breath, substernal chest pain and a productive cough following burn pit exposure. He was started on broad spectrum antibiotics and steroids for a suspected respiratory tract infection.  Initial chest x-ray demonstrated some minor hilar infiltrates. On day 5 of his antibiotic course he developed worsening dyspnea, was febrile to 39.5 degC, a breathing frequency of 32 bpm and his SpO2 was 91%. He was placed on high flow nasal cannula at 50% and 40 L/min.  After 12 hours he was intubated.  The soldier is 6'3'' and weighs 215 lbs.  Suctioning reveals thick, tenacious, brownish-yellow secretions.  Therapeutic bronchoscopy is performed and 15-20 ml secretions removed and sent for culture and sensitivity. Initial gram stain suggests acinetobacter baumanni. Antibiotics are changed to a carbapenem. He is scheduled for CCATT to definitive care in the morning.</t>
+  </si>
+  <si>
+    <t>A 54-year-old, Black contractor was injured in a motor vehicle accident sustaining multiple rib fractures and pulmonary contusion. He lost consciousness at the scene, sustained a complex jaw fracture, near transection of the tongue with significant blood loss and noted to have blood in the trachea at intubation.  His initial chest x-ray demonstrated right middle lobe consolidation and some evidence of hyperinflation.  The patient has a smoking history of 2 packs per day for 35 years and has primary hypertension managed with drug therapy.   He is 5'8'' and weighs 235 lbs.  Suctioning reveals a moderate amount of old blood. Gram stain of secretions shows no bacteria. He is scheduled for CCATT to definitive care that night.</t>
   </si>
 </sst>
 </file>
@@ -1268,6 +1268,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1276,9 +1279,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1728,16 +1728,16 @@
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>133</v>
+        <v>210</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -1768,11 +1768,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -1830,7 +1830,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -1850,13 +1850,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1868,13 +1868,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>22</v>
@@ -1884,15 +1884,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>155</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -1900,13 +1900,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>24</v>
@@ -1916,13 +1916,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -1930,15 +1930,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>170</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="20"/>
+      <c r="B15" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="9" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -1946,13 +1946,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="B16" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -1999,10 +1999,10 @@
         <v>567</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -2011,7 +2011,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>42</v>
@@ -2023,10 +2023,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -2035,7 +2035,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>42</v>
@@ -2047,10 +2047,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -2059,7 +2059,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>41</v>
@@ -2071,10 +2071,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -2083,7 +2083,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -2095,10 +2095,10 @@
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -2107,7 +2107,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
@@ -2119,10 +2119,10 @@
         <v>0.2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -2137,16 +2137,16 @@
         <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -2154,13 +2154,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -2172,13 +2172,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>197</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="B26" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -2186,15 +2186,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H27" s="9"/>
     </row>
@@ -2202,15 +2202,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="B28" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="9" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -2218,13 +2218,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>196</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
+      <c r="B29" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
@@ -2232,13 +2232,13 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
+      <c r="B30" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
     </row>
@@ -2285,10 +2285,10 @@
         <v>567</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -2297,7 +2297,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>42</v>
@@ -2309,10 +2309,10 @@
         <v>12</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -2321,7 +2321,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>42</v>
@@ -2333,10 +2333,10 @@
         <v>12</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -2345,7 +2345,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>41</v>
@@ -2357,10 +2357,10 @@
         <v>35</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -2369,7 +2369,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>30</v>
@@ -2381,10 +2381,10 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -2393,7 +2393,7 @@
         <v>29</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>30</v>
@@ -2405,10 +2405,10 @@
         <v>0.3</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -2423,16 +2423,16 @@
         <v>35</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -2440,13 +2440,13 @@
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
       <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
@@ -2458,13 +2458,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="18" t="s">
-        <v>198</v>
-      </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
+      <c r="B40" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
@@ -2472,15 +2472,15 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="20"/>
+      <c r="B41" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="21"/>
       <c r="G41" s="9" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -2488,13 +2488,13 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
+      <c r="B42" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
       <c r="G42" s="9"/>
       <c r="H42" s="10"/>
     </row>
@@ -2541,10 +2541,10 @@
         <v>490</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -2565,10 +2565,10 @@
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H45" s="10"/>
     </row>
@@ -2577,22 +2577,22 @@
         <v>29</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E46" s="2">
         <v>2</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H46" s="10"/>
     </row>
@@ -2600,13 +2600,13 @@
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="18"/>
       <c r="G47" s="1" t="s">
         <v>6</v>
       </c>
@@ -2618,15 +2618,15 @@
       <c r="A48" s="8">
         <v>4</v>
       </c>
-      <c r="B48" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="20"/>
+      <c r="B48" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="21"/>
       <c r="G48" s="9" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="H48" s="10"/>
     </row>
@@ -2634,13 +2634,13 @@
       <c r="A49" s="8">
         <v>4</v>
       </c>
-      <c r="B49" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
+      <c r="B49" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
       <c r="G49" s="9"/>
       <c r="H49" s="10"/>
     </row>
@@ -2687,10 +2687,10 @@
         <v>490</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H51" s="10"/>
     </row>
@@ -2699,7 +2699,7 @@
         <v>29</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>41</v>
@@ -2711,10 +2711,10 @@
         <v>3</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H52" s="10"/>
     </row>
@@ -2729,16 +2729,16 @@
         <v>35</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E53" s="2">
         <v>3</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H53" s="10"/>
     </row>
@@ -2759,10 +2759,10 @@
         <v>3</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H54" s="10"/>
     </row>
@@ -2783,10 +2783,10 @@
         <v>3</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H55" s="10"/>
     </row>
@@ -2795,7 +2795,7 @@
         <v>29</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>30</v>
@@ -2807,15 +2807,33 @@
         <v>3</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="H56" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B49:F49"/>
@@ -2832,24 +2850,6 @@
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B29:F29"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2905,10 +2905,10 @@
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -2937,11 +2937,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -3005,7 +3005,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -3025,13 +3025,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3043,13 +3043,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>22</v>
@@ -3059,15 +3059,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -3075,13 +3075,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10"/>
     </row>
@@ -3089,13 +3089,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -3103,15 +3103,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>183</v>
-      </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="B15" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -3119,13 +3119,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="B16" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
@@ -3172,10 +3172,10 @@
         <v>600</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -3184,7 +3184,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>42</v>
@@ -3196,10 +3196,10 @@
         <v>24</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -3208,7 +3208,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>42</v>
@@ -3220,10 +3220,10 @@
         <v>36</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -3232,7 +3232,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>41</v>
@@ -3244,10 +3244,10 @@
         <v>68</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -3256,7 +3256,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -3268,10 +3268,10 @@
         <v>0.49</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -3280,7 +3280,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
@@ -3292,10 +3292,10 @@
         <v>0.19</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -3303,13 +3303,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -3321,13 +3321,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="B25" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -3335,15 +3335,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="B26" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="H26" s="9"/>
     </row>
@@ -3365,13 +3365,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="B28" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
@@ -3379,13 +3379,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
+      <c r="B29" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
       <c r="G29" s="9"/>
       <c r="H29" s="10"/>
     </row>
@@ -3432,10 +3432,10 @@
         <v>600</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -3444,7 +3444,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>42</v>
@@ -3456,10 +3456,10 @@
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -3468,7 +3468,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>42</v>
@@ -3480,10 +3480,10 @@
         <v>1</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -3504,10 +3504,10 @@
         <v>1</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -3528,10 +3528,10 @@
         <v>1</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -3539,13 +3539,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -3557,13 +3557,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
+      <c r="B37" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
     </row>
@@ -3574,12 +3574,12 @@
       <c r="B38" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="21"/>
       <c r="G38" s="9" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -3587,13 +3587,13 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
+      <c r="B39" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
       <c r="G39" s="9"/>
       <c r="H39" s="10"/>
     </row>
@@ -3640,10 +3640,10 @@
         <v>600</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -3652,7 +3652,7 @@
         <v>29</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>42</v>
@@ -3664,10 +3664,10 @@
         <v>2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H42" s="10"/>
     </row>
@@ -3676,7 +3676,7 @@
         <v>29</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>42</v>
@@ -3688,10 +3688,10 @@
         <v>2</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H43" s="10"/>
     </row>
@@ -3712,10 +3712,10 @@
         <v>2</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -3736,35 +3736,15 @@
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H45" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B38:F38"/>
@@ -3776,6 +3756,26 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3829,10 +3829,10 @@
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>150</v>
+        <v>212</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -3859,11 +3859,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -3927,7 +3927,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -3947,13 +3947,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3968,10 +3968,10 @@
       <c r="B11" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="21"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>22</v>
@@ -3981,15 +3981,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -3997,13 +3997,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10" t="s">
         <v>24</v>
@@ -4013,13 +4013,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -4027,15 +4027,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="B15" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -4043,13 +4043,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="B16" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
@@ -4096,10 +4096,10 @@
         <v>420</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -4108,7 +4108,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>42</v>
@@ -4120,10 +4120,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -4132,7 +4132,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>42</v>
@@ -4144,10 +4144,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -4156,7 +4156,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>41</v>
@@ -4168,10 +4168,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -4180,7 +4180,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -4192,10 +4192,10 @@
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -4204,7 +4204,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
@@ -4216,10 +4216,10 @@
         <v>0.2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -4234,16 +4234,16 @@
         <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -4251,13 +4251,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -5285,13 +5285,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="B26" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -5299,15 +5299,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="14"/>
@@ -6331,15 +6331,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>169</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="B28" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="9" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="14"/>
@@ -7363,13 +7363,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
+      <c r="B29" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
@@ -7377,13 +7377,13 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
+      <c r="B30" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
       <c r="H30" s="10"/>
       <c r="I30" s="14"/>
       <c r="J30" s="14"/>
@@ -9461,10 +9461,10 @@
         <v>420</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -9473,7 +9473,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>42</v>
@@ -9485,10 +9485,10 @@
         <v>12</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -9497,7 +9497,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>42</v>
@@ -9509,10 +9509,10 @@
         <v>12</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -9521,7 +9521,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>41</v>
@@ -9533,10 +9533,10 @@
         <v>33</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -9545,7 +9545,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>30</v>
@@ -9557,10 +9557,10 @@
         <v>0.65</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -9569,7 +9569,7 @@
         <v>29</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>30</v>
@@ -9581,10 +9581,10 @@
         <v>0.4</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -9599,16 +9599,16 @@
         <v>35</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="E38" s="2">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -9616,13 +9616,13 @@
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
       <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
@@ -10650,13 +10650,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
+      <c r="B40" s="19" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
@@ -10664,15 +10664,15 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
+      <c r="B41" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
       <c r="G41" s="9" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="H41" s="10"/>
       <c r="I41" s="14"/>
@@ -11696,13 +11696,13 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
+      <c r="B42" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
       <c r="G42" s="9"/>
       <c r="H42" s="10"/>
       <c r="I42" s="14"/>
@@ -13781,10 +13781,10 @@
         <v>340</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -13805,34 +13805,15 @@
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H45" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B41:F41"/>
@@ -13845,6 +13826,25 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -13898,10 +13898,10 @@
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>62</v>
+        <v>213</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -13928,11 +13928,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -13996,7 +13996,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -14016,13 +14016,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -14034,13 +14034,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>22</v>
@@ -14050,15 +14050,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -14066,13 +14066,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10" t="s">
         <v>24</v>
@@ -14082,13 +14082,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -14096,15 +14096,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="20"/>
+      <c r="B15" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="9" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -14112,13 +14112,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="B16" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
@@ -14165,10 +14165,10 @@
         <v>500</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -14177,7 +14177,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>42</v>
@@ -14189,10 +14189,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -14201,7 +14201,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>42</v>
@@ -14213,10 +14213,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -14225,7 +14225,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>41</v>
@@ -14237,10 +14237,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -14249,7 +14249,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -14261,10 +14261,10 @@
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -14273,7 +14273,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
@@ -14285,10 +14285,10 @@
         <v>0.2</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -14303,16 +14303,16 @@
         <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -14320,13 +14320,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -14338,13 +14338,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="B26" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -14352,15 +14352,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>190</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="B27" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -14368,13 +14368,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="B28" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
@@ -14382,15 +14382,15 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
+      <c r="B29" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
       <c r="G29" s="9" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="H29" s="10"/>
     </row>
@@ -14437,10 +14437,10 @@
         <v>500</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -14449,7 +14449,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>41</v>
@@ -14464,7 +14464,7 @@
         <v>32</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -14488,7 +14488,7 @@
         <v>32</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -14512,7 +14512,7 @@
         <v>32</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -14533,10 +14533,10 @@
         <v>1</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -14560,7 +14560,7 @@
         <v>32</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -14584,7 +14584,7 @@
         <v>32</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -14592,13 +14592,13 @@
       <c r="A38" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
       <c r="G38" s="1" t="s">
         <v>6</v>
       </c>
@@ -14610,13 +14610,13 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>207</v>
-      </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
+      <c r="B39" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
     </row>
@@ -14624,15 +14624,15 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
       <c r="G40" s="9" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H40" s="10"/>
     </row>
@@ -14640,29 +14640,29 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="18" t="s">
-        <v>185</v>
-      </c>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
+      <c r="B41" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
       <c r="G41" s="9"/>
       <c r="H41" s="10" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
+      <c r="B42" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
       <c r="G42" s="9"/>
       <c r="H42" s="10"/>
     </row>
@@ -14709,10 +14709,10 @@
         <v>500</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -14721,7 +14721,7 @@
         <v>29</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>41</v>
@@ -14736,7 +14736,7 @@
         <v>32</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H45" s="10"/>
     </row>
@@ -14760,7 +14760,7 @@
         <v>32</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H46" s="10"/>
     </row>
@@ -14784,7 +14784,7 @@
         <v>32</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H47" s="10"/>
     </row>
@@ -14805,10 +14805,10 @@
         <v>2</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H48" s="10"/>
     </row>
@@ -14832,7 +14832,7 @@
         <v>32</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H49" s="10"/>
     </row>
@@ -14856,31 +14856,12 @@
         <v>32</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H50" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B42:F42"/>
@@ -14893,6 +14874,25 @@
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -14946,10 +14946,10 @@
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>63</v>
+        <v>214</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -14976,11 +14976,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -15044,7 +15044,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -15064,13 +15064,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -15082,13 +15082,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>22</v>
@@ -15098,15 +15098,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -15114,15 +15114,15 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H13" s="10" t="s">
         <v>24</v>
@@ -15132,13 +15132,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -15146,15 +15146,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="20"/>
+      <c r="B15" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="9" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -15162,15 +15162,15 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="B16" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
       <c r="G16" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="H16" s="10"/>
     </row>
@@ -15217,10 +15217,10 @@
         <v>376</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -15229,7 +15229,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>42</v>
@@ -15241,10 +15241,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -15253,7 +15253,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>42</v>
@@ -15265,10 +15265,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -15277,7 +15277,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>41</v>
@@ -15289,10 +15289,10 @@
         <v>35</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -15301,7 +15301,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -15313,10 +15313,10 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -15325,7 +15325,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
@@ -15337,10 +15337,10 @@
         <v>0.3</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -15355,16 +15355,16 @@
         <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -15372,13 +15372,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -15390,13 +15390,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="B26" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -15404,15 +15404,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -15420,13 +15420,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="B28" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
@@ -15434,15 +15434,15 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
+      <c r="B29" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
       <c r="G29" s="9" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H29" s="10"/>
     </row>
@@ -15489,10 +15489,10 @@
         <v>376</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -15501,7 +15501,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>41</v>
@@ -15516,7 +15516,7 @@
         <v>32</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -15537,10 +15537,10 @@
         <v>1</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -15564,7 +15564,7 @@
         <v>32</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -15588,7 +15588,7 @@
         <v>32</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -15596,13 +15596,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -15614,13 +15614,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
+      <c r="B37" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
     </row>
@@ -15628,15 +15628,15 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
       <c r="G38" s="9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -15644,13 +15644,13 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
+      <c r="B39" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
       <c r="G39" s="9"/>
       <c r="H39" s="10"/>
     </row>
@@ -15697,10 +15697,10 @@
         <v>376</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -15709,7 +15709,7 @@
         <v>29</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>41</v>
@@ -15724,7 +15724,7 @@
         <v>32</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="H42" s="10"/>
     </row>
@@ -15745,10 +15745,10 @@
         <v>2</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H43" s="10"/>
     </row>
@@ -15772,7 +15772,7 @@
         <v>32</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -15796,31 +15796,12 @@
         <v>32</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H45" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B39:F39"/>
@@ -15832,6 +15813,25 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -15885,10 +15885,10 @@
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>64</v>
+        <v>215</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -15915,11 +15915,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -15983,7 +15983,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -16003,13 +16003,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -16021,13 +16021,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>22</v>
@@ -16037,15 +16037,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -16053,13 +16053,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>57</v>
       </c>
@@ -16070,14 +16070,14 @@
         <v>1</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>192</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="20"/>
+        <v>185</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="21"/>
       <c r="G14" s="9" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -16085,15 +16085,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="B15" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -16140,10 +16140,10 @@
         <v>520</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H17" s="10"/>
     </row>
@@ -16152,7 +16152,7 @@
         <v>29</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>42</v>
@@ -16164,10 +16164,10 @@
         <v>12</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -16176,7 +16176,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>42</v>
@@ -16188,10 +16188,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -16200,7 +16200,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>41</v>
@@ -16212,10 +16212,10 @@
         <v>35</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -16224,7 +16224,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>30</v>
@@ -16236,10 +16236,10 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -16248,7 +16248,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -16260,10 +16260,10 @@
         <v>0.3</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -16278,16 +16278,16 @@
         <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -16295,13 +16295,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -16313,13 +16313,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>211</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="B25" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -16327,15 +16327,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="B26" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H26" s="10"/>
     </row>
@@ -16343,13 +16343,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="B27" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
@@ -16357,15 +16357,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>189</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="B28" s="19" t="s">
+        <v>182</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="9" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -16412,10 +16412,10 @@
         <v>1</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -16424,7 +16424,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>42</v>
@@ -16436,10 +16436,10 @@
         <v>1</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -16448,7 +16448,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>42</v>
@@ -16460,10 +16460,10 @@
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -16471,13 +16471,13 @@
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
       <c r="G33" s="1" t="s">
         <v>6</v>
       </c>
@@ -16489,13 +16489,13 @@
       <c r="A34" s="8">
         <v>3</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>212</v>
-      </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
+      <c r="B34" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
     </row>
@@ -16503,15 +16503,15 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
       <c r="G35" s="9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -16519,13 +16519,13 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+      <c r="B36" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
       <c r="G36" s="9"/>
       <c r="H36" s="10"/>
     </row>
@@ -16572,10 +16572,10 @@
         <v>520</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -16584,7 +16584,7 @@
         <v>29</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>42</v>
@@ -16596,10 +16596,10 @@
         <v>2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H39" s="10"/>
     </row>
@@ -16608,7 +16608,7 @@
         <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>42</v>
@@ -16620,34 +16620,15 @@
         <v>2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H40" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B15:F15"/>
@@ -16658,6 +16639,25 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -16711,10 +16711,10 @@
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>65</v>
+        <v>216</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -16741,11 +16741,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -16809,7 +16809,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -16829,13 +16829,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -16847,13 +16847,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>22</v>
@@ -16863,15 +16863,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="B12" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
       <c r="G12" s="9" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -16879,13 +16879,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
       <c r="G13" s="9" t="s">
         <v>57</v>
       </c>
@@ -16895,15 +16895,15 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="B14" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
       <c r="G14" s="9" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -16911,15 +16911,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="B15" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
       <c r="G15" s="9" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -16966,10 +16966,10 @@
         <v>460</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H17" s="10"/>
     </row>
@@ -16978,7 +16978,7 @@
         <v>29</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>42</v>
@@ -16990,10 +16990,10 @@
         <v>12</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -17002,7 +17002,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>42</v>
@@ -17014,10 +17014,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -17026,7 +17026,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>41</v>
@@ -17038,10 +17038,10 @@
         <v>40</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -17050,7 +17050,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>30</v>
@@ -17062,10 +17062,10 @@
         <v>0.54</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -17074,7 +17074,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -17086,10 +17086,10 @@
         <v>0.2</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -17104,16 +17104,16 @@
         <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -17121,13 +17121,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -17139,13 +17139,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="18" t="s">
-        <v>214</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="B25" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -17153,15 +17153,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="B26" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
       <c r="G26" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H26" s="10"/>
     </row>
@@ -17169,13 +17169,13 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="B27" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
@@ -17183,15 +17183,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="B28" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="9" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -17238,10 +17238,10 @@
         <v>1</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -17250,7 +17250,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>42</v>
@@ -17262,10 +17262,10 @@
         <v>1</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -17274,7 +17274,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>42</v>
@@ -17286,10 +17286,10 @@
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -17297,13 +17297,13 @@
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
       <c r="G33" s="1" t="s">
         <v>6</v>
       </c>
@@ -17315,13 +17315,13 @@
       <c r="A34" s="8">
         <v>3</v>
       </c>
-      <c r="B34" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18"/>
+      <c r="B34" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
     </row>
@@ -17329,15 +17329,15 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
       <c r="G35" s="9" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -17345,13 +17345,13 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+      <c r="B36" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
       <c r="G36" s="9"/>
       <c r="H36" s="10"/>
     </row>
@@ -17398,10 +17398,10 @@
         <v>460</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -17410,7 +17410,7 @@
         <v>29</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>42</v>
@@ -17422,10 +17422,10 @@
         <v>2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H39" s="10"/>
     </row>
@@ -17434,7 +17434,7 @@
         <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>42</v>
@@ -17446,34 +17446,15 @@
         <v>2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H40" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B36:F36"/>
@@ -17484,6 +17465,25 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programming\Pulse\engine\data\human\adult\validation\Scenarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BFE21B-C3AF-4926-9633-0B8D4F08B8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEC1198-A848-4AC9-A553-FBC82454F1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29580" yWindow="780" windowWidth="43200" windowHeight="23445" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26280" yWindow="3165" windowWidth="31200" windowHeight="28275" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="215">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -235,9 +235,6 @@
     <t>Hypoxemic Respiratory Failure - Pneumonia</t>
   </si>
   <si>
-    <t xml:space="preserve">After intubation he is on mechanical ventilation and remains sedated with a RASS of -2. </t>
-  </si>
-  <si>
     <t>TidalVolume</t>
   </si>
   <si>
@@ -313,48 +310,7 @@
     <t>ExpiratoryRespiratoryResistance</t>
   </si>
   <si>
-    <t>Diagnosis: Mild ARDS.
-&lt;br /&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnosis: Pneumothorax.
-&lt;br /&gt;
-</t>
-  </si>
-  <si>
-    <t>Resolution of pneumothorax with needle decompression.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upon arrival to the recovery room she is on mechanical ventilation and remains sedated.  Upon arrival to the recovery room she is on mechanical ventilation and remains sedated.  </t>
-  </si>
-  <si>
-    <t>Diagnosis: Right Mainstem Intubation.
-&lt;br /&gt; &lt;br /&gt;</t>
-  </si>
-  <si>
     <t>Right mainstem resolution.</t>
-  </si>
-  <si>
-    <t>Suction patient.</t>
-  </si>
-  <si>
-    <t>Remove plug.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnosis: Mild ARDS.
-&lt;br /&gt; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnosis: Moderate ARDS.
-&lt;br /&gt; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnosis: Increased Secretions.
-&lt;br /&gt; </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnosis: ETT plug.
-&lt;br /&gt; </t>
   </si>
   <si>
     <t>PIP</t>
@@ -592,31 +548,6 @@
       { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.25 }}}]
   }}
 }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The patient is loaded in the aircraft for transport to level III care.  Twenty minutes into the transport SpO2 falls and PIP and Pplat are increased. (decreased compliance).  The patient remains sedated and is not triggering the ventilator.  </t>
-  </si>
-  <si>
-    <t>Vital signs demonstrate the response to injury.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The patient is agitated and PIP and Pplat have increased, SpO2 has fallen, and ETCO2 has decreased. </t>
-  </si>
-  <si>
-    <t>The patient is loaded onto the aircraft for transfer to Level III care. During transport the patient becomes agitated and respiratory rate increases, SpO2 has fallen, and ETCO2 has increased.</t>
-  </si>
-  <si>
-    <t>Vital signs demonstrate a hyperdynamic response to illness blood gas suggests mild ARDS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnosis: Mild Pneumonia.
-&lt;br /&gt; </t>
-  </si>
-  <si>
-    <t>Vital signs demonstrate an appropriate response to illness. Blood gases suggests mild ARDS.</t>
-  </si>
-  <si>
-    <t>The patient is loaded onto the aircraft for transfer to Level III care. During transport the patient is heavily sedated.  Immediately after take-off multiple ventilator alarms sound,  tidal volume falls, respiratory rate increases, SpO2 has fallen, and ETCO2 has increased. The patient is growing agitated.   Attempting to manually ventilate the patient meets extreme resistance and no air movement.</t>
   </si>
   <si>
     <t>Ventilator settings are:
@@ -905,13 +836,217 @@
     <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 3, "Unit": "min" }}}}</t>
   </si>
   <si>
+    <t>&lt;br /&gt;
+Ventilator settings are (delivered VT of 460 ml):
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| PC-CMV | NA     | 20          | NA           | NA  | 0.5    | 10       | 5            | 0.40 |</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario1-InsultsApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario1-InitialHemeostasis.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario1-InsultsOutcome.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario2-InitialHemeostasis.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario2-InsultsApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario2-InsultsOutcome.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario3-InitialHemeostasis.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario3-InsultsApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario3-InsultsOutcome.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario4-InitialHemeostasis.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario4-InsultsApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario4-InsultsOutcome.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario5-InitialHemeostasis.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario5-InsultsApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario5-InsultsOutcome.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario6-InitialHemeostasis.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario6-InsultsOutcome.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario6-InsultsApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario7-InitialHemeostasis.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario7-InsultsApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario7-InsultsOutcome.json"} }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 22 year-old soldier was involved in a motor vehicle crash with rollover and ejection from the vehicle.  He suffered multiple rib fractures, a right femur fracture, multiple lacerations and pulmonary contusion.  He underwent internal fixation of the femur fracture, received 4 units of whole blood, had a chest tube placed for a small hemothorax and returned from the operating room on mechanical ventilation. The patient is sedated and is not currently triggering the ventilator.  Intraoperatively 3 L of crystalloids were administered. The patient is 6'2'' tall, weighs 200 lbs and has no known comorbidities or allergies.  Chest radiograph demonstrates bi-basilar early consolidation, presence of the chest tube and pulmonary contusion. </t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Assess baseline status
+ - Recognize moderate ARDS
+Recommended Actions:
+ - Increase RR to 24/min to increase pH above 7.25
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The patient is loaded in the aircraft for transport to level III care.  Twenty minutes into the transport SpO2 falls and PIP and Pplat are increased (decreased compliance).  The patient remains sedated and is not triggering the ventilator.  </t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Recognize and treat pneumothorax
+Recommended Actions:
+ - Increase in Pplat without concomitant increase in PIP indicates abruptly decreased compliance
+ - This observation along with diminished breath sounds and hyper-resonance with percussion on one side indicate pneumothorax
+ - Recommend needle decompression
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>Needle decompression procedure performed.</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Recognize resolution of pneumothorax.
+Recommended Actions:
+ - SpO2, breath sounds, plateau pressure indicate pneumothorax resolved
+ - But pH low and DP high so decrease VT to 400 and increase RR to 30
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two hours later the patient is agitated. Both PIP and Pplat have increased. The SpO2 has fallen, and etCO2 has decreased. </t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Recognize right mainstem intubation and recommend repositioning of endotracheal tube
+Recommended Actions:
+ - Greatly increased DP, absence of breath sounds on the left side but normal sound to palpation indicate right mainstem intubation
+ - Reposition endotracheal tube and re-assess 
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Assess baseline status
+ - Recognize moderate ARDS
+Recommended Actions:
+ - Increase PEEP to 10 cm H2O  
+ - Consider increasing inspiratory time to eliminate early cycling
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The patient is loaded onto the aircraft for transfer to Level III care. During transport the patient becomes agitated and respiratory rate increases, SpO2 has fallen, and etPCO2 has increased. </t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Recognize hypoventilation due to increased secretions
+ - Recognize gas trapping due to high respiratory rate (expiratory flow does not return to zero)
+Recommended Actions:
+ - Check for pneumothorax
+ - Suction
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient is suctioned for large volume of thick secretions. </t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Recognize that suctioning decreased airway resistance and restored tidal volume)
+Recommended Actions:
+ - Increase PEEP to 10 cm H2O  
+ - Consider increasing inspiratory time to eliminate early cycling
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>A 54-year-old, Black contractor was injured in a motor vehicle accident sustaining multiple rib fractures and pulmonary contusion. He lost consciousness at the scene, sustained a complex jaw fracture, near transection of the tongue with significant blood loss and noted to have blood in the trachea at intubation. After intubation he is on mechanical ventilation and remains sedated with a RASS of -2
+His initial chest x-ray demonstrated right middle lobe consolidation and some evidence of hyperinflation. The patient has a smoking history of 2 packs per day for 35 years and has primary hypertension managed with drug therapy. He is 5'8'' and weighs 235 lbs. Suctioning reveals a moderate amount of old blood. Gram stain of secretions shows no bacteria. He is scheduled for CCATT to definitive care that night.</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Assess baseline status
+Recommended Actions:
+ - None
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The patient is loaded onto the aircraft for transfer to Level III care. During transport the patient is heavily sedated. Immediately after take-off multiple ventilator alarms sound, tidal volume falls, respiratory rate increases, SpO2 has fallen, and etPCO2 has increased. The patient is growing agitated. Attempting to manually ventilate the patient meets extreme resistance and no air movement. </t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ -  Recognize plugged ET tube
+Recommended Actions:
+ - Suction ET tube to remove obstruction 
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>Patient suctioned and ET tube obstruction removed.</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ -  Recognize success of suctioning 
+Recommended Actions:
+ - Consider increasing inspiratory time to eliminate early cycling 
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 23 year old soldier suffered developed shortness of breath, substernal chest pain and a productive cough following burn pit exposure. He was started on broad spectrum antibiotics and steroids for a suspected respiratory tract infection. Initial chest x-ray demonstrated some minor hilar infiltrates. On day 5 of his antibiotic course he developed worsening dyspnea, was febrile to 39.5 C, a breathing frequency of 32 bpm and his SpO2 was 91%. He was placed on high flow nasal cannula at 50% and 40 L/min. After 12 hours he was intubated.After intubation he is on mechanical ventilation and remains sedated with a RASS of -2.
+The soldier is 6'3'' and weighs 215 lbs. Suctioning reveals thick, tenacious, brownish-yellow secretions. Therapeutic bronchoscopy is performed and 15-20 mL secretions removed and sent for culture and sensitivity. Initial gram stain suggests acinetobacter baumanni. Antibiotics are changed to a carbapenem. He is scheduled for CCATT to definitive care in the morning. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 28 year old sailor suffered a crush injury during the transfer of supplies from a fork lift. She suffered an open book pelvic fracture, ruptured bladder and splenic laceration. She required a massive transfusion and intraoperative open reduction and internal fixation of the pelvic fracture. The spleen was removed and the bladder repaired. Blood loss was estimated at 2.5 L. The sailor is 5'5" and weighs 138 lbs. </t>
+  </si>
+  <si>
+    <t>A 25 year-old soldier was injured following an IED detonation while dismounted. He suffered a traumatic amputation of the right lower extremity below the knee, multiple puncture wounds from fragments in the left lower extremity and lost consciousness at the scene. A tourniquet was applied and the hemorrhage mitigated. Both eardrums were ruptured and his GCS was 12. He underwent a massive transfusion, received 10 units of whole blood, crystalloid infusions and platelets. In the operating room primary control of hemorrhage was achieved and the lower extremity amputation addressed using standard techniques. The patient arrived from the operating room on mechanical ventilation. He was sedated and is not currently triggering the ventilator. The patient is 5'9" tall, weighs 170 lbs and has no known comorbidities or allergies.</t>
+  </si>
+  <si>
+    <t>A 25 year-old active duty Marine was involved in a training accident where a Humvee was wrecked. She has a mild traumatic brain injury, flail chest and pulmonary contusions. The patient is 5'7" tall, weighs 170 lbs and has no known allergies. She is sedated and not triggering the ventilator.</t>
+  </si>
+  <si>
+    <t>A 62 year-old contractor developed pneumonia while working on a water purification system. He has 90- pack year history of cigarette smoking (2 packs per day x 45 years), has type II diabetes and primary hypertension managed with oral medications. He uses a rescue inhaler (albuterol) and is on a maintenance inhaled corticosteroid. His pre-deployment FEV-1 is 43% of predicted. The patient is 5'9" tall, weighs 210 lbs and has no known allergies.
+Chest radiograph demonstrates left-lower lobe consolidation, haziness in the right lower lobe, flattened diaphragms and hyperinflation in the upper lung fields. Heart rate is normal sinus rhythm and occasional PVC's. Patient is sedated and not triggering ventilator.</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Assess baseline status
+ - Recognize mild ARDS
+Recommended Actions:
+ - Increase RR to 24/min to increase pH above 7.25
+&lt;br /&gt;</t>
+  </si>
+  <si>
     <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
   { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
   "Mode": "AssistedControl", 
   "InspirationWaveform": "Square",
   "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.6 } },
   "InspiratoryPeriod": { "ScalarTime": { "Value": 0.5, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 24, "Unit": "cmH2O" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 26.5, "Unit": "cmH2O" } },
   "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
   "RespirationRate": { "ScalarFrequency": { "Value": 10, "Unit": "1/min" } },
    "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
@@ -920,11 +1055,11 @@
   </si>
   <si>
     <t>&lt;br /&gt;
-Ventilator settings are (delivered VT of 520 ml):
+Ventilator settings are (VT delivered = 6.9 mL/kg (ideal)):
 &lt;br /&gt;
 | Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
 | ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| PC-CMV | NA     | 24          | NA           | NA  | 0.5    | 10       | 8            | 0.60 |</t>
+| PC-CMV | NA     | 26.5          | NA           | NA  | 0.5    | 10       | 8            | 0.60 |</t>
   </si>
   <si>
     <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
@@ -936,101 +1071,9 @@
   "InspiratoryPressure": { "ScalarPressure": { "Value": 20, "Unit": "cmH2O" } },
   "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
   "RespirationRate": { "ScalarFrequency": { "Value": 10, "Unit": "1/min" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+   "InspirationPatientTriggerFlow": { "ScalarVolumePerTime": { "Value": 1.0, "Unit": "L/min" } }
   }}
 }</t>
-  </si>
-  <si>
-    <t>&lt;br /&gt;
-Ventilator settings are (delivered VT of 460 ml):
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| PC-CMV | NA     | 20          | NA           | NA  | 0.5    | 10       | 5            | 0.40 |</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario1-InsultsApplied.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario1-InitialHemeostasis.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario1-InsultsOutcome.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario2-InitialHemeostasis.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario2-InsultsApplied.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario2-InsultsOutcome.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario3-InitialHemeostasis.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario3-InsultsApplied.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario3-InsultsOutcome.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario4-InitialHemeostasis.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario4-InsultsApplied.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario4-InsultsOutcome.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario5-InitialHemeostasis.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario5-InsultsApplied.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario5-InsultsOutcome.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario6-InitialHemeostasis.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario6-InsultsOutcome.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario6-InsultsApplied.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario7-InitialHemeostasis.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario7-InsultsApplied.json"} }</t>
-  </si>
-  <si>
-    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario7-InsultsOutcome.json"} }</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A 22 year-old soldier was involved in a motor vehicle crash with rollover and ejection from the vehicle.  He suffered multiple rib fractures, a right femur fracture, multiple lacerations and pulmonary contusion.  He underwent internal fixation of the femur fracture, received 4 units of whole blood, had a chest tube placed for a small hemothorax and returned from the operating room on mechanical ventilation. The patient is sedated and is not currently triggering the ventilator.  Intraoperatively 3 L of crystalloids were administered. The patient is 6'2'' tall, weighs 200 lbs and has no known comorbidities or allergies.  Chest radiograph demonstrates bi-basilar early consolidation, presence of the chest tube and pulmonary contusion. </t>
-  </si>
-  <si>
-    <t>A 62 year-old contractor developed pneumonia while working on a water purification system. He has 90- pack year history of cigarette smoking (2 packs per day x 45 years), has type II diabetes and primary hypertension managed with oral medications. He uses a rescue inhaler (albuterol) and is on a maintenance inhaled corticosteroid. His pre-deployment FEV-1 is 43% of predicted. The patient is 5'9'' tall, weighs 210 lbs and has no known allergies. Chest radiograph demonstrates left-lower lobe consolidation, haziness in the right lower lobe, flattened diaphragms and hyperinflation in the upper lung fields. Heart rate is normal sinus rhythm and occasional PVC's. Patient is sedated and not triggering ventilator.</t>
-  </si>
-  <si>
-    <t>A 25 year-old active duty Marine was involved in a training accident where a Humvee was wrecked. She has a mild traumatic brain injury, flail chest and pulmonary contusions. The patient is 5'7'' tall, weighs 170 lbs and has no known allergies. She is sedated and not triggering the ventilator.</t>
-  </si>
-  <si>
-    <t>A 25 year-old soldier was injured following an IED detonation while dismounted. He suffered a traumatic amputation of the right lower extremity below the knee, multiple puncture wounds from fragments in the left lower extremity and lost consciousness at the scene. A tourniquet was applied and the hemorrhage mitigated.  Both eardrums were ruptured and his GCS was 12.  He underwent a massive transfusion, received 10 units of whole blood, crystalloid infusions and platelets. In the operating room primary control of hemorrhage was achieved and the lower extremity amputation addressed using standard techniques. The patient arrived from the operating room on mechanical ventilation. He was sedated and is not currently triggering the ventilator. The patient is 5'9'' tall, weighs 170 lbs and has no known comorbidities or allergies.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A 28 year old sailor suffered a crush injury during the transfer of supplies from a fork lift.  She suffered an open book pelvic fracture, ruptured bladder and splenic laceration.  She required a massive transfusion and intraoperative open reduction and internal fixation of the pelvic fracture.  The spleen was removed and the bladder repaired.  Blood loss was estimated at 2.5 L. The sailor is 5'5'' and weighs 138 lbs.  </t>
-  </si>
-  <si>
-    <t>A 23 year old soldier suffered developed shortness of breath, substernal chest pain and a productive cough following burn pit exposure. He was started on broad spectrum antibiotics and steroids for a suspected respiratory tract infection.  Initial chest x-ray demonstrated some minor hilar infiltrates. On day 5 of his antibiotic course he developed worsening dyspnea, was febrile to 39.5 degC, a breathing frequency of 32 bpm and his SpO2 was 91%. He was placed on high flow nasal cannula at 50% and 40 L/min.  After 12 hours he was intubated.  The soldier is 6'3'' and weighs 215 lbs.  Suctioning reveals thick, tenacious, brownish-yellow secretions.  Therapeutic bronchoscopy is performed and 15-20 ml secretions removed and sent for culture and sensitivity. Initial gram stain suggests acinetobacter baumanni. Antibiotics are changed to a carbapenem. He is scheduled for CCATT to definitive care in the morning.</t>
-  </si>
-  <si>
-    <t>A 54-year-old, Black contractor was injured in a motor vehicle accident sustaining multiple rib fractures and pulmonary contusion. He lost consciousness at the scene, sustained a complex jaw fracture, near transection of the tongue with significant blood loss and noted to have blood in the trachea at intubation.  His initial chest x-ray demonstrated right middle lobe consolidation and some evidence of hyperinflation.  The patient has a smoking history of 2 packs per day for 35 years and has primary hypertension managed with drug therapy.   He is 5'8'' and weighs 235 lbs.  Suctioning reveals a moderate amount of old blood. Gram stain of secretions shows no bacteria. He is scheduled for CCATT to definitive care that night.</t>
   </si>
 </sst>
 </file>
@@ -1268,9 +1311,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1279,6 +1319,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1728,16 +1771,16 @@
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -1768,11 +1811,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -1830,7 +1873,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -1850,13 +1893,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1868,13 +1911,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9" t="s">
         <v>22</v>
@@ -1884,15 +1927,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -1900,13 +1943,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9" t="s">
         <v>24</v>
@@ -1916,13 +1959,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
     </row>
@@ -1930,15 +1973,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="21"/>
+      <c r="B15" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20"/>
       <c r="G15" s="9" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -1946,13 +1989,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="B16" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
     </row>
@@ -1987,10 +2030,10 @@
         <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>31</v>
@@ -1999,10 +2042,10 @@
         <v>567</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -2011,7 +2054,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>42</v>
@@ -2023,10 +2066,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -2035,7 +2078,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>42</v>
@@ -2047,10 +2090,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -2059,7 +2102,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>41</v>
@@ -2071,10 +2114,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -2083,7 +2126,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -2095,10 +2138,10 @@
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -2107,7 +2150,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
@@ -2119,10 +2162,10 @@
         <v>0.2</v>
       </c>
       <c r="F23" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -2137,16 +2180,16 @@
         <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -2154,13 +2197,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -2172,13 +2215,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>190</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -2186,15 +2229,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="H27" s="9"/>
     </row>
@@ -2202,15 +2245,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -2218,13 +2261,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="B29" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
@@ -2232,13 +2275,13 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
+      <c r="B30" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
     </row>
@@ -2273,10 +2316,10 @@
         <v>40</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>31</v>
@@ -2285,10 +2328,10 @@
         <v>567</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -2297,7 +2340,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>42</v>
@@ -2309,10 +2352,10 @@
         <v>12</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -2321,7 +2364,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>42</v>
@@ -2333,10 +2376,10 @@
         <v>12</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -2345,7 +2388,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>41</v>
@@ -2357,10 +2400,10 @@
         <v>35</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -2369,7 +2412,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>30</v>
@@ -2381,10 +2424,10 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -2393,7 +2436,7 @@
         <v>29</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>30</v>
@@ -2405,10 +2448,10 @@
         <v>0.3</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -2423,16 +2466,16 @@
         <v>35</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -2440,13 +2483,13 @@
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
       <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
@@ -2458,13 +2501,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>191</v>
-      </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
+      <c r="B40" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
@@ -2472,15 +2515,15 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="21"/>
+      <c r="B41" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="20"/>
       <c r="G41" s="9" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -2488,13 +2531,13 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
+      <c r="B42" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
       <c r="G42" s="9"/>
       <c r="H42" s="10"/>
     </row>
@@ -2529,10 +2572,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>31</v>
@@ -2541,10 +2584,10 @@
         <v>490</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -2565,10 +2608,10 @@
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H45" s="10"/>
     </row>
@@ -2577,22 +2620,22 @@
         <v>29</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E46" s="2">
         <v>2</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H46" s="10"/>
     </row>
@@ -2600,13 +2643,13 @@
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
       <c r="G47" s="1" t="s">
         <v>6</v>
       </c>
@@ -2618,15 +2661,15 @@
       <c r="A48" s="8">
         <v>4</v>
       </c>
-      <c r="B48" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="21"/>
+      <c r="B48" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="20"/>
       <c r="G48" s="9" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="H48" s="10"/>
     </row>
@@ -2634,13 +2677,13 @@
       <c r="A49" s="8">
         <v>4</v>
       </c>
-      <c r="B49" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
+      <c r="B49" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
       <c r="G49" s="9"/>
       <c r="H49" s="10"/>
     </row>
@@ -2675,10 +2718,10 @@
         <v>40</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>31</v>
@@ -2687,10 +2730,10 @@
         <v>490</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H51" s="10"/>
     </row>
@@ -2699,7 +2742,7 @@
         <v>29</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>41</v>
@@ -2711,10 +2754,10 @@
         <v>3</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H52" s="10"/>
     </row>
@@ -2729,16 +2772,16 @@
         <v>35</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E53" s="2">
         <v>3</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H53" s="10"/>
     </row>
@@ -2759,10 +2802,10 @@
         <v>3</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H54" s="10"/>
     </row>
@@ -2783,10 +2826,10 @@
         <v>3</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H55" s="10"/>
     </row>
@@ -2795,7 +2838,7 @@
         <v>29</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>30</v>
@@ -2807,33 +2850,15 @@
         <v>3</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H56" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="B13:F13"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B49:F49"/>
@@ -2850,6 +2875,24 @@
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B29:F29"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -2905,10 +2948,10 @@
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -2937,11 +2980,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -3005,7 +3048,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -3025,13 +3068,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3043,13 +3086,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>22</v>
@@ -3059,15 +3102,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -3075,13 +3118,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10"/>
     </row>
@@ -3089,13 +3132,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -3103,15 +3146,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="B15" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
       <c r="G15" s="9" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -3119,13 +3162,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="B16" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
@@ -3160,10 +3203,10 @@
         <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>31</v>
@@ -3172,10 +3215,10 @@
         <v>600</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -3184,7 +3227,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>42</v>
@@ -3196,10 +3239,10 @@
         <v>24</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -3208,7 +3251,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>42</v>
@@ -3220,10 +3263,10 @@
         <v>36</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -3232,7 +3275,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>41</v>
@@ -3244,10 +3287,10 @@
         <v>68</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -3256,7 +3299,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -3268,10 +3311,10 @@
         <v>0.49</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -3280,7 +3323,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
@@ -3292,10 +3335,10 @@
         <v>0.19</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -3303,13 +3346,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -3321,13 +3364,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="B25" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -3335,15 +3378,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="H26" s="9"/>
     </row>
@@ -3365,13 +3408,13 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
@@ -3379,13 +3422,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="B29" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="9"/>
       <c r="H29" s="10"/>
     </row>
@@ -3420,10 +3463,10 @@
         <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>31</v>
@@ -3432,10 +3475,10 @@
         <v>600</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -3444,7 +3487,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>42</v>
@@ -3456,10 +3499,10 @@
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -3468,7 +3511,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>42</v>
@@ -3480,10 +3523,10 @@
         <v>1</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -3504,10 +3547,10 @@
         <v>1</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -3528,10 +3571,10 @@
         <v>1</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -3539,13 +3582,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+      <c r="C36" s="21"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="21"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -3557,13 +3600,13 @@
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
+      <c r="B37" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
       <c r="G37" s="9"/>
       <c r="H37" s="9"/>
     </row>
@@ -3574,12 +3617,12 @@
       <c r="B38" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="21"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="20"/>
       <c r="G38" s="9" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -3587,13 +3630,13 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
+      <c r="B39" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
       <c r="G39" s="9"/>
       <c r="H39" s="10"/>
     </row>
@@ -3628,10 +3671,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>31</v>
@@ -3640,10 +3683,10 @@
         <v>600</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -3652,7 +3695,7 @@
         <v>29</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>42</v>
@@ -3664,10 +3707,10 @@
         <v>2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H42" s="10"/>
     </row>
@@ -3676,7 +3719,7 @@
         <v>29</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>42</v>
@@ -3688,10 +3731,10 @@
         <v>2</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H43" s="10"/>
     </row>
@@ -3712,10 +3755,10 @@
         <v>2</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -3736,15 +3779,35 @@
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H45" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B38:F38"/>
@@ -3756,26 +3819,6 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3829,10 +3872,10 @@
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -3859,11 +3902,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -3927,7 +3970,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -3947,13 +3990,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3968,10 +4011,10 @@
       <c r="B11" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-      <c r="F11" s="21"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="20"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>22</v>
@@ -3981,15 +4024,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>148</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -3997,13 +4040,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10" t="s">
         <v>24</v>
@@ -4013,13 +4056,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -4027,15 +4070,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
+      <c r="B15" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
       <c r="G15" s="9" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -4043,13 +4086,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="B16" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
@@ -4084,10 +4127,10 @@
         <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>31</v>
@@ -4096,10 +4139,10 @@
         <v>420</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -4108,7 +4151,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>42</v>
@@ -4120,10 +4163,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -4132,7 +4175,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>42</v>
@@ -4144,10 +4187,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -4156,7 +4199,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>41</v>
@@ -4168,10 +4211,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -4180,7 +4223,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -4192,10 +4235,10 @@
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -4204,7 +4247,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
@@ -4216,10 +4259,10 @@
         <v>0.2</v>
       </c>
       <c r="F23" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -4234,16 +4277,16 @@
         <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -4251,13 +4294,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -5285,13 +5328,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -5299,15 +5342,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
+      <c r="B27" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="14"/>
@@ -6331,15 +6374,15 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="14"/>
@@ -7363,13 +7406,13 @@
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>196</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="B29" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="9"/>
       <c r="H29" s="9"/>
     </row>
@@ -7377,13 +7420,13 @@
       <c r="A30" s="8">
         <v>2</v>
       </c>
-      <c r="B30" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
+      <c r="B30" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
       <c r="H30" s="10"/>
       <c r="I30" s="14"/>
       <c r="J30" s="14"/>
@@ -9449,10 +9492,10 @@
         <v>40</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>31</v>
@@ -9461,10 +9504,10 @@
         <v>420</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -9473,7 +9516,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>42</v>
@@ -9485,10 +9528,10 @@
         <v>12</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -9497,7 +9540,7 @@
         <v>29</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>42</v>
@@ -9509,10 +9552,10 @@
         <v>12</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -9521,7 +9564,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>41</v>
@@ -9533,10 +9576,10 @@
         <v>33</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -9545,7 +9588,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>30</v>
@@ -9557,10 +9600,10 @@
         <v>0.65</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -9569,7 +9612,7 @@
         <v>29</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>30</v>
@@ -9581,10 +9624,10 @@
         <v>0.4</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -9599,16 +9642,16 @@
         <v>35</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="E38" s="2">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -9616,13 +9659,13 @@
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21"/>
       <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
@@ -10650,13 +10693,13 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
+      <c r="B40" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
       <c r="G40" s="9"/>
       <c r="H40" s="9"/>
     </row>
@@ -10664,15 +10707,15 @@
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
+      <c r="B41" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
       <c r="G41" s="9" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="H41" s="10"/>
       <c r="I41" s="14"/>
@@ -11696,13 +11739,13 @@
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
+      <c r="B42" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
       <c r="G42" s="9"/>
       <c r="H42" s="10"/>
       <c r="I42" s="14"/>
@@ -13769,10 +13812,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>31</v>
@@ -13781,10 +13824,10 @@
         <v>340</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -13805,15 +13848,34 @@
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H45" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B41:F41"/>
@@ -13826,25 +13888,6 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -13898,10 +13941,10 @@
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -13928,11 +13971,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -13996,7 +14039,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -14016,13 +14059,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -14034,31 +14077,31 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="127.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>79</v>
+        <v>211</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -14066,13 +14109,13 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
       <c r="G13" s="9"/>
       <c r="H13" s="10" t="s">
         <v>24</v>
@@ -14082,13 +14125,13 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9"/>
       <c r="H14" s="10"/>
     </row>
@@ -14096,15 +14139,15 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="21"/>
+      <c r="B15" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="20"/>
       <c r="G15" s="9" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -14112,13 +14155,13 @@
       <c r="A16" s="8">
         <v>1</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
+      <c r="B16" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
       <c r="G16" s="9"/>
       <c r="H16" s="10"/>
     </row>
@@ -14153,10 +14196,10 @@
         <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>31</v>
@@ -14165,10 +14208,10 @@
         <v>500</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -14177,7 +14220,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>42</v>
@@ -14189,10 +14232,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -14201,7 +14244,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>42</v>
@@ -14213,10 +14256,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -14225,7 +14268,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>41</v>
@@ -14237,10 +14280,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -14249,7 +14292,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -14261,10 +14304,10 @@
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -14273,7 +14316,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
@@ -14285,10 +14328,10 @@
         <v>0.2</v>
       </c>
       <c r="F23" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -14303,16 +14346,16 @@
         <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -14320,13 +14363,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -14338,13 +14381,13 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9"/>
       <c r="H26" s="9"/>
     </row>
@@ -14352,15 +14395,15 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="B27" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -14368,29 +14411,29 @@
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9"/>
       <c r="H28" s="9"/>
     </row>
-    <row r="29" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="188.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>2</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="B29" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="9" t="s">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="H29" s="10"/>
     </row>
@@ -14425,10 +14468,10 @@
         <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>31</v>
@@ -14437,10 +14480,10 @@
         <v>500</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -14449,7 +14492,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>41</v>
@@ -14464,7 +14507,7 @@
         <v>32</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -14488,7 +14531,7 @@
         <v>32</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -14512,7 +14555,7 @@
         <v>32</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -14533,10 +14576,10 @@
         <v>1</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -14560,7 +14603,7 @@
         <v>32</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -14584,7 +14627,7 @@
         <v>32</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -14592,13 +14635,13 @@
       <c r="A38" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="21"/>
       <c r="G38" s="1" t="s">
         <v>6</v>
       </c>
@@ -14610,13 +14653,13 @@
       <c r="A39" s="8">
         <v>3</v>
       </c>
-      <c r="B39" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
+      <c r="B39" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
       <c r="G39" s="9"/>
       <c r="H39" s="9"/>
     </row>
@@ -14624,45 +14667,47 @@
       <c r="A40" s="8">
         <v>3</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
       <c r="G40" s="9" t="s">
-        <v>81</v>
+        <v>191</v>
       </c>
       <c r="H40" s="10"/>
     </row>
-    <row r="41" spans="1:8" ht="139.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" ht="171.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="8">
         <v>3</v>
       </c>
-      <c r="B41" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="9"/>
+      <c r="B41" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="9" t="s">
+        <v>192</v>
+      </c>
       <c r="H41" s="10" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>3</v>
       </c>
-      <c r="B42" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
+      <c r="B42" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
       <c r="G42" s="9"/>
       <c r="H42" s="10"/>
     </row>
@@ -14697,10 +14742,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>31</v>
@@ -14709,10 +14754,10 @@
         <v>500</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -14721,7 +14766,7 @@
         <v>29</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>41</v>
@@ -14736,7 +14781,7 @@
         <v>32</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H45" s="10"/>
     </row>
@@ -14760,7 +14805,7 @@
         <v>32</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H46" s="10"/>
     </row>
@@ -14784,7 +14829,7 @@
         <v>32</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H47" s="10"/>
     </row>
@@ -14805,10 +14850,10 @@
         <v>2</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H48" s="10"/>
     </row>
@@ -14832,7 +14877,7 @@
         <v>32</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H49" s="10"/>
     </row>
@@ -14856,12 +14901,31 @@
         <v>32</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="H50" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B42:F42"/>
@@ -14874,25 +14938,6 @@
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -14905,7 +14950,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AMJ45"/>
+  <dimension ref="A1:AMJ44"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="12" customWidth="1"/>
@@ -14946,10 +14991,10 @@
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -14976,11 +15021,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -15044,7 +15089,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -15064,13 +15109,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -15082,145 +15127,149 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="126.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>88</v>
+        <v>188</v>
       </c>
       <c r="H12" s="10"/>
     </row>
-    <row r="13" spans="1:8" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="H13" s="10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B13" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:8" ht="215.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>25</v>
+      <c r="B14" s="18" t="s">
+        <v>147</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
       <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="9"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="9" t="s">
+        <v>142</v>
+      </c>
       <c r="H14" s="10"/>
     </row>
-    <row r="15" spans="1:8" ht="215.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="9" t="s">
-        <v>162</v>
-      </c>
+      <c r="B15" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="9"/>
       <c r="H15" s="10"/>
     </row>
-    <row r="16" spans="1:8" ht="95.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="8">
-        <v>1</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="H16" s="10"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H16" s="15" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="17" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="2">
+        <v>376</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H17" s="10"/>
     </row>
     <row r="18" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E18" s="2">
-        <v>376</v>
+        <v>12</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>128</v>
+        <v>88</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>104</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -15241,10 +15290,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -15253,22 +15302,22 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E20" s="2">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -15277,22 +15326,22 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E21" s="2">
-        <v>35</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -15301,7 +15350,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -15310,13 +15359,13 @@
         <v>31</v>
       </c>
       <c r="E22" s="2">
-        <v>0.56999999999999995</v>
+        <v>0.3</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>119</v>
+        <v>89</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -15325,186 +15374,186 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0.3</v>
-      </c>
       <c r="F23" s="11" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="H23" s="10"/>
     </row>
-    <row r="24" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H24" s="10"/>
-    </row>
-    <row r="25" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
+    <row r="24" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B24" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
+      <c r="G24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="8">
+        <v>2</v>
+      </c>
       <c r="B25" s="18" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
-      <c r="G25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+    </row>
+    <row r="26" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>201</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-    </row>
-    <row r="27" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="H26" s="10"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H27" s="10"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="B27" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+    </row>
+    <row r="28" spans="1:8" ht="144.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>202</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="8">
-        <v>2</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="H29" s="10"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
+      <c r="B28" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
+      <c r="G28" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="H28" s="10"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B29" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F29" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H30" s="15" t="s">
+      <c r="H29" s="15" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="30" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="2">
+        <v>376</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30" s="10"/>
     </row>
     <row r="31" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E31" s="2">
-        <v>376</v>
+        <v>1</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>128</v>
+        <v>32</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="H31" s="10"/>
     </row>
     <row r="32" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>48</v>
@@ -15513,34 +15562,34 @@
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G32" s="13" t="s">
-        <v>65</v>
+        <v>109</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="H32" s="10"/>
     </row>
-    <row r="33" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E33" s="2">
         <v>1</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>69</v>
+        <v>32</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -15549,7 +15598,7 @@
         <v>40</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>45</v>
@@ -15564,155 +15613,155 @@
         <v>32</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H34" s="10"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E35" s="2">
-        <v>1</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G35" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H35" s="10"/>
-    </row>
-    <row r="36" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
+    <row r="35" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="B35" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H35" s="15" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="8">
+        <v>3</v>
+      </c>
       <c r="B36" s="18" t="s">
-        <v>20</v>
+        <v>180</v>
       </c>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
-      <c r="G36" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+    </row>
+    <row r="37" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>3</v>
       </c>
-      <c r="B37" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="9"/>
+      <c r="B37" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H37" s="10"/>
     </row>
     <row r="38" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="9" t="s">
-        <v>84</v>
-      </c>
+      <c r="B38" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="9"/>
       <c r="H38" s="10"/>
     </row>
-    <row r="39" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="8">
-        <v>3</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="10"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B39" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C39" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F39" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H40" s="15" t="s">
+      <c r="H39" s="15" t="s">
         <v>7</v>
       </c>
+    </row>
+    <row r="40" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" s="2">
+        <v>376</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H40" s="10"/>
     </row>
     <row r="41" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E41" s="2">
-        <v>376</v>
+        <v>2</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>128</v>
+        <v>32</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>46</v>
@@ -15721,34 +15770,34 @@
         <v>2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G42" s="13" t="s">
-        <v>65</v>
+        <v>109</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="H42" s="10"/>
     </row>
-    <row r="43" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E43" s="2">
         <v>2</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>69</v>
+        <v>32</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="H43" s="10"/>
     </row>
@@ -15757,7 +15806,7 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>45</v>
@@ -15772,52 +15821,18 @@
         <v>32</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="H44" s="10"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A45" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E45" s="2">
-        <v>2</v>
-      </c>
-      <c r="F45" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H45" s="10"/>
-    </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
+  <mergeCells count="29">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="E5:F9"/>
@@ -15826,12 +15841,21 @@
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -15885,10 +15909,10 @@
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -15915,11 +15939,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -15983,7 +16007,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -16003,13 +16027,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -16021,80 +16045,76 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="147" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="H12" s="10"/>
     </row>
-    <row r="13" spans="1:8" ht="41.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="H13" s="10"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
     </row>
     <row r="14" spans="1:8" ht="205.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>1</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>185</v>
-      </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="21"/>
+        <v>212</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="20"/>
       <c r="G14" s="9" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="H14" s="10"/>
     </row>
-    <row r="15" spans="1:8" ht="108.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="9" t="s">
-        <v>154</v>
-      </c>
+      <c r="B15" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="9"/>
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -16128,22 +16148,22 @@
         <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E17" s="2">
-        <v>520</v>
+        <v>583</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H17" s="10"/>
     </row>
@@ -16152,7 +16172,7 @@
         <v>29</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>42</v>
@@ -16164,10 +16184,10 @@
         <v>12</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -16176,7 +16196,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>42</v>
@@ -16188,10 +16208,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -16200,7 +16220,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>41</v>
@@ -16212,10 +16232,10 @@
         <v>35</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -16224,7 +16244,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>30</v>
@@ -16236,10 +16256,10 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -16248,7 +16268,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -16260,10 +16280,10 @@
         <v>0.3</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -16278,16 +16298,16 @@
         <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -16295,13 +16315,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -16313,13 +16333,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>204</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="B25" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -16327,15 +16347,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
-        <v>89</v>
+        <v>196</v>
       </c>
       <c r="H26" s="10"/>
     </row>
@@ -16343,29 +16363,29 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="B27" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="152.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>182</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -16400,10 +16420,10 @@
         <v>40</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>48</v>
@@ -16412,10 +16432,10 @@
         <v>1</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -16424,7 +16444,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>42</v>
@@ -16436,10 +16456,10 @@
         <v>1</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -16448,7 +16468,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>42</v>
@@ -16460,10 +16480,10 @@
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -16471,13 +16491,13 @@
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
       <c r="G33" s="1" t="s">
         <v>6</v>
       </c>
@@ -16489,13 +16509,13 @@
       <c r="A34" s="8">
         <v>3</v>
       </c>
-      <c r="B34" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
+      <c r="B34" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
     </row>
@@ -16503,30 +16523,32 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
+      <c r="B35" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
       <c r="G35" s="9" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" ht="120" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="9"/>
+      <c r="B36" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="9" t="s">
+        <v>199</v>
+      </c>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -16560,10 +16582,10 @@
         <v>40</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>31</v>
@@ -16572,10 +16594,10 @@
         <v>520</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -16584,7 +16606,7 @@
         <v>29</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>42</v>
@@ -16596,10 +16618,10 @@
         <v>2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H39" s="10"/>
     </row>
@@ -16608,7 +16630,7 @@
         <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>42</v>
@@ -16620,15 +16642,34 @@
         <v>2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H40" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B15:F15"/>
@@ -16639,25 +16680,6 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -16705,16 +16727,16 @@
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
       <c r="E2" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F2" s="25" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
@@ -16741,11 +16763,11 @@
       <c r="A4" s="7">
         <v>0</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
       <c r="G4" s="3"/>
       <c r="H4" s="16" t="s">
         <v>8</v>
@@ -16809,7 +16831,7 @@
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
       <c r="G8" s="26" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H8" s="26"/>
     </row>
@@ -16829,13 +16851,13 @@
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -16847,13 +16869,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>22</v>
@@ -16863,15 +16885,15 @@
       <c r="A12" s="8">
         <v>1</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="B12" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -16879,31 +16901,29 @@
       <c r="A13" s="8">
         <v>1</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="9" t="s">
-        <v>57</v>
-      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="9"/>
       <c r="H13" s="10"/>
     </row>
     <row r="14" spans="1:8" ht="189" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="B14" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
       <c r="G14" s="9" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -16911,16 +16931,14 @@
       <c r="A15" s="8">
         <v>1</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="9" t="s">
-        <v>156</v>
-      </c>
+      <c r="B15" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="9"/>
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -16954,10 +16972,10 @@
         <v>40</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>31</v>
@@ -16966,10 +16984,10 @@
         <v>460</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H17" s="10"/>
     </row>
@@ -16978,7 +16996,7 @@
         <v>29</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>42</v>
@@ -16990,10 +17008,10 @@
         <v>12</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -17002,7 +17020,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>42</v>
@@ -17014,10 +17032,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -17026,7 +17044,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>41</v>
@@ -17038,10 +17056,10 @@
         <v>40</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -17050,7 +17068,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>30</v>
@@ -17062,10 +17080,10 @@
         <v>0.54</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -17074,7 +17092,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -17086,10 +17104,10 @@
         <v>0.2</v>
       </c>
       <c r="F22" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -17104,16 +17122,16 @@
         <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -17121,13 +17139,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="21"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -17139,13 +17157,13 @@
       <c r="A25" s="8">
         <v>2</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="B25" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
       <c r="G25" s="9"/>
       <c r="H25" s="9"/>
     </row>
@@ -17153,15 +17171,15 @@
       <c r="A26" s="8">
         <v>2</v>
       </c>
-      <c r="B26" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
-        <v>90</v>
+        <v>202</v>
       </c>
       <c r="H26" s="10"/>
     </row>
@@ -17169,29 +17187,29 @@
       <c r="A27" s="8">
         <v>2</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="B27" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="18"/>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
       <c r="G27" s="9"/>
       <c r="H27" s="9"/>
     </row>
-    <row r="28" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="105" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>2</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="B28" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>157</v>
+        <v>203</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -17226,10 +17244,10 @@
         <v>40</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>48</v>
@@ -17238,10 +17256,10 @@
         <v>1</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -17250,7 +17268,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>42</v>
@@ -17262,10 +17280,10 @@
         <v>1</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -17274,7 +17292,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>42</v>
@@ -17286,10 +17304,10 @@
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -17297,13 +17315,13 @@
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
       <c r="G33" s="1" t="s">
         <v>6</v>
       </c>
@@ -17315,13 +17333,13 @@
       <c r="A34" s="8">
         <v>3</v>
       </c>
-      <c r="B34" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
+      <c r="B34" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
       <c r="G34" s="9"/>
       <c r="H34" s="9"/>
     </row>
@@ -17329,30 +17347,32 @@
       <c r="A35" s="8">
         <v>3</v>
       </c>
-      <c r="B35" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
+      <c r="B35" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
       <c r="G35" s="9" t="s">
-        <v>86</v>
+        <v>204</v>
       </c>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" ht="105" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="9"/>
+      <c r="B36" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="9" t="s">
+        <v>205</v>
+      </c>
       <c r="H36" s="10"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -17386,10 +17406,10 @@
         <v>40</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>31</v>
@@ -17398,10 +17418,10 @@
         <v>460</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -17410,7 +17430,7 @@
         <v>29</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>42</v>
@@ -17422,10 +17442,10 @@
         <v>2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H39" s="10"/>
     </row>
@@ -17434,7 +17454,7 @@
         <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>42</v>
@@ -17446,15 +17466,34 @@
         <v>2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H40" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="E5:F9"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B36:F36"/>
@@ -17465,25 +17504,6 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="E5:F9"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="F2:H2"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BEC1198-A848-4AC9-A553-FBC82454F1D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76CE13C2-12DA-40E7-9F92-C2E4D0FF7D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26280" yWindow="3165" windowWidth="31200" windowHeight="28275" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="450" yWindow="3330" windowWidth="29880" windowHeight="26985" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="228">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -325,24 +325,6 @@
     <t>BransonSME, ChatburnSME</t>
   </si>
   <si>
-    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
-  {
-    "Severity": [ 
-      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.3 }}},
-      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.3 }}}]
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
-  {
-    "Severity": [ 
-      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}},
-      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}}]
-  }}
-}</t>
-  </si>
-  <si>
     <t>The patient is loaded in the aircraft for transport to level III care. Twenty minutes into the transport, SpO2 falls and both PIP and Pplat are increased. The patient is triggering the ventilator.
 &lt;br /&gt;</t>
   </si>
@@ -440,16 +422,6 @@
     <t>VT (measured)</t>
   </si>
   <si>
-    <t xml:space="preserve">    { "PatientAction": { "ChronicObstructivePulmonaryDiseaseExacerbation":
-      {
-        "BronchitisSeverity": { "Scalar0To1": { "Value": 0.6 }},
-        "EmphysemaSeverity": [ 
-          { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}},
-          { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}}]
-      }}
-    }</t>
-  </si>
-  <si>
     <t>Rinsp for moderate COPD</t>
   </si>
   <si>
@@ -484,23 +456,6 @@
   </si>
   <si>
     <t>lessThanValue</t>
-  </si>
-  <si>
-    <t>Ventilator settings are (VT Target = 6.9 mL/kg (ideal)):
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.567    | NA          | 59          | NA  | 0.6    | 20      | 5            | 0.4 |</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    { "PatientAction": { "ChronicObstructivePulmonaryDiseaseExacerbation":
-      {
-        "BronchitisSeverity": { "Scalar0To1": { "Value": 0.9 }},
-        "EmphysemaSeverity": [ 
-          { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}},
-          { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}}]
-      }}
-    }</t>
   </si>
   <si>
     <t>Patient suctioned and albuterol administered.
@@ -525,147 +480,11 @@
  - Increase PEEP</t>
   </si>
   <si>
-    <t>Learning Objectives:
- - Evaluate ventilatory status
-Recommended Actions:
- - Increase RR to 27 to get acceptable pH
-&lt;br /&gt;</t>
-  </si>
-  <si>
     <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
   {
     "Severity": [ 
       { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.27}}},
       { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.27 }}}]
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
-  {
-    "Severity": [ 
-      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.25 }}},
-      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.25 }}}]
-  }}
-}</t>
-  </si>
-  <si>
-    <t>Ventilator settings are:
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.42  | NA          | 51           | NA  | 0.51  | 20       | 8            | 0.50 |</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 51, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.51, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 420, "Unit": "mL" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>Ventialtor settings are changed. PEEP and FiO2 increased, tidal volume decreased.
-Learning Objectives:
- - Evaluate effects of changes
-Recommended Actions:
- - Increase tidal volume to previous setting
- - Patient unable to trigger fast enough to improve pH
-Ventilator settings are updated to:
- - FIO2 = 0.50-1.00
- - PEEP = 8-12 cmH2O
- - VT = 0.42-0.34 L
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.34   | NA          | 51           | NA  | 0.41  | 20       | 12            | 1.00 |</t>
-  </si>
-  <si>
-    <t>Ventilator settings are (VT Target = 6.9 mL/kg (ideal)):
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.488    | NA          | 52          | NA  | 0.6    | 20      | 5            | 0.4 |</t>
-  </si>
-  <si>
-    <t>Ventilator settings are (VT Target = 6.6 mL/kg (ideal)):
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.376    | NA          | 42          | NA  | 0.6    | 20      | 5            | 0.4 |</t>
-  </si>
-  <si>
-    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
-  {
-    "Severity": [ 
-      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.91 }}},
-      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.91 }}}]
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 59, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 51, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 1.0 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.41, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 12, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 340, "Unit": "mL" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 52, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 488, "Unit": "mL" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 42, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 20, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 376, "Unit": "mL" } },
-  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
   </si>
@@ -753,28 +572,6 @@
 | VC-CMV | 0.490    | NA          | 50          | NA  | 0.6    | 20      | 5            | 0.5 |</t>
   </si>
   <si>
-    <t>Ventilator settings are:
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.600    | NA          | 64          | NA  | 0.6    | 18       | 5            | 0.4 |</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 64, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 18, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 600, "Unit": "mL" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
     <t>Twenty minutes into the transport the patient is slightly agitated and is making inspiratory efforts that are not in sync with the ventilator.
 Learning Objectives:
  - Recognize increased airway resistance (PIP much higher than Pplat)
@@ -801,15 +598,6 @@
     <t>Leak improves.</t>
   </si>
   <si>
-    <t>{ "PatientAction": { "PneumoniaExacerbation":
-  {
-    "Severity": [ 
-      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.3 }}},
-      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.3 }}}]
-  }}
-}</t>
-  </si>
-  <si>
     <t>{ "PatientAction": {
       "AirwayObstruction": {
         "Severity": {
@@ -836,14 +624,6 @@
     <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 3, "Unit": "min" }}}}</t>
   </si>
   <si>
-    <t>&lt;br /&gt;
-Ventilator settings are (delivered VT of 460 ml):
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| PC-CMV | NA     | 20          | NA           | NA  | 0.5    | 10       | 5            | 0.40 |</t>
-  </si>
-  <si>
     <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario1-InsultsApplied.json"} }</t>
   </si>
   <si>
@@ -908,14 +688,6 @@
   </si>
   <si>
     <t xml:space="preserve">A 22 year-old soldier was involved in a motor vehicle crash with rollover and ejection from the vehicle.  He suffered multiple rib fractures, a right femur fracture, multiple lacerations and pulmonary contusion.  He underwent internal fixation of the femur fracture, received 4 units of whole blood, had a chest tube placed for a small hemothorax and returned from the operating room on mechanical ventilation. The patient is sedated and is not currently triggering the ventilator.  Intraoperatively 3 L of crystalloids were administered. The patient is 6'2'' tall, weighs 200 lbs and has no known comorbidities or allergies.  Chest radiograph demonstrates bi-basilar early consolidation, presence of the chest tube and pulmonary contusion. </t>
-  </si>
-  <si>
-    <t>Learning Objectives:
- - Assess baseline status
- - Recognize moderate ARDS
-Recommended Actions:
- - Increase RR to 24/min to increase pH above 7.25
-&lt;br /&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">The patient is loaded in the aircraft for transport to level III care.  Twenty minutes into the transport SpO2 falls and PIP and Pplat are increased (decreased compliance).  The patient remains sedated and is not triggering the ventilator.  </t>
@@ -933,14 +705,6 @@
     <t>Needle decompression procedure performed.</t>
   </si>
   <si>
-    <t>Learning Objectives:
- - Recognize resolution of pneumothorax.
-Recommended Actions:
- - SpO2, breath sounds, plateau pressure indicate pneumothorax resolved
- - But pH low and DP high so decrease VT to 400 and increase RR to 30
-&lt;br /&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">Two hours later the patient is agitated. Both PIP and Pplat have increased. The SpO2 has fallen, and etCO2 has decreased. </t>
   </si>
   <si>
@@ -949,15 +713,6 @@
 Recommended Actions:
  - Greatly increased DP, absence of breath sounds on the left side but normal sound to palpation indicate right mainstem intubation
  - Reposition endotracheal tube and re-assess 
-&lt;br /&gt;</t>
-  </si>
-  <si>
-    <t>Learning Objectives:
- - Assess baseline status
- - Recognize moderate ARDS
-Recommended Actions:
- - Increase PEEP to 10 cm H2O  
- - Consider increasing inspiratory time to eliminate early cycling
 &lt;br /&gt;</t>
   </si>
   <si>
@@ -976,14 +731,6 @@
     <t xml:space="preserve">Patient is suctioned for large volume of thick secretions. </t>
   </si>
   <si>
-    <t>Learning Objectives:
- - Recognize that suctioning decreased airway resistance and restored tidal volume)
-Recommended Actions:
- - Increase PEEP to 10 cm H2O  
- - Consider increasing inspiratory time to eliminate early cycling
-&lt;br /&gt;</t>
-  </si>
-  <si>
     <t>A 54-year-old, Black contractor was injured in a motor vehicle accident sustaining multiple rib fractures and pulmonary contusion. He lost consciousness at the scene, sustained a complex jaw fracture, near transection of the tongue with significant blood loss and noted to have blood in the trachea at intubation. After intubation he is on mechanical ventilation and remains sedated with a RASS of -2
 His initial chest x-ray demonstrated right middle lobe consolidation and some evidence of hyperinflation. The patient has a smoking history of 2 packs per day for 35 years and has primary hypertension managed with drug therapy. He is 5'8'' and weighs 235 lbs. Suctioning reveals a moderate amount of old blood. Gram stain of secretions shows no bacteria. He is scheduled for CCATT to definitive care that night.</t>
   </si>
@@ -1008,13 +755,6 @@
     <t>Patient suctioned and ET tube obstruction removed.</t>
   </si>
   <si>
-    <t>Learning Objectives:
- -  Recognize success of suctioning 
-Recommended Actions:
- - Consider increasing inspiratory time to eliminate early cycling 
-&lt;br /&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">A 23 year old soldier suffered developed shortness of breath, substernal chest pain and a productive cough following burn pit exposure. He was started on broad spectrum antibiotics and steroids for a suspected respiratory tract infection. Initial chest x-ray demonstrated some minor hilar infiltrates. On day 5 of his antibiotic course he developed worsening dyspnea, was febrile to 39.5 C, a breathing frequency of 32 bpm and his SpO2 was 91%. He was placed on high flow nasal cannula at 50% and 40 L/min. After 12 hours he was intubated.After intubation he is on mechanical ventilation and remains sedated with a RASS of -2.
 The soldier is 6'3'' and weighs 215 lbs. Suctioning reveals thick, tenacious, brownish-yellow secretions. Therapeutic bronchoscopy is performed and 15-20 mL secretions removed and sent for culture and sensitivity. Initial gram stain suggests acinetobacter baumanni. Antibiotics are changed to a carbapenem. He is scheduled for CCATT to definitive care in the morning. </t>
   </si>
@@ -1030,14 +770,331 @@
   <si>
     <t>A 62 year-old contractor developed pneumonia while working on a water purification system. He has 90- pack year history of cigarette smoking (2 packs per day x 45 years), has type II diabetes and primary hypertension managed with oral medications. He uses a rescue inhaler (albuterol) and is on a maintenance inhaled corticosteroid. His pre-deployment FEV-1 is 43% of predicted. The patient is 5'9" tall, weighs 210 lbs and has no known allergies.
 Chest radiograph demonstrates left-lower lobe consolidation, haziness in the right lower lobe, flattened diaphragms and hyperinflation in the upper lung fields. Heart rate is normal sinus rhythm and occasional PVC's. Patient is sedated and not triggering ventilator.</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario1-InterventionApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario2-InterventionApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario3-InterventionApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario4-InterventionApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario5-InterventionApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario6-InterventionApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "SerializeState": { "Mode": "Save", "Filename": "CSTARS-Scenario7-InterventionApplied.json"} }</t>
+  </si>
+  <si>
+    <t>{ "AdvanceTime": { "Time": { "ScalarTime": { "Value": 10, "Unit": "min" }}}}</t>
+  </si>
+  <si>
+    <t>Ventilator settings are:
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.600    | NA          | 64          | NA  | 0.6    | 12       | 5            | 0.4 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 64, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 12, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 600, "Unit": "mL" } },
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>Ventilator settings are (VT Target = 6.9 mL/kg (ideal)):
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.567    | NA          | 59          | NA  | 0.62    | 24      | 5            | 0.4 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 59, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.62, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 567, "Unit": "mL" } },
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>Ventilator settings are (VT Target = 6.9 mL/kg (ideal)):
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.488    | NA          | 54          | NA  | 0.6    | 24      | 5            | 0.4 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 54, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 488, "Unit": "mL" } },
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>Ventilator settings are (VT Target = 6.6 mL/kg (ideal)):
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.376    | NA          | 42          | NA  | 0.6    | 24      | 5            | 0.4 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 42, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.6, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 24, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 376, "Unit": "mL" } },
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Evaluate ventilatory status
+Recommended Actions:
+ - None
+&lt;br /&gt;</t>
   </si>
   <si>
     <t>Learning Objectives:
  - Assess baseline status
  - Recognize mild ARDS
 Recommended Actions:
- - Increase RR to 24/min to increase pH above 7.25
+ - None
 &lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Recognize resolution of pneumothorax.
+Recommended Actions:
+ - SpO2, breath sounds, plateau pressure indicate pneumothorax resolved
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Assess baseline status
+ - Recognize moderate ARDS
+Recommended Actions:
+ - None
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ -  Recognize success of suctioning 
+Recommended Actions:
+ - None
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Recognize that suctioning decreased airway resistance and restored tidal volume)
+Recommended Actions:
+ - None
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>Ventilator settings are:
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.42  | NA          | 51           | NA  | 0.52  | 27       | 8            | 0.50 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 51, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.5 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.52, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 27, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 420, "Unit": "mL" } },
+   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>Ventialtor settings are changed. PEEP and FiO2 increased.
+Learning Objectives:
+ - Evaluate effects of changes
+Recommended Actions:
+ - None
+Ventilator settings are updated to:
+ - FIO2 = 0.50-&gt;1.00
+ - PEEP = 8-&gt;12 cmH2O
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.420   | NA          | 51           | NA  | 0.52  | 20       | 12            | 1.00 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 51, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 1.0 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.52, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 12, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 27, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 420, "Unit": "mL" } },
+   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    { "PatientAction": { "ChronicObstructivePulmonaryDiseaseExacerbation":
+      {
+        "BronchitisSeverity": { "Scalar0To1": { "Value": 0.9 }},
+        "EmphysemaSeverity": [ 
+          { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.55 }}},
+          { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.55 }}}]
+      }}
+    }</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.53 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.53 }}}]
+  }}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    { "PatientAction": { "ChronicObstructivePulmonaryDiseaseExacerbation":
+      {
+        "BronchitisSeverity": { "Scalar0To1": { "Value": 0.6 }},
+        "EmphysemaSeverity": [ 
+          { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.63 }}},
+          { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.63 }}}]
+      }}
+    }</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.29 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.29 }}}]
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.8, "Unit": "s" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 15.4, "Unit": "cmH2O" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 10, "Unit": "1/min" } },
+  "InspirationPatientTriggerFlow": { "ScalarVolumePerTime": { "Value": 1.0, "Unit": "L/min"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>&lt;br /&gt;
+Ventilator settings are (delivered VT of 460 ml):
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| PC-CMV | NA     | 15.4          | NA           | NA  | 0.8    | 10       | 5            | 0.40 |</t>
+  </si>
+  <si>
+    <t>licker2021hypoxic</t>
+  </si>
+  <si>
+    <t>greaterThanValue</t>
+  </si>
+  <si>
+    <t>[0.3, 0.5]</t>
+  </si>
+  <si>
+    <t>[0.2, 0.4]</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.27 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.27 }}}]
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.28 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.28 }}}]
+  }}
+}</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.915 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.915 }}}]
+  }}
+}</t>
+  </si>
+  <si>
+    <t>PaO2/FiO2 for moderate ARDS</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": { "PneumoniaExacerbation":
+  {
+    "Severity": [ 
+      { "Compartment": "LeftLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}},
+      { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.6 }}}]
+  }}
+}</t>
+  </si>
+  <si>
+    <t>&lt;br /&gt;
+Ventilator settings are (VT delivered = 6.9 mL/kg (ideal)):
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| PC-CMV | NA     | 22.4          | NA           | NA  | 0.8    | 10       | 10            | 0.60 |</t>
   </si>
   <si>
     <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
@@ -1045,33 +1102,11 @@
   "Mode": "AssistedControl", 
   "InspirationWaveform": "Square",
   "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.6 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.5, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 26.5, "Unit": "cmH2O" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.8, "Unit": "s" } },
+  "InspiratoryPressure": { "ScalarPressure": { "Value": 22.4, "Unit": "cmH2O" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 10, "Unit": "cmH2O" } },
   "RespirationRate": { "ScalarFrequency": { "Value": 10, "Unit": "1/min" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>&lt;br /&gt;
-Ventilator settings are (VT delivered = 6.9 mL/kg (ideal)):
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| PC-CMV | NA     | 26.5          | NA           | NA  | 0.5    | 10       | 8            | 0.60 |</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorPressureControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.5, "Unit": "s" } },
-  "InspiratoryPressure": { "ScalarPressure": { "Value": 20, "Unit": "cmH2O" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 5, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 10, "Unit": "1/min" } },
-   "InspirationPatientTriggerFlow": { "ScalarVolumePerTime": { "Value": 1.0, "Unit": "L/min" } }
+  "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
   }}
 }</t>
   </si>
@@ -1314,6 +1349,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1321,10 +1359,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1337,9 +1375,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1732,7 +1767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMJ56"/>
+  <dimension ref="A1:AMJ57"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="12" customWidth="1"/>
@@ -1759,31 +1794,31 @@
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
       <c r="AMG1" s="14"/>
       <c r="AMH1" s="14"/>
       <c r="AMI1" s="14"/>
       <c r="AMJ1" s="14"/>
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="A2" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="F2" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
       <c r="AMG2" s="14"/>
       <c r="AMH2" s="14"/>
       <c r="AMI2" s="14"/>
@@ -1848,10 +1883,10 @@
       <c r="D6" s="7"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="26"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
@@ -1860,10 +1895,10 @@
       <c r="D7" s="7"/>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="26"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -1872,10 +1907,10 @@
       <c r="D8" s="7"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="26"/>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
@@ -1884,22 +1919,22 @@
       <c r="D9" s="7"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="26"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1928,14 +1963,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>137</v>
+        <v>221</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -1974,14 +2009,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="20"/>
+        <v>196</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="9" t="s">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -1990,7 +2025,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -2042,10 +2077,10 @@
         <v>567</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -2066,10 +2101,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -2090,10 +2125,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -2114,10 +2149,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -2126,7 +2161,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -2138,10 +2173,10 @@
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -2150,22 +2185,22 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0.2</v>
+        <v>91</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -2180,16 +2215,16 @@
         <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="F24" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -2197,13 +2232,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -2216,7 +2251,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
@@ -2237,7 +2272,7 @@
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H27" s="9"/>
     </row>
@@ -2246,14 +2281,14 @@
         <v>2</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -2262,7 +2297,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>166</v>
+        <v>145</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -2276,7 +2311,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>87</v>
+        <v>192</v>
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
@@ -2328,10 +2363,10 @@
         <v>567</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -2352,10 +2387,10 @@
         <v>12</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -2376,10 +2411,10 @@
         <v>12</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -2400,10 +2435,10 @@
         <v>35</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -2412,7 +2447,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>30</v>
@@ -2424,10 +2459,10 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -2436,22 +2471,22 @@
         <v>29</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E37" s="2">
-        <v>0.3</v>
+        <v>91</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>219</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -2466,16 +2501,16 @@
         <v>35</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>94</v>
+        <v>224</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -2483,13 +2518,13 @@
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
       <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
@@ -2502,7 +2537,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="C40" s="18"/>
       <c r="D40" s="18"/>
@@ -2516,14 +2551,14 @@
         <v>3</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="20"/>
+        <v>136</v>
+      </c>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="21"/>
       <c r="G41" s="9" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -2532,7 +2567,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C42" s="18"/>
       <c r="D42" s="18"/>
@@ -2584,10 +2619,10 @@
         <v>490</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -2620,13 +2655,13 @@
         <v>29</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E46" s="2">
         <v>2</v>
@@ -2635,7 +2670,7 @@
         <v>82</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H46" s="10"/>
     </row>
@@ -2643,13 +2678,13 @@
       <c r="A47" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="19"/>
       <c r="G47" s="1" t="s">
         <v>6</v>
       </c>
@@ -2662,126 +2697,116 @@
         <v>4</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>152</v>
-      </c>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="20"/>
+        <v>135</v>
+      </c>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="21"/>
       <c r="G48" s="9" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="H48" s="10"/>
     </row>
-    <row r="49" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="8">
         <v>4</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>87</v>
+        <v>185</v>
       </c>
       <c r="C49" s="18"/>
       <c r="D49" s="18"/>
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
       <c r="G49" s="9"/>
-      <c r="H49" s="10"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
+      <c r="H49" s="9"/>
+    </row>
+    <row r="50" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="8">
+        <v>4</v>
+      </c>
+      <c r="B50" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="21"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="10"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B51" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C51" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F51" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H50" s="15" t="s">
+      <c r="H51" s="15" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E51" s="2">
-        <v>490</v>
-      </c>
-      <c r="F51" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H51" s="10"/>
     </row>
     <row r="52" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E52" s="2">
-        <v>3</v>
+        <v>490</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="G52" s="13" t="s">
-        <v>64</v>
+        <v>107</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="H52" s="10"/>
     </row>
     <row r="53" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="E53" s="2">
         <v>3</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="H53" s="10"/>
     </row>
@@ -2790,13 +2815,13 @@
         <v>33</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>35</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="E54" s="2">
         <v>3</v>
@@ -2805,16 +2830,16 @@
         <v>109</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H54" s="10"/>
     </row>
     <row r="55" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>35</v>
@@ -2826,10 +2851,10 @@
         <v>3</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="H55" s="10"/>
     </row>
@@ -2838,30 +2863,55 @@
         <v>29</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E56" s="2">
         <v>3</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>92</v>
       </c>
       <c r="H56" s="10"/>
     </row>
+    <row r="57" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E57" s="2">
+        <v>3</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H57" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="35">
+    <mergeCell ref="B49:F49"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B48:F48"/>
-    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
@@ -2905,7 +2955,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMJ45"/>
+  <dimension ref="A1:AMJ46"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="12" customWidth="1"/>
@@ -2932,29 +2982,29 @@
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
       <c r="AMI1" s="14"/>
       <c r="AMJ1" s="14"/>
     </row>
     <row r="2" spans="1:1024" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="F2" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
       <c r="AMI2" s="14"/>
       <c r="AMJ2" s="14"/>
     </row>
@@ -3023,10 +3073,10 @@
       <c r="D6" s="7"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="26"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
@@ -3035,10 +3085,10 @@
       <c r="D7" s="7"/>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="26"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:1024" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -3047,10 +3097,10 @@
       <c r="D8" s="7"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="26"/>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
@@ -3059,22 +3109,22 @@
       <c r="D9" s="7"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="26"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -3103,14 +3153,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>117</v>
+        <v>213</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -3147,14 +3197,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="9" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -3163,7 +3213,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -3215,10 +3265,10 @@
         <v>600</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -3239,10 +3289,10 @@
         <v>24</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -3263,10 +3313,10 @@
         <v>36</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -3287,10 +3337,10 @@
         <v>68</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -3299,7 +3349,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -3311,10 +3361,10 @@
         <v>0.49</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -3323,7 +3373,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
@@ -3335,10 +3385,10 @@
         <v>0.19</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -3346,13 +3396,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -3365,7 +3415,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>169</v>
+        <v>148</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
@@ -3379,14 +3429,14 @@
         <v>2</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="H26" s="9"/>
     </row>
@@ -3409,7 +3459,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
@@ -3423,7 +3473,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -3475,10 +3525,10 @@
         <v>600</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -3582,13 +3632,13 @@
       <c r="A36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="21"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
       <c r="G36" s="1" t="s">
         <v>6</v>
       </c>
@@ -3601,7 +3651,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
@@ -3614,103 +3664,93 @@
       <c r="A38" s="8">
         <v>3</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="21"/>
       <c r="G38" s="9" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H38" s="10"/>
     </row>
-    <row r="39" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>3</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>87</v>
+        <v>186</v>
       </c>
       <c r="C39" s="18"/>
       <c r="D39" s="18"/>
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
       <c r="G39" s="9"/>
-      <c r="H39" s="10"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
+      <c r="H39" s="9"/>
+    </row>
+    <row r="40" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="8">
+        <v>3</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="10"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B41" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C41" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F41" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G41" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H40" s="15" t="s">
+      <c r="H41" s="15" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E41" s="2">
-        <v>600</v>
-      </c>
-      <c r="F41" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E42" s="2">
-        <v>2</v>
+        <v>600</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G42" s="13" t="s">
-        <v>62</v>
+        <v>86</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="H42" s="10"/>
     </row>
@@ -3719,7 +3759,7 @@
         <v>29</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>42</v>
@@ -3734,19 +3774,19 @@
         <v>82</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H43" s="10"/>
     </row>
     <row r="44" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>48</v>
@@ -3758,7 +3798,7 @@
         <v>82</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -3767,7 +3807,7 @@
         <v>40</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>45</v>
@@ -3782,12 +3822,36 @@
         <v>82</v>
       </c>
       <c r="G45" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H45" s="10"/>
+    </row>
+    <row r="46" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E46" s="2">
+        <v>2</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G46" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="H45" s="10"/>
+      <c r="H46" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
@@ -3811,7 +3875,7 @@
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B40:F40"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B29:F29"/>
@@ -3819,6 +3883,7 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B39:F39"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -3831,7 +3896,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AMJ45"/>
+  <dimension ref="A1:AMJ46"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="12" customWidth="1"/>
@@ -3858,27 +3923,27 @@
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="F2" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
@@ -3945,10 +4010,10 @@
       <c r="D6" s="7"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="26"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
@@ -3957,10 +4022,10 @@
       <c r="D7" s="7"/>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="26"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -3969,10 +4034,10 @@
       <c r="D8" s="7"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="26"/>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
@@ -3981,22 +4046,22 @@
       <c r="D9" s="7"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="26"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -4008,13 +4073,13 @@
       <c r="A11" s="8">
         <v>1</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="21"/>
       <c r="G11" s="9"/>
       <c r="H11" s="10" t="s">
         <v>22</v>
@@ -4025,14 +4090,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>135</v>
+        <v>201</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -4071,14 +4136,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>139</v>
+        <v>208</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="9" t="s">
-        <v>138</v>
+        <v>207</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -4087,7 +4152,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -4139,10 +4204,10 @@
         <v>420</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -4163,10 +4228,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -4187,10 +4252,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -4211,10 +4276,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -4223,7 +4288,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -4235,10 +4300,10 @@
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -4247,22 +4312,22 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0.2</v>
+        <v>91</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -4277,16 +4342,16 @@
         <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="F24" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -4294,13 +4359,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -5329,7 +5394,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>172</v>
+        <v>151</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
@@ -5350,7 +5415,7 @@
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="14"/>
@@ -6375,14 +6440,14 @@
         <v>2</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="14"/>
@@ -7407,7 +7472,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -7421,7 +7486,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
@@ -9504,10 +9569,10 @@
         <v>420</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -9528,10 +9593,10 @@
         <v>12</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -9552,10 +9617,10 @@
         <v>12</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -9576,10 +9641,10 @@
         <v>33</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -9588,7 +9653,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>30</v>
@@ -9600,10 +9665,10 @@
         <v>0.65</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -9612,22 +9677,22 @@
         <v>29</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>31</v>
+        <v>218</v>
       </c>
       <c r="E37" s="2">
         <v>0.4</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -9642,16 +9707,16 @@
         <v>35</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E38" s="2">
         <v>100</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -9659,13 +9724,13 @@
       <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C39" s="21"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="21"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
       <c r="G39" s="1" t="s">
         <v>6</v>
       </c>
@@ -10694,7 +10759,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="C40" s="18"/>
       <c r="D40" s="18"/>
@@ -10708,14 +10773,14 @@
         <v>3</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>145</v>
+        <v>210</v>
       </c>
       <c r="C41" s="18"/>
       <c r="D41" s="18"/>
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
       <c r="G41" s="9" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="H41" s="10"/>
       <c r="I41" s="14"/>
@@ -11735,1061 +11800,33 @@
       <c r="AMI41" s="14"/>
       <c r="AMJ41" s="14"/>
     </row>
-    <row r="42" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1024" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>3</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>87</v>
+        <v>187</v>
       </c>
       <c r="C42" s="18"/>
       <c r="D42" s="18"/>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
       <c r="G42" s="9"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="14"/>
-      <c r="O42" s="14"/>
-      <c r="P42" s="14"/>
-      <c r="Q42" s="14"/>
-      <c r="R42" s="14"/>
-      <c r="S42" s="14"/>
-      <c r="T42" s="14"/>
-      <c r="U42" s="14"/>
-      <c r="V42" s="14"/>
-      <c r="W42" s="14"/>
-      <c r="X42" s="14"/>
-      <c r="Y42" s="14"/>
-      <c r="Z42" s="14"/>
-      <c r="AA42" s="14"/>
-      <c r="AB42" s="14"/>
-      <c r="AC42" s="14"/>
-      <c r="AD42" s="14"/>
-      <c r="AE42" s="14"/>
-      <c r="AF42" s="14"/>
-      <c r="AG42" s="14"/>
-      <c r="AH42" s="14"/>
-      <c r="AI42" s="14"/>
-      <c r="AJ42" s="14"/>
-      <c r="AK42" s="14"/>
-      <c r="AL42" s="14"/>
-      <c r="AM42" s="14"/>
-      <c r="AN42" s="14"/>
-      <c r="AO42" s="14"/>
-      <c r="AP42" s="14"/>
-      <c r="AQ42" s="14"/>
-      <c r="AR42" s="14"/>
-      <c r="AS42" s="14"/>
-      <c r="AT42" s="14"/>
-      <c r="AU42" s="14"/>
-      <c r="AV42" s="14"/>
-      <c r="AW42" s="14"/>
-      <c r="AX42" s="14"/>
-      <c r="AY42" s="14"/>
-      <c r="AZ42" s="14"/>
-      <c r="BA42" s="14"/>
-      <c r="BB42" s="14"/>
-      <c r="BC42" s="14"/>
-      <c r="BD42" s="14"/>
-      <c r="BE42" s="14"/>
-      <c r="BF42" s="14"/>
-      <c r="BG42" s="14"/>
-      <c r="BH42" s="14"/>
-      <c r="BI42" s="14"/>
-      <c r="BJ42" s="14"/>
-      <c r="BK42" s="14"/>
-      <c r="BL42" s="14"/>
-      <c r="BM42" s="14"/>
-      <c r="BN42" s="14"/>
-      <c r="BO42" s="14"/>
-      <c r="BP42" s="14"/>
-      <c r="BQ42" s="14"/>
-      <c r="BR42" s="14"/>
-      <c r="BS42" s="14"/>
-      <c r="BT42" s="14"/>
-      <c r="BU42" s="14"/>
-      <c r="BV42" s="14"/>
-      <c r="BW42" s="14"/>
-      <c r="BX42" s="14"/>
-      <c r="BY42" s="14"/>
-      <c r="BZ42" s="14"/>
-      <c r="CA42" s="14"/>
-      <c r="CB42" s="14"/>
-      <c r="CC42" s="14"/>
-      <c r="CD42" s="14"/>
-      <c r="CE42" s="14"/>
-      <c r="CF42" s="14"/>
-      <c r="CG42" s="14"/>
-      <c r="CH42" s="14"/>
-      <c r="CI42" s="14"/>
-      <c r="CJ42" s="14"/>
-      <c r="CK42" s="14"/>
-      <c r="CL42" s="14"/>
-      <c r="CM42" s="14"/>
-      <c r="CN42" s="14"/>
-      <c r="CO42" s="14"/>
-      <c r="CP42" s="14"/>
-      <c r="CQ42" s="14"/>
-      <c r="CR42" s="14"/>
-      <c r="CS42" s="14"/>
-      <c r="CT42" s="14"/>
-      <c r="CU42" s="14"/>
-      <c r="CV42" s="14"/>
-      <c r="CW42" s="14"/>
-      <c r="CX42" s="14"/>
-      <c r="CY42" s="14"/>
-      <c r="CZ42" s="14"/>
-      <c r="DA42" s="14"/>
-      <c r="DB42" s="14"/>
-      <c r="DC42" s="14"/>
-      <c r="DD42" s="14"/>
-      <c r="DE42" s="14"/>
-      <c r="DF42" s="14"/>
-      <c r="DG42" s="14"/>
-      <c r="DH42" s="14"/>
-      <c r="DI42" s="14"/>
-      <c r="DJ42" s="14"/>
-      <c r="DK42" s="14"/>
-      <c r="DL42" s="14"/>
-      <c r="DM42" s="14"/>
-      <c r="DN42" s="14"/>
-      <c r="DO42" s="14"/>
-      <c r="DP42" s="14"/>
-      <c r="DQ42" s="14"/>
-      <c r="DR42" s="14"/>
-      <c r="DS42" s="14"/>
-      <c r="DT42" s="14"/>
-      <c r="DU42" s="14"/>
-      <c r="DV42" s="14"/>
-      <c r="DW42" s="14"/>
-      <c r="DX42" s="14"/>
-      <c r="DY42" s="14"/>
-      <c r="DZ42" s="14"/>
-      <c r="EA42" s="14"/>
-      <c r="EB42" s="14"/>
-      <c r="EC42" s="14"/>
-      <c r="ED42" s="14"/>
-      <c r="EE42" s="14"/>
-      <c r="EF42" s="14"/>
-      <c r="EG42" s="14"/>
-      <c r="EH42" s="14"/>
-      <c r="EI42" s="14"/>
-      <c r="EJ42" s="14"/>
-      <c r="EK42" s="14"/>
-      <c r="EL42" s="14"/>
-      <c r="EM42" s="14"/>
-      <c r="EN42" s="14"/>
-      <c r="EO42" s="14"/>
-      <c r="EP42" s="14"/>
-      <c r="EQ42" s="14"/>
-      <c r="ER42" s="14"/>
-      <c r="ES42" s="14"/>
-      <c r="ET42" s="14"/>
-      <c r="EU42" s="14"/>
-      <c r="EV42" s="14"/>
-      <c r="EW42" s="14"/>
-      <c r="EX42" s="14"/>
-      <c r="EY42" s="14"/>
-      <c r="EZ42" s="14"/>
-      <c r="FA42" s="14"/>
-      <c r="FB42" s="14"/>
-      <c r="FC42" s="14"/>
-      <c r="FD42" s="14"/>
-      <c r="FE42" s="14"/>
-      <c r="FF42" s="14"/>
-      <c r="FG42" s="14"/>
-      <c r="FH42" s="14"/>
-      <c r="FI42" s="14"/>
-      <c r="FJ42" s="14"/>
-      <c r="FK42" s="14"/>
-      <c r="FL42" s="14"/>
-      <c r="FM42" s="14"/>
-      <c r="FN42" s="14"/>
-      <c r="FO42" s="14"/>
-      <c r="FP42" s="14"/>
-      <c r="FQ42" s="14"/>
-      <c r="FR42" s="14"/>
-      <c r="FS42" s="14"/>
-      <c r="FT42" s="14"/>
-      <c r="FU42" s="14"/>
-      <c r="FV42" s="14"/>
-      <c r="FW42" s="14"/>
-      <c r="FX42" s="14"/>
-      <c r="FY42" s="14"/>
-      <c r="FZ42" s="14"/>
-      <c r="GA42" s="14"/>
-      <c r="GB42" s="14"/>
-      <c r="GC42" s="14"/>
-      <c r="GD42" s="14"/>
-      <c r="GE42" s="14"/>
-      <c r="GF42" s="14"/>
-      <c r="GG42" s="14"/>
-      <c r="GH42" s="14"/>
-      <c r="GI42" s="14"/>
-      <c r="GJ42" s="14"/>
-      <c r="GK42" s="14"/>
-      <c r="GL42" s="14"/>
-      <c r="GM42" s="14"/>
-      <c r="GN42" s="14"/>
-      <c r="GO42" s="14"/>
-      <c r="GP42" s="14"/>
-      <c r="GQ42" s="14"/>
-      <c r="GR42" s="14"/>
-      <c r="GS42" s="14"/>
-      <c r="GT42" s="14"/>
-      <c r="GU42" s="14"/>
-      <c r="GV42" s="14"/>
-      <c r="GW42" s="14"/>
-      <c r="GX42" s="14"/>
-      <c r="GY42" s="14"/>
-      <c r="GZ42" s="14"/>
-      <c r="HA42" s="14"/>
-      <c r="HB42" s="14"/>
-      <c r="HC42" s="14"/>
-      <c r="HD42" s="14"/>
-      <c r="HE42" s="14"/>
-      <c r="HF42" s="14"/>
-      <c r="HG42" s="14"/>
-      <c r="HH42" s="14"/>
-      <c r="HI42" s="14"/>
-      <c r="HJ42" s="14"/>
-      <c r="HK42" s="14"/>
-      <c r="HL42" s="14"/>
-      <c r="HM42" s="14"/>
-      <c r="HN42" s="14"/>
-      <c r="HO42" s="14"/>
-      <c r="HP42" s="14"/>
-      <c r="HQ42" s="14"/>
-      <c r="HR42" s="14"/>
-      <c r="HS42" s="14"/>
-      <c r="HT42" s="14"/>
-      <c r="HU42" s="14"/>
-      <c r="HV42" s="14"/>
-      <c r="HW42" s="14"/>
-      <c r="HX42" s="14"/>
-      <c r="HY42" s="14"/>
-      <c r="HZ42" s="14"/>
-      <c r="IA42" s="14"/>
-      <c r="IB42" s="14"/>
-      <c r="IC42" s="14"/>
-      <c r="ID42" s="14"/>
-      <c r="IE42" s="14"/>
-      <c r="IF42" s="14"/>
-      <c r="IG42" s="14"/>
-      <c r="IH42" s="14"/>
-      <c r="II42" s="14"/>
-      <c r="IJ42" s="14"/>
-      <c r="IK42" s="14"/>
-      <c r="IL42" s="14"/>
-      <c r="IM42" s="14"/>
-      <c r="IN42" s="14"/>
-      <c r="IO42" s="14"/>
-      <c r="IP42" s="14"/>
-      <c r="IQ42" s="14"/>
-      <c r="IR42" s="14"/>
-      <c r="IS42" s="14"/>
-      <c r="IT42" s="14"/>
-      <c r="IU42" s="14"/>
-      <c r="IV42" s="14"/>
-      <c r="IW42" s="14"/>
-      <c r="IX42" s="14"/>
-      <c r="IY42" s="14"/>
-      <c r="IZ42" s="14"/>
-      <c r="JA42" s="14"/>
-      <c r="JB42" s="14"/>
-      <c r="JC42" s="14"/>
-      <c r="JD42" s="14"/>
-      <c r="JE42" s="14"/>
-      <c r="JF42" s="14"/>
-      <c r="JG42" s="14"/>
-      <c r="JH42" s="14"/>
-      <c r="JI42" s="14"/>
-      <c r="JJ42" s="14"/>
-      <c r="JK42" s="14"/>
-      <c r="JL42" s="14"/>
-      <c r="JM42" s="14"/>
-      <c r="JN42" s="14"/>
-      <c r="JO42" s="14"/>
-      <c r="JP42" s="14"/>
-      <c r="JQ42" s="14"/>
-      <c r="JR42" s="14"/>
-      <c r="JS42" s="14"/>
-      <c r="JT42" s="14"/>
-      <c r="JU42" s="14"/>
-      <c r="JV42" s="14"/>
-      <c r="JW42" s="14"/>
-      <c r="JX42" s="14"/>
-      <c r="JY42" s="14"/>
-      <c r="JZ42" s="14"/>
-      <c r="KA42" s="14"/>
-      <c r="KB42" s="14"/>
-      <c r="KC42" s="14"/>
-      <c r="KD42" s="14"/>
-      <c r="KE42" s="14"/>
-      <c r="KF42" s="14"/>
-      <c r="KG42" s="14"/>
-      <c r="KH42" s="14"/>
-      <c r="KI42" s="14"/>
-      <c r="KJ42" s="14"/>
-      <c r="KK42" s="14"/>
-      <c r="KL42" s="14"/>
-      <c r="KM42" s="14"/>
-      <c r="KN42" s="14"/>
-      <c r="KO42" s="14"/>
-      <c r="KP42" s="14"/>
-      <c r="KQ42" s="14"/>
-      <c r="KR42" s="14"/>
-      <c r="KS42" s="14"/>
-      <c r="KT42" s="14"/>
-      <c r="KU42" s="14"/>
-      <c r="KV42" s="14"/>
-      <c r="KW42" s="14"/>
-      <c r="KX42" s="14"/>
-      <c r="KY42" s="14"/>
-      <c r="KZ42" s="14"/>
-      <c r="LA42" s="14"/>
-      <c r="LB42" s="14"/>
-      <c r="LC42" s="14"/>
-      <c r="LD42" s="14"/>
-      <c r="LE42" s="14"/>
-      <c r="LF42" s="14"/>
-      <c r="LG42" s="14"/>
-      <c r="LH42" s="14"/>
-      <c r="LI42" s="14"/>
-      <c r="LJ42" s="14"/>
-      <c r="LK42" s="14"/>
-      <c r="LL42" s="14"/>
-      <c r="LM42" s="14"/>
-      <c r="LN42" s="14"/>
-      <c r="LO42" s="14"/>
-      <c r="LP42" s="14"/>
-      <c r="LQ42" s="14"/>
-      <c r="LR42" s="14"/>
-      <c r="LS42" s="14"/>
-      <c r="LT42" s="14"/>
-      <c r="LU42" s="14"/>
-      <c r="LV42" s="14"/>
-      <c r="LW42" s="14"/>
-      <c r="LX42" s="14"/>
-      <c r="LY42" s="14"/>
-      <c r="LZ42" s="14"/>
-      <c r="MA42" s="14"/>
-      <c r="MB42" s="14"/>
-      <c r="MC42" s="14"/>
-      <c r="MD42" s="14"/>
-      <c r="ME42" s="14"/>
-      <c r="MF42" s="14"/>
-      <c r="MG42" s="14"/>
-      <c r="MH42" s="14"/>
-      <c r="MI42" s="14"/>
-      <c r="MJ42" s="14"/>
-      <c r="MK42" s="14"/>
-      <c r="ML42" s="14"/>
-      <c r="MM42" s="14"/>
-      <c r="MN42" s="14"/>
-      <c r="MO42" s="14"/>
-      <c r="MP42" s="14"/>
-      <c r="MQ42" s="14"/>
-      <c r="MR42" s="14"/>
-      <c r="MS42" s="14"/>
-      <c r="MT42" s="14"/>
-      <c r="MU42" s="14"/>
-      <c r="MV42" s="14"/>
-      <c r="MW42" s="14"/>
-      <c r="MX42" s="14"/>
-      <c r="MY42" s="14"/>
-      <c r="MZ42" s="14"/>
-      <c r="NA42" s="14"/>
-      <c r="NB42" s="14"/>
-      <c r="NC42" s="14"/>
-      <c r="ND42" s="14"/>
-      <c r="NE42" s="14"/>
-      <c r="NF42" s="14"/>
-      <c r="NG42" s="14"/>
-      <c r="NH42" s="14"/>
-      <c r="NI42" s="14"/>
-      <c r="NJ42" s="14"/>
-      <c r="NK42" s="14"/>
-      <c r="NL42" s="14"/>
-      <c r="NM42" s="14"/>
-      <c r="NN42" s="14"/>
-      <c r="NO42" s="14"/>
-      <c r="NP42" s="14"/>
-      <c r="NQ42" s="14"/>
-      <c r="NR42" s="14"/>
-      <c r="NS42" s="14"/>
-      <c r="NT42" s="14"/>
-      <c r="NU42" s="14"/>
-      <c r="NV42" s="14"/>
-      <c r="NW42" s="14"/>
-      <c r="NX42" s="14"/>
-      <c r="NY42" s="14"/>
-      <c r="NZ42" s="14"/>
-      <c r="OA42" s="14"/>
-      <c r="OB42" s="14"/>
-      <c r="OC42" s="14"/>
-      <c r="OD42" s="14"/>
-      <c r="OE42" s="14"/>
-      <c r="OF42" s="14"/>
-      <c r="OG42" s="14"/>
-      <c r="OH42" s="14"/>
-      <c r="OI42" s="14"/>
-      <c r="OJ42" s="14"/>
-      <c r="OK42" s="14"/>
-      <c r="OL42" s="14"/>
-      <c r="OM42" s="14"/>
-      <c r="ON42" s="14"/>
-      <c r="OO42" s="14"/>
-      <c r="OP42" s="14"/>
-      <c r="OQ42" s="14"/>
-      <c r="OR42" s="14"/>
-      <c r="OS42" s="14"/>
-      <c r="OT42" s="14"/>
-      <c r="OU42" s="14"/>
-      <c r="OV42" s="14"/>
-      <c r="OW42" s="14"/>
-      <c r="OX42" s="14"/>
-      <c r="OY42" s="14"/>
-      <c r="OZ42" s="14"/>
-      <c r="PA42" s="14"/>
-      <c r="PB42" s="14"/>
-      <c r="PC42" s="14"/>
-      <c r="PD42" s="14"/>
-      <c r="PE42" s="14"/>
-      <c r="PF42" s="14"/>
-      <c r="PG42" s="14"/>
-      <c r="PH42" s="14"/>
-      <c r="PI42" s="14"/>
-      <c r="PJ42" s="14"/>
-      <c r="PK42" s="14"/>
-      <c r="PL42" s="14"/>
-      <c r="PM42" s="14"/>
-      <c r="PN42" s="14"/>
-      <c r="PO42" s="14"/>
-      <c r="PP42" s="14"/>
-      <c r="PQ42" s="14"/>
-      <c r="PR42" s="14"/>
-      <c r="PS42" s="14"/>
-      <c r="PT42" s="14"/>
-      <c r="PU42" s="14"/>
-      <c r="PV42" s="14"/>
-      <c r="PW42" s="14"/>
-      <c r="PX42" s="14"/>
-      <c r="PY42" s="14"/>
-      <c r="PZ42" s="14"/>
-      <c r="QA42" s="14"/>
-      <c r="QB42" s="14"/>
-      <c r="QC42" s="14"/>
-      <c r="QD42" s="14"/>
-      <c r="QE42" s="14"/>
-      <c r="QF42" s="14"/>
-      <c r="QG42" s="14"/>
-      <c r="QH42" s="14"/>
-      <c r="QI42" s="14"/>
-      <c r="QJ42" s="14"/>
-      <c r="QK42" s="14"/>
-      <c r="QL42" s="14"/>
-      <c r="QM42" s="14"/>
-      <c r="QN42" s="14"/>
-      <c r="QO42" s="14"/>
-      <c r="QP42" s="14"/>
-      <c r="QQ42" s="14"/>
-      <c r="QR42" s="14"/>
-      <c r="QS42" s="14"/>
-      <c r="QT42" s="14"/>
-      <c r="QU42" s="14"/>
-      <c r="QV42" s="14"/>
-      <c r="QW42" s="14"/>
-      <c r="QX42" s="14"/>
-      <c r="QY42" s="14"/>
-      <c r="QZ42" s="14"/>
-      <c r="RA42" s="14"/>
-      <c r="RB42" s="14"/>
-      <c r="RC42" s="14"/>
-      <c r="RD42" s="14"/>
-      <c r="RE42" s="14"/>
-      <c r="RF42" s="14"/>
-      <c r="RG42" s="14"/>
-      <c r="RH42" s="14"/>
-      <c r="RI42" s="14"/>
-      <c r="RJ42" s="14"/>
-      <c r="RK42" s="14"/>
-      <c r="RL42" s="14"/>
-      <c r="RM42" s="14"/>
-      <c r="RN42" s="14"/>
-      <c r="RO42" s="14"/>
-      <c r="RP42" s="14"/>
-      <c r="RQ42" s="14"/>
-      <c r="RR42" s="14"/>
-      <c r="RS42" s="14"/>
-      <c r="RT42" s="14"/>
-      <c r="RU42" s="14"/>
-      <c r="RV42" s="14"/>
-      <c r="RW42" s="14"/>
-      <c r="RX42" s="14"/>
-      <c r="RY42" s="14"/>
-      <c r="RZ42" s="14"/>
-      <c r="SA42" s="14"/>
-      <c r="SB42" s="14"/>
-      <c r="SC42" s="14"/>
-      <c r="SD42" s="14"/>
-      <c r="SE42" s="14"/>
-      <c r="SF42" s="14"/>
-      <c r="SG42" s="14"/>
-      <c r="SH42" s="14"/>
-      <c r="SI42" s="14"/>
-      <c r="SJ42" s="14"/>
-      <c r="SK42" s="14"/>
-      <c r="SL42" s="14"/>
-      <c r="SM42" s="14"/>
-      <c r="SN42" s="14"/>
-      <c r="SO42" s="14"/>
-      <c r="SP42" s="14"/>
-      <c r="SQ42" s="14"/>
-      <c r="SR42" s="14"/>
-      <c r="SS42" s="14"/>
-      <c r="ST42" s="14"/>
-      <c r="SU42" s="14"/>
-      <c r="SV42" s="14"/>
-      <c r="SW42" s="14"/>
-      <c r="SX42" s="14"/>
-      <c r="SY42" s="14"/>
-      <c r="SZ42" s="14"/>
-      <c r="TA42" s="14"/>
-      <c r="TB42" s="14"/>
-      <c r="TC42" s="14"/>
-      <c r="TD42" s="14"/>
-      <c r="TE42" s="14"/>
-      <c r="TF42" s="14"/>
-      <c r="TG42" s="14"/>
-      <c r="TH42" s="14"/>
-      <c r="TI42" s="14"/>
-      <c r="TJ42" s="14"/>
-      <c r="TK42" s="14"/>
-      <c r="TL42" s="14"/>
-      <c r="TM42" s="14"/>
-      <c r="TN42" s="14"/>
-      <c r="TO42" s="14"/>
-      <c r="TP42" s="14"/>
-      <c r="TQ42" s="14"/>
-      <c r="TR42" s="14"/>
-      <c r="TS42" s="14"/>
-      <c r="TT42" s="14"/>
-      <c r="TU42" s="14"/>
-      <c r="TV42" s="14"/>
-      <c r="TW42" s="14"/>
-      <c r="TX42" s="14"/>
-      <c r="TY42" s="14"/>
-      <c r="TZ42" s="14"/>
-      <c r="UA42" s="14"/>
-      <c r="UB42" s="14"/>
-      <c r="UC42" s="14"/>
-      <c r="UD42" s="14"/>
-      <c r="UE42" s="14"/>
-      <c r="UF42" s="14"/>
-      <c r="UG42" s="14"/>
-      <c r="UH42" s="14"/>
-      <c r="UI42" s="14"/>
-      <c r="UJ42" s="14"/>
-      <c r="UK42" s="14"/>
-      <c r="UL42" s="14"/>
-      <c r="UM42" s="14"/>
-      <c r="UN42" s="14"/>
-      <c r="UO42" s="14"/>
-      <c r="UP42" s="14"/>
-      <c r="UQ42" s="14"/>
-      <c r="UR42" s="14"/>
-      <c r="US42" s="14"/>
-      <c r="UT42" s="14"/>
-      <c r="UU42" s="14"/>
-      <c r="UV42" s="14"/>
-      <c r="UW42" s="14"/>
-      <c r="UX42" s="14"/>
-      <c r="UY42" s="14"/>
-      <c r="UZ42" s="14"/>
-      <c r="VA42" s="14"/>
-      <c r="VB42" s="14"/>
-      <c r="VC42" s="14"/>
-      <c r="VD42" s="14"/>
-      <c r="VE42" s="14"/>
-      <c r="VF42" s="14"/>
-      <c r="VG42" s="14"/>
-      <c r="VH42" s="14"/>
-      <c r="VI42" s="14"/>
-      <c r="VJ42" s="14"/>
-      <c r="VK42" s="14"/>
-      <c r="VL42" s="14"/>
-      <c r="VM42" s="14"/>
-      <c r="VN42" s="14"/>
-      <c r="VO42" s="14"/>
-      <c r="VP42" s="14"/>
-      <c r="VQ42" s="14"/>
-      <c r="VR42" s="14"/>
-      <c r="VS42" s="14"/>
-      <c r="VT42" s="14"/>
-      <c r="VU42" s="14"/>
-      <c r="VV42" s="14"/>
-      <c r="VW42" s="14"/>
-      <c r="VX42" s="14"/>
-      <c r="VY42" s="14"/>
-      <c r="VZ42" s="14"/>
-      <c r="WA42" s="14"/>
-      <c r="WB42" s="14"/>
-      <c r="WC42" s="14"/>
-      <c r="WD42" s="14"/>
-      <c r="WE42" s="14"/>
-      <c r="WF42" s="14"/>
-      <c r="WG42" s="14"/>
-      <c r="WH42" s="14"/>
-      <c r="WI42" s="14"/>
-      <c r="WJ42" s="14"/>
-      <c r="WK42" s="14"/>
-      <c r="WL42" s="14"/>
-      <c r="WM42" s="14"/>
-      <c r="WN42" s="14"/>
-      <c r="WO42" s="14"/>
-      <c r="WP42" s="14"/>
-      <c r="WQ42" s="14"/>
-      <c r="WR42" s="14"/>
-      <c r="WS42" s="14"/>
-      <c r="WT42" s="14"/>
-      <c r="WU42" s="14"/>
-      <c r="WV42" s="14"/>
-      <c r="WW42" s="14"/>
-      <c r="WX42" s="14"/>
-      <c r="WY42" s="14"/>
-      <c r="WZ42" s="14"/>
-      <c r="XA42" s="14"/>
-      <c r="XB42" s="14"/>
-      <c r="XC42" s="14"/>
-      <c r="XD42" s="14"/>
-      <c r="XE42" s="14"/>
-      <c r="XF42" s="14"/>
-      <c r="XG42" s="14"/>
-      <c r="XH42" s="14"/>
-      <c r="XI42" s="14"/>
-      <c r="XJ42" s="14"/>
-      <c r="XK42" s="14"/>
-      <c r="XL42" s="14"/>
-      <c r="XM42" s="14"/>
-      <c r="XN42" s="14"/>
-      <c r="XO42" s="14"/>
-      <c r="XP42" s="14"/>
-      <c r="XQ42" s="14"/>
-      <c r="XR42" s="14"/>
-      <c r="XS42" s="14"/>
-      <c r="XT42" s="14"/>
-      <c r="XU42" s="14"/>
-      <c r="XV42" s="14"/>
-      <c r="XW42" s="14"/>
-      <c r="XX42" s="14"/>
-      <c r="XY42" s="14"/>
-      <c r="XZ42" s="14"/>
-      <c r="YA42" s="14"/>
-      <c r="YB42" s="14"/>
-      <c r="YC42" s="14"/>
-      <c r="YD42" s="14"/>
-      <c r="YE42" s="14"/>
-      <c r="YF42" s="14"/>
-      <c r="YG42" s="14"/>
-      <c r="YH42" s="14"/>
-      <c r="YI42" s="14"/>
-      <c r="YJ42" s="14"/>
-      <c r="YK42" s="14"/>
-      <c r="YL42" s="14"/>
-      <c r="YM42" s="14"/>
-      <c r="YN42" s="14"/>
-      <c r="YO42" s="14"/>
-      <c r="YP42" s="14"/>
-      <c r="YQ42" s="14"/>
-      <c r="YR42" s="14"/>
-      <c r="YS42" s="14"/>
-      <c r="YT42" s="14"/>
-      <c r="YU42" s="14"/>
-      <c r="YV42" s="14"/>
-      <c r="YW42" s="14"/>
-      <c r="YX42" s="14"/>
-      <c r="YY42" s="14"/>
-      <c r="YZ42" s="14"/>
-      <c r="ZA42" s="14"/>
-      <c r="ZB42" s="14"/>
-      <c r="ZC42" s="14"/>
-      <c r="ZD42" s="14"/>
-      <c r="ZE42" s="14"/>
-      <c r="ZF42" s="14"/>
-      <c r="ZG42" s="14"/>
-      <c r="ZH42" s="14"/>
-      <c r="ZI42" s="14"/>
-      <c r="ZJ42" s="14"/>
-      <c r="ZK42" s="14"/>
-      <c r="ZL42" s="14"/>
-      <c r="ZM42" s="14"/>
-      <c r="ZN42" s="14"/>
-      <c r="ZO42" s="14"/>
-      <c r="ZP42" s="14"/>
-      <c r="ZQ42" s="14"/>
-      <c r="ZR42" s="14"/>
-      <c r="ZS42" s="14"/>
-      <c r="ZT42" s="14"/>
-      <c r="ZU42" s="14"/>
-      <c r="ZV42" s="14"/>
-      <c r="ZW42" s="14"/>
-      <c r="ZX42" s="14"/>
-      <c r="ZY42" s="14"/>
-      <c r="ZZ42" s="14"/>
-      <c r="AAA42" s="14"/>
-      <c r="AAB42" s="14"/>
-      <c r="AAC42" s="14"/>
-      <c r="AAD42" s="14"/>
-      <c r="AAE42" s="14"/>
-      <c r="AAF42" s="14"/>
-      <c r="AAG42" s="14"/>
-      <c r="AAH42" s="14"/>
-      <c r="AAI42" s="14"/>
-      <c r="AAJ42" s="14"/>
-      <c r="AAK42" s="14"/>
-      <c r="AAL42" s="14"/>
-      <c r="AAM42" s="14"/>
-      <c r="AAN42" s="14"/>
-      <c r="AAO42" s="14"/>
-      <c r="AAP42" s="14"/>
-      <c r="AAQ42" s="14"/>
-      <c r="AAR42" s="14"/>
-      <c r="AAS42" s="14"/>
-      <c r="AAT42" s="14"/>
-      <c r="AAU42" s="14"/>
-      <c r="AAV42" s="14"/>
-      <c r="AAW42" s="14"/>
-      <c r="AAX42" s="14"/>
-      <c r="AAY42" s="14"/>
-      <c r="AAZ42" s="14"/>
-      <c r="ABA42" s="14"/>
-      <c r="ABB42" s="14"/>
-      <c r="ABC42" s="14"/>
-      <c r="ABD42" s="14"/>
-      <c r="ABE42" s="14"/>
-      <c r="ABF42" s="14"/>
-      <c r="ABG42" s="14"/>
-      <c r="ABH42" s="14"/>
-      <c r="ABI42" s="14"/>
-      <c r="ABJ42" s="14"/>
-      <c r="ABK42" s="14"/>
-      <c r="ABL42" s="14"/>
-      <c r="ABM42" s="14"/>
-      <c r="ABN42" s="14"/>
-      <c r="ABO42" s="14"/>
-      <c r="ABP42" s="14"/>
-      <c r="ABQ42" s="14"/>
-      <c r="ABR42" s="14"/>
-      <c r="ABS42" s="14"/>
-      <c r="ABT42" s="14"/>
-      <c r="ABU42" s="14"/>
-      <c r="ABV42" s="14"/>
-      <c r="ABW42" s="14"/>
-      <c r="ABX42" s="14"/>
-      <c r="ABY42" s="14"/>
-      <c r="ABZ42" s="14"/>
-      <c r="ACA42" s="14"/>
-      <c r="ACB42" s="14"/>
-      <c r="ACC42" s="14"/>
-      <c r="ACD42" s="14"/>
-      <c r="ACE42" s="14"/>
-      <c r="ACF42" s="14"/>
-      <c r="ACG42" s="14"/>
-      <c r="ACH42" s="14"/>
-      <c r="ACI42" s="14"/>
-      <c r="ACJ42" s="14"/>
-      <c r="ACK42" s="14"/>
-      <c r="ACL42" s="14"/>
-      <c r="ACM42" s="14"/>
-      <c r="ACN42" s="14"/>
-      <c r="ACO42" s="14"/>
-      <c r="ACP42" s="14"/>
-      <c r="ACQ42" s="14"/>
-      <c r="ACR42" s="14"/>
-      <c r="ACS42" s="14"/>
-      <c r="ACT42" s="14"/>
-      <c r="ACU42" s="14"/>
-      <c r="ACV42" s="14"/>
-      <c r="ACW42" s="14"/>
-      <c r="ACX42" s="14"/>
-      <c r="ACY42" s="14"/>
-      <c r="ACZ42" s="14"/>
-      <c r="ADA42" s="14"/>
-      <c r="ADB42" s="14"/>
-      <c r="ADC42" s="14"/>
-      <c r="ADD42" s="14"/>
-      <c r="ADE42" s="14"/>
-      <c r="ADF42" s="14"/>
-      <c r="ADG42" s="14"/>
-      <c r="ADH42" s="14"/>
-      <c r="ADI42" s="14"/>
-      <c r="ADJ42" s="14"/>
-      <c r="ADK42" s="14"/>
-      <c r="ADL42" s="14"/>
-      <c r="ADM42" s="14"/>
-      <c r="ADN42" s="14"/>
-      <c r="ADO42" s="14"/>
-      <c r="ADP42" s="14"/>
-      <c r="ADQ42" s="14"/>
-      <c r="ADR42" s="14"/>
-      <c r="ADS42" s="14"/>
-      <c r="ADT42" s="14"/>
-      <c r="ADU42" s="14"/>
-      <c r="ADV42" s="14"/>
-      <c r="ADW42" s="14"/>
-      <c r="ADX42" s="14"/>
-      <c r="ADY42" s="14"/>
-      <c r="ADZ42" s="14"/>
-      <c r="AEA42" s="14"/>
-      <c r="AEB42" s="14"/>
-      <c r="AEC42" s="14"/>
-      <c r="AED42" s="14"/>
-      <c r="AEE42" s="14"/>
-      <c r="AEF42" s="14"/>
-      <c r="AEG42" s="14"/>
-      <c r="AEH42" s="14"/>
-      <c r="AEI42" s="14"/>
-      <c r="AEJ42" s="14"/>
-      <c r="AEK42" s="14"/>
-      <c r="AEL42" s="14"/>
-      <c r="AEM42" s="14"/>
-      <c r="AEN42" s="14"/>
-      <c r="AEO42" s="14"/>
-      <c r="AEP42" s="14"/>
-      <c r="AEQ42" s="14"/>
-      <c r="AER42" s="14"/>
-      <c r="AES42" s="14"/>
-      <c r="AET42" s="14"/>
-      <c r="AEU42" s="14"/>
-      <c r="AEV42" s="14"/>
-      <c r="AEW42" s="14"/>
-      <c r="AEX42" s="14"/>
-      <c r="AEY42" s="14"/>
-      <c r="AEZ42" s="14"/>
-      <c r="AFA42" s="14"/>
-      <c r="AFB42" s="14"/>
-      <c r="AFC42" s="14"/>
-      <c r="AFD42" s="14"/>
-      <c r="AFE42" s="14"/>
-      <c r="AFF42" s="14"/>
-      <c r="AFG42" s="14"/>
-      <c r="AFH42" s="14"/>
-      <c r="AFI42" s="14"/>
-      <c r="AFJ42" s="14"/>
-      <c r="AFK42" s="14"/>
-      <c r="AFL42" s="14"/>
-      <c r="AFM42" s="14"/>
-      <c r="AFN42" s="14"/>
-      <c r="AFO42" s="14"/>
-      <c r="AFP42" s="14"/>
-      <c r="AFQ42" s="14"/>
-      <c r="AFR42" s="14"/>
-      <c r="AFS42" s="14"/>
-      <c r="AFT42" s="14"/>
-      <c r="AFU42" s="14"/>
-      <c r="AFV42" s="14"/>
-      <c r="AFW42" s="14"/>
-      <c r="AFX42" s="14"/>
-      <c r="AFY42" s="14"/>
-      <c r="AFZ42" s="14"/>
-      <c r="AGA42" s="14"/>
-      <c r="AGB42" s="14"/>
-      <c r="AGC42" s="14"/>
-      <c r="AGD42" s="14"/>
-      <c r="AGE42" s="14"/>
-      <c r="AGF42" s="14"/>
-      <c r="AGG42" s="14"/>
-      <c r="AGH42" s="14"/>
-      <c r="AGI42" s="14"/>
-      <c r="AGJ42" s="14"/>
-      <c r="AGK42" s="14"/>
-      <c r="AGL42" s="14"/>
-      <c r="AGM42" s="14"/>
-      <c r="AGN42" s="14"/>
-      <c r="AGO42" s="14"/>
-      <c r="AGP42" s="14"/>
-      <c r="AGQ42" s="14"/>
-      <c r="AGR42" s="14"/>
-      <c r="AGS42" s="14"/>
-      <c r="AGT42" s="14"/>
-      <c r="AGU42" s="14"/>
-      <c r="AGV42" s="14"/>
-      <c r="AGW42" s="14"/>
-      <c r="AGX42" s="14"/>
-      <c r="AGY42" s="14"/>
-      <c r="AGZ42" s="14"/>
-      <c r="AHA42" s="14"/>
-      <c r="AHB42" s="14"/>
-      <c r="AHC42" s="14"/>
-      <c r="AHD42" s="14"/>
-      <c r="AHE42" s="14"/>
-      <c r="AHF42" s="14"/>
-      <c r="AHG42" s="14"/>
-      <c r="AHH42" s="14"/>
-      <c r="AHI42" s="14"/>
-      <c r="AHJ42" s="14"/>
-      <c r="AHK42" s="14"/>
-      <c r="AHL42" s="14"/>
-      <c r="AHM42" s="14"/>
-      <c r="AHN42" s="14"/>
-      <c r="AHO42" s="14"/>
-      <c r="AHP42" s="14"/>
-      <c r="AHQ42" s="14"/>
-      <c r="AHR42" s="14"/>
-      <c r="AHS42" s="14"/>
-      <c r="AHT42" s="14"/>
-      <c r="AHU42" s="14"/>
-      <c r="AHV42" s="14"/>
-      <c r="AHW42" s="14"/>
-      <c r="AHX42" s="14"/>
-      <c r="AHY42" s="14"/>
-      <c r="AHZ42" s="14"/>
-      <c r="AIA42" s="14"/>
-      <c r="AIB42" s="14"/>
-      <c r="AIC42" s="14"/>
-      <c r="AID42" s="14"/>
-      <c r="AIE42" s="14"/>
-      <c r="AIF42" s="14"/>
-      <c r="AIG42" s="14"/>
-      <c r="AIH42" s="14"/>
-      <c r="AII42" s="14"/>
-      <c r="AIJ42" s="14"/>
-      <c r="AIK42" s="14"/>
-      <c r="AIL42" s="14"/>
-      <c r="AIM42" s="14"/>
-      <c r="AIN42" s="14"/>
-      <c r="AIO42" s="14"/>
-      <c r="AIP42" s="14"/>
-      <c r="AIQ42" s="14"/>
-      <c r="AIR42" s="14"/>
-      <c r="AIS42" s="14"/>
-      <c r="AIT42" s="14"/>
-      <c r="AIU42" s="14"/>
-      <c r="AIV42" s="14"/>
-      <c r="AIW42" s="14"/>
-      <c r="AIX42" s="14"/>
-      <c r="AIY42" s="14"/>
-      <c r="AIZ42" s="14"/>
-      <c r="AJA42" s="14"/>
-      <c r="AJB42" s="14"/>
-      <c r="AJC42" s="14"/>
-      <c r="AJD42" s="14"/>
-      <c r="AJE42" s="14"/>
-      <c r="AJF42" s="14"/>
-      <c r="AJG42" s="14"/>
-      <c r="AJH42" s="14"/>
-      <c r="AJI42" s="14"/>
-      <c r="AJJ42" s="14"/>
-      <c r="AJK42" s="14"/>
-      <c r="AJL42" s="14"/>
-      <c r="AJM42" s="14"/>
-      <c r="AJN42" s="14"/>
-      <c r="AJO42" s="14"/>
-      <c r="AJP42" s="14"/>
-      <c r="AJQ42" s="14"/>
-      <c r="AJR42" s="14"/>
-      <c r="AJS42" s="14"/>
-      <c r="AJT42" s="14"/>
-      <c r="AJU42" s="14"/>
-      <c r="AJV42" s="14"/>
-      <c r="AJW42" s="14"/>
-      <c r="AJX42" s="14"/>
-      <c r="AJY42" s="14"/>
-      <c r="AJZ42" s="14"/>
-      <c r="AKA42" s="14"/>
-      <c r="AKB42" s="14"/>
-      <c r="AKC42" s="14"/>
-      <c r="AKD42" s="14"/>
-      <c r="AKE42" s="14"/>
-      <c r="AKF42" s="14"/>
-      <c r="AKG42" s="14"/>
-      <c r="AKH42" s="14"/>
-      <c r="AKI42" s="14"/>
-      <c r="AKJ42" s="14"/>
-      <c r="AKK42" s="14"/>
-      <c r="AKL42" s="14"/>
-      <c r="AKM42" s="14"/>
-      <c r="AKN42" s="14"/>
-      <c r="AKO42" s="14"/>
-      <c r="AKP42" s="14"/>
-      <c r="AKQ42" s="14"/>
-      <c r="AKR42" s="14"/>
-      <c r="AKS42" s="14"/>
-      <c r="AKT42" s="14"/>
-      <c r="AKU42" s="14"/>
-      <c r="AKV42" s="14"/>
-      <c r="AKW42" s="14"/>
-      <c r="AKX42" s="14"/>
-      <c r="AKY42" s="14"/>
-      <c r="AKZ42" s="14"/>
-      <c r="ALA42" s="14"/>
-      <c r="ALB42" s="14"/>
-      <c r="ALC42" s="14"/>
-      <c r="ALD42" s="14"/>
-      <c r="ALE42" s="14"/>
-      <c r="ALF42" s="14"/>
-      <c r="ALG42" s="14"/>
-      <c r="ALH42" s="14"/>
-      <c r="ALI42" s="14"/>
-      <c r="ALJ42" s="14"/>
-      <c r="ALK42" s="14"/>
-      <c r="ALL42" s="14"/>
-      <c r="ALM42" s="14"/>
-      <c r="ALN42" s="14"/>
-      <c r="ALO42" s="14"/>
-      <c r="ALP42" s="14"/>
-      <c r="ALQ42" s="14"/>
-      <c r="ALR42" s="14"/>
-      <c r="ALS42" s="14"/>
-      <c r="ALT42" s="14"/>
-      <c r="ALU42" s="14"/>
-      <c r="ALV42" s="14"/>
-      <c r="ALW42" s="14"/>
-      <c r="ALX42" s="14"/>
-      <c r="ALY42" s="14"/>
-      <c r="ALZ42" s="14"/>
-      <c r="AMA42" s="14"/>
-      <c r="AMB42" s="14"/>
-      <c r="AMC42" s="14"/>
-      <c r="AMD42" s="14"/>
-      <c r="AME42" s="14"/>
-      <c r="AMF42" s="14"/>
-      <c r="AMG42" s="14"/>
-      <c r="AMH42" s="14"/>
-      <c r="AMI42" s="14"/>
-      <c r="AMJ42" s="14"/>
-    </row>
-    <row r="43" spans="1:1024" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>7</v>
-      </c>
+      <c r="H42" s="9"/>
+    </row>
+    <row r="43" spans="1:1024" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="8">
+        <v>3</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="10"/>
       <c r="I43" s="14"/>
       <c r="J43" s="14"/>
       <c r="K43" s="14"/>
@@ -13807,56 +12844,1098 @@
       <c r="AMI43" s="14"/>
       <c r="AMJ43" s="14"/>
     </row>
-    <row r="44" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E44" s="2">
-        <v>340</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H44" s="10"/>
+    <row r="44" spans="1:1024" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H44" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="14"/>
+      <c r="L44" s="14"/>
+      <c r="M44" s="14"/>
+      <c r="N44" s="14"/>
+      <c r="O44" s="14"/>
+      <c r="P44" s="14"/>
+      <c r="Q44" s="14"/>
+      <c r="R44" s="14"/>
+      <c r="S44" s="14"/>
+      <c r="T44" s="14"/>
+      <c r="U44" s="14"/>
+      <c r="V44" s="14"/>
+      <c r="W44" s="14"/>
+      <c r="X44" s="14"/>
+      <c r="Y44" s="14"/>
+      <c r="Z44" s="14"/>
+      <c r="AA44" s="14"/>
+      <c r="AB44" s="14"/>
+      <c r="AC44" s="14"/>
+      <c r="AD44" s="14"/>
+      <c r="AE44" s="14"/>
+      <c r="AF44" s="14"/>
+      <c r="AG44" s="14"/>
+      <c r="AH44" s="14"/>
+      <c r="AI44" s="14"/>
+      <c r="AJ44" s="14"/>
+      <c r="AK44" s="14"/>
+      <c r="AL44" s="14"/>
+      <c r="AM44" s="14"/>
+      <c r="AN44" s="14"/>
+      <c r="AO44" s="14"/>
+      <c r="AP44" s="14"/>
+      <c r="AQ44" s="14"/>
+      <c r="AR44" s="14"/>
+      <c r="AS44" s="14"/>
+      <c r="AT44" s="14"/>
+      <c r="AU44" s="14"/>
+      <c r="AV44" s="14"/>
+      <c r="AW44" s="14"/>
+      <c r="AX44" s="14"/>
+      <c r="AY44" s="14"/>
+      <c r="AZ44" s="14"/>
+      <c r="BA44" s="14"/>
+      <c r="BB44" s="14"/>
+      <c r="BC44" s="14"/>
+      <c r="BD44" s="14"/>
+      <c r="BE44" s="14"/>
+      <c r="BF44" s="14"/>
+      <c r="BG44" s="14"/>
+      <c r="BH44" s="14"/>
+      <c r="BI44" s="14"/>
+      <c r="BJ44" s="14"/>
+      <c r="BK44" s="14"/>
+      <c r="BL44" s="14"/>
+      <c r="BM44" s="14"/>
+      <c r="BN44" s="14"/>
+      <c r="BO44" s="14"/>
+      <c r="BP44" s="14"/>
+      <c r="BQ44" s="14"/>
+      <c r="BR44" s="14"/>
+      <c r="BS44" s="14"/>
+      <c r="BT44" s="14"/>
+      <c r="BU44" s="14"/>
+      <c r="BV44" s="14"/>
+      <c r="BW44" s="14"/>
+      <c r="BX44" s="14"/>
+      <c r="BY44" s="14"/>
+      <c r="BZ44" s="14"/>
+      <c r="CA44" s="14"/>
+      <c r="CB44" s="14"/>
+      <c r="CC44" s="14"/>
+      <c r="CD44" s="14"/>
+      <c r="CE44" s="14"/>
+      <c r="CF44" s="14"/>
+      <c r="CG44" s="14"/>
+      <c r="CH44" s="14"/>
+      <c r="CI44" s="14"/>
+      <c r="CJ44" s="14"/>
+      <c r="CK44" s="14"/>
+      <c r="CL44" s="14"/>
+      <c r="CM44" s="14"/>
+      <c r="CN44" s="14"/>
+      <c r="CO44" s="14"/>
+      <c r="CP44" s="14"/>
+      <c r="CQ44" s="14"/>
+      <c r="CR44" s="14"/>
+      <c r="CS44" s="14"/>
+      <c r="CT44" s="14"/>
+      <c r="CU44" s="14"/>
+      <c r="CV44" s="14"/>
+      <c r="CW44" s="14"/>
+      <c r="CX44" s="14"/>
+      <c r="CY44" s="14"/>
+      <c r="CZ44" s="14"/>
+      <c r="DA44" s="14"/>
+      <c r="DB44" s="14"/>
+      <c r="DC44" s="14"/>
+      <c r="DD44" s="14"/>
+      <c r="DE44" s="14"/>
+      <c r="DF44" s="14"/>
+      <c r="DG44" s="14"/>
+      <c r="DH44" s="14"/>
+      <c r="DI44" s="14"/>
+      <c r="DJ44" s="14"/>
+      <c r="DK44" s="14"/>
+      <c r="DL44" s="14"/>
+      <c r="DM44" s="14"/>
+      <c r="DN44" s="14"/>
+      <c r="DO44" s="14"/>
+      <c r="DP44" s="14"/>
+      <c r="DQ44" s="14"/>
+      <c r="DR44" s="14"/>
+      <c r="DS44" s="14"/>
+      <c r="DT44" s="14"/>
+      <c r="DU44" s="14"/>
+      <c r="DV44" s="14"/>
+      <c r="DW44" s="14"/>
+      <c r="DX44" s="14"/>
+      <c r="DY44" s="14"/>
+      <c r="DZ44" s="14"/>
+      <c r="EA44" s="14"/>
+      <c r="EB44" s="14"/>
+      <c r="EC44" s="14"/>
+      <c r="ED44" s="14"/>
+      <c r="EE44" s="14"/>
+      <c r="EF44" s="14"/>
+      <c r="EG44" s="14"/>
+      <c r="EH44" s="14"/>
+      <c r="EI44" s="14"/>
+      <c r="EJ44" s="14"/>
+      <c r="EK44" s="14"/>
+      <c r="EL44" s="14"/>
+      <c r="EM44" s="14"/>
+      <c r="EN44" s="14"/>
+      <c r="EO44" s="14"/>
+      <c r="EP44" s="14"/>
+      <c r="EQ44" s="14"/>
+      <c r="ER44" s="14"/>
+      <c r="ES44" s="14"/>
+      <c r="ET44" s="14"/>
+      <c r="EU44" s="14"/>
+      <c r="EV44" s="14"/>
+      <c r="EW44" s="14"/>
+      <c r="EX44" s="14"/>
+      <c r="EY44" s="14"/>
+      <c r="EZ44" s="14"/>
+      <c r="FA44" s="14"/>
+      <c r="FB44" s="14"/>
+      <c r="FC44" s="14"/>
+      <c r="FD44" s="14"/>
+      <c r="FE44" s="14"/>
+      <c r="FF44" s="14"/>
+      <c r="FG44" s="14"/>
+      <c r="FH44" s="14"/>
+      <c r="FI44" s="14"/>
+      <c r="FJ44" s="14"/>
+      <c r="FK44" s="14"/>
+      <c r="FL44" s="14"/>
+      <c r="FM44" s="14"/>
+      <c r="FN44" s="14"/>
+      <c r="FO44" s="14"/>
+      <c r="FP44" s="14"/>
+      <c r="FQ44" s="14"/>
+      <c r="FR44" s="14"/>
+      <c r="FS44" s="14"/>
+      <c r="FT44" s="14"/>
+      <c r="FU44" s="14"/>
+      <c r="FV44" s="14"/>
+      <c r="FW44" s="14"/>
+      <c r="FX44" s="14"/>
+      <c r="FY44" s="14"/>
+      <c r="FZ44" s="14"/>
+      <c r="GA44" s="14"/>
+      <c r="GB44" s="14"/>
+      <c r="GC44" s="14"/>
+      <c r="GD44" s="14"/>
+      <c r="GE44" s="14"/>
+      <c r="GF44" s="14"/>
+      <c r="GG44" s="14"/>
+      <c r="GH44" s="14"/>
+      <c r="GI44" s="14"/>
+      <c r="GJ44" s="14"/>
+      <c r="GK44" s="14"/>
+      <c r="GL44" s="14"/>
+      <c r="GM44" s="14"/>
+      <c r="GN44" s="14"/>
+      <c r="GO44" s="14"/>
+      <c r="GP44" s="14"/>
+      <c r="GQ44" s="14"/>
+      <c r="GR44" s="14"/>
+      <c r="GS44" s="14"/>
+      <c r="GT44" s="14"/>
+      <c r="GU44" s="14"/>
+      <c r="GV44" s="14"/>
+      <c r="GW44" s="14"/>
+      <c r="GX44" s="14"/>
+      <c r="GY44" s="14"/>
+      <c r="GZ44" s="14"/>
+      <c r="HA44" s="14"/>
+      <c r="HB44" s="14"/>
+      <c r="HC44" s="14"/>
+      <c r="HD44" s="14"/>
+      <c r="HE44" s="14"/>
+      <c r="HF44" s="14"/>
+      <c r="HG44" s="14"/>
+      <c r="HH44" s="14"/>
+      <c r="HI44" s="14"/>
+      <c r="HJ44" s="14"/>
+      <c r="HK44" s="14"/>
+      <c r="HL44" s="14"/>
+      <c r="HM44" s="14"/>
+      <c r="HN44" s="14"/>
+      <c r="HO44" s="14"/>
+      <c r="HP44" s="14"/>
+      <c r="HQ44" s="14"/>
+      <c r="HR44" s="14"/>
+      <c r="HS44" s="14"/>
+      <c r="HT44" s="14"/>
+      <c r="HU44" s="14"/>
+      <c r="HV44" s="14"/>
+      <c r="HW44" s="14"/>
+      <c r="HX44" s="14"/>
+      <c r="HY44" s="14"/>
+      <c r="HZ44" s="14"/>
+      <c r="IA44" s="14"/>
+      <c r="IB44" s="14"/>
+      <c r="IC44" s="14"/>
+      <c r="ID44" s="14"/>
+      <c r="IE44" s="14"/>
+      <c r="IF44" s="14"/>
+      <c r="IG44" s="14"/>
+      <c r="IH44" s="14"/>
+      <c r="II44" s="14"/>
+      <c r="IJ44" s="14"/>
+      <c r="IK44" s="14"/>
+      <c r="IL44" s="14"/>
+      <c r="IM44" s="14"/>
+      <c r="IN44" s="14"/>
+      <c r="IO44" s="14"/>
+      <c r="IP44" s="14"/>
+      <c r="IQ44" s="14"/>
+      <c r="IR44" s="14"/>
+      <c r="IS44" s="14"/>
+      <c r="IT44" s="14"/>
+      <c r="IU44" s="14"/>
+      <c r="IV44" s="14"/>
+      <c r="IW44" s="14"/>
+      <c r="IX44" s="14"/>
+      <c r="IY44" s="14"/>
+      <c r="IZ44" s="14"/>
+      <c r="JA44" s="14"/>
+      <c r="JB44" s="14"/>
+      <c r="JC44" s="14"/>
+      <c r="JD44" s="14"/>
+      <c r="JE44" s="14"/>
+      <c r="JF44" s="14"/>
+      <c r="JG44" s="14"/>
+      <c r="JH44" s="14"/>
+      <c r="JI44" s="14"/>
+      <c r="JJ44" s="14"/>
+      <c r="JK44" s="14"/>
+      <c r="JL44" s="14"/>
+      <c r="JM44" s="14"/>
+      <c r="JN44" s="14"/>
+      <c r="JO44" s="14"/>
+      <c r="JP44" s="14"/>
+      <c r="JQ44" s="14"/>
+      <c r="JR44" s="14"/>
+      <c r="JS44" s="14"/>
+      <c r="JT44" s="14"/>
+      <c r="JU44" s="14"/>
+      <c r="JV44" s="14"/>
+      <c r="JW44" s="14"/>
+      <c r="JX44" s="14"/>
+      <c r="JY44" s="14"/>
+      <c r="JZ44" s="14"/>
+      <c r="KA44" s="14"/>
+      <c r="KB44" s="14"/>
+      <c r="KC44" s="14"/>
+      <c r="KD44" s="14"/>
+      <c r="KE44" s="14"/>
+      <c r="KF44" s="14"/>
+      <c r="KG44" s="14"/>
+      <c r="KH44" s="14"/>
+      <c r="KI44" s="14"/>
+      <c r="KJ44" s="14"/>
+      <c r="KK44" s="14"/>
+      <c r="KL44" s="14"/>
+      <c r="KM44" s="14"/>
+      <c r="KN44" s="14"/>
+      <c r="KO44" s="14"/>
+      <c r="KP44" s="14"/>
+      <c r="KQ44" s="14"/>
+      <c r="KR44" s="14"/>
+      <c r="KS44" s="14"/>
+      <c r="KT44" s="14"/>
+      <c r="KU44" s="14"/>
+      <c r="KV44" s="14"/>
+      <c r="KW44" s="14"/>
+      <c r="KX44" s="14"/>
+      <c r="KY44" s="14"/>
+      <c r="KZ44" s="14"/>
+      <c r="LA44" s="14"/>
+      <c r="LB44" s="14"/>
+      <c r="LC44" s="14"/>
+      <c r="LD44" s="14"/>
+      <c r="LE44" s="14"/>
+      <c r="LF44" s="14"/>
+      <c r="LG44" s="14"/>
+      <c r="LH44" s="14"/>
+      <c r="LI44" s="14"/>
+      <c r="LJ44" s="14"/>
+      <c r="LK44" s="14"/>
+      <c r="LL44" s="14"/>
+      <c r="LM44" s="14"/>
+      <c r="LN44" s="14"/>
+      <c r="LO44" s="14"/>
+      <c r="LP44" s="14"/>
+      <c r="LQ44" s="14"/>
+      <c r="LR44" s="14"/>
+      <c r="LS44" s="14"/>
+      <c r="LT44" s="14"/>
+      <c r="LU44" s="14"/>
+      <c r="LV44" s="14"/>
+      <c r="LW44" s="14"/>
+      <c r="LX44" s="14"/>
+      <c r="LY44" s="14"/>
+      <c r="LZ44" s="14"/>
+      <c r="MA44" s="14"/>
+      <c r="MB44" s="14"/>
+      <c r="MC44" s="14"/>
+      <c r="MD44" s="14"/>
+      <c r="ME44" s="14"/>
+      <c r="MF44" s="14"/>
+      <c r="MG44" s="14"/>
+      <c r="MH44" s="14"/>
+      <c r="MI44" s="14"/>
+      <c r="MJ44" s="14"/>
+      <c r="MK44" s="14"/>
+      <c r="ML44" s="14"/>
+      <c r="MM44" s="14"/>
+      <c r="MN44" s="14"/>
+      <c r="MO44" s="14"/>
+      <c r="MP44" s="14"/>
+      <c r="MQ44" s="14"/>
+      <c r="MR44" s="14"/>
+      <c r="MS44" s="14"/>
+      <c r="MT44" s="14"/>
+      <c r="MU44" s="14"/>
+      <c r="MV44" s="14"/>
+      <c r="MW44" s="14"/>
+      <c r="MX44" s="14"/>
+      <c r="MY44" s="14"/>
+      <c r="MZ44" s="14"/>
+      <c r="NA44" s="14"/>
+      <c r="NB44" s="14"/>
+      <c r="NC44" s="14"/>
+      <c r="ND44" s="14"/>
+      <c r="NE44" s="14"/>
+      <c r="NF44" s="14"/>
+      <c r="NG44" s="14"/>
+      <c r="NH44" s="14"/>
+      <c r="NI44" s="14"/>
+      <c r="NJ44" s="14"/>
+      <c r="NK44" s="14"/>
+      <c r="NL44" s="14"/>
+      <c r="NM44" s="14"/>
+      <c r="NN44" s="14"/>
+      <c r="NO44" s="14"/>
+      <c r="NP44" s="14"/>
+      <c r="NQ44" s="14"/>
+      <c r="NR44" s="14"/>
+      <c r="NS44" s="14"/>
+      <c r="NT44" s="14"/>
+      <c r="NU44" s="14"/>
+      <c r="NV44" s="14"/>
+      <c r="NW44" s="14"/>
+      <c r="NX44" s="14"/>
+      <c r="NY44" s="14"/>
+      <c r="NZ44" s="14"/>
+      <c r="OA44" s="14"/>
+      <c r="OB44" s="14"/>
+      <c r="OC44" s="14"/>
+      <c r="OD44" s="14"/>
+      <c r="OE44" s="14"/>
+      <c r="OF44" s="14"/>
+      <c r="OG44" s="14"/>
+      <c r="OH44" s="14"/>
+      <c r="OI44" s="14"/>
+      <c r="OJ44" s="14"/>
+      <c r="OK44" s="14"/>
+      <c r="OL44" s="14"/>
+      <c r="OM44" s="14"/>
+      <c r="ON44" s="14"/>
+      <c r="OO44" s="14"/>
+      <c r="OP44" s="14"/>
+      <c r="OQ44" s="14"/>
+      <c r="OR44" s="14"/>
+      <c r="OS44" s="14"/>
+      <c r="OT44" s="14"/>
+      <c r="OU44" s="14"/>
+      <c r="OV44" s="14"/>
+      <c r="OW44" s="14"/>
+      <c r="OX44" s="14"/>
+      <c r="OY44" s="14"/>
+      <c r="OZ44" s="14"/>
+      <c r="PA44" s="14"/>
+      <c r="PB44" s="14"/>
+      <c r="PC44" s="14"/>
+      <c r="PD44" s="14"/>
+      <c r="PE44" s="14"/>
+      <c r="PF44" s="14"/>
+      <c r="PG44" s="14"/>
+      <c r="PH44" s="14"/>
+      <c r="PI44" s="14"/>
+      <c r="PJ44" s="14"/>
+      <c r="PK44" s="14"/>
+      <c r="PL44" s="14"/>
+      <c r="PM44" s="14"/>
+      <c r="PN44" s="14"/>
+      <c r="PO44" s="14"/>
+      <c r="PP44" s="14"/>
+      <c r="PQ44" s="14"/>
+      <c r="PR44" s="14"/>
+      <c r="PS44" s="14"/>
+      <c r="PT44" s="14"/>
+      <c r="PU44" s="14"/>
+      <c r="PV44" s="14"/>
+      <c r="PW44" s="14"/>
+      <c r="PX44" s="14"/>
+      <c r="PY44" s="14"/>
+      <c r="PZ44" s="14"/>
+      <c r="QA44" s="14"/>
+      <c r="QB44" s="14"/>
+      <c r="QC44" s="14"/>
+      <c r="QD44" s="14"/>
+      <c r="QE44" s="14"/>
+      <c r="QF44" s="14"/>
+      <c r="QG44" s="14"/>
+      <c r="QH44" s="14"/>
+      <c r="QI44" s="14"/>
+      <c r="QJ44" s="14"/>
+      <c r="QK44" s="14"/>
+      <c r="QL44" s="14"/>
+      <c r="QM44" s="14"/>
+      <c r="QN44" s="14"/>
+      <c r="QO44" s="14"/>
+      <c r="QP44" s="14"/>
+      <c r="QQ44" s="14"/>
+      <c r="QR44" s="14"/>
+      <c r="QS44" s="14"/>
+      <c r="QT44" s="14"/>
+      <c r="QU44" s="14"/>
+      <c r="QV44" s="14"/>
+      <c r="QW44" s="14"/>
+      <c r="QX44" s="14"/>
+      <c r="QY44" s="14"/>
+      <c r="QZ44" s="14"/>
+      <c r="RA44" s="14"/>
+      <c r="RB44" s="14"/>
+      <c r="RC44" s="14"/>
+      <c r="RD44" s="14"/>
+      <c r="RE44" s="14"/>
+      <c r="RF44" s="14"/>
+      <c r="RG44" s="14"/>
+      <c r="RH44" s="14"/>
+      <c r="RI44" s="14"/>
+      <c r="RJ44" s="14"/>
+      <c r="RK44" s="14"/>
+      <c r="RL44" s="14"/>
+      <c r="RM44" s="14"/>
+      <c r="RN44" s="14"/>
+      <c r="RO44" s="14"/>
+      <c r="RP44" s="14"/>
+      <c r="RQ44" s="14"/>
+      <c r="RR44" s="14"/>
+      <c r="RS44" s="14"/>
+      <c r="RT44" s="14"/>
+      <c r="RU44" s="14"/>
+      <c r="RV44" s="14"/>
+      <c r="RW44" s="14"/>
+      <c r="RX44" s="14"/>
+      <c r="RY44" s="14"/>
+      <c r="RZ44" s="14"/>
+      <c r="SA44" s="14"/>
+      <c r="SB44" s="14"/>
+      <c r="SC44" s="14"/>
+      <c r="SD44" s="14"/>
+      <c r="SE44" s="14"/>
+      <c r="SF44" s="14"/>
+      <c r="SG44" s="14"/>
+      <c r="SH44" s="14"/>
+      <c r="SI44" s="14"/>
+      <c r="SJ44" s="14"/>
+      <c r="SK44" s="14"/>
+      <c r="SL44" s="14"/>
+      <c r="SM44" s="14"/>
+      <c r="SN44" s="14"/>
+      <c r="SO44" s="14"/>
+      <c r="SP44" s="14"/>
+      <c r="SQ44" s="14"/>
+      <c r="SR44" s="14"/>
+      <c r="SS44" s="14"/>
+      <c r="ST44" s="14"/>
+      <c r="SU44" s="14"/>
+      <c r="SV44" s="14"/>
+      <c r="SW44" s="14"/>
+      <c r="SX44" s="14"/>
+      <c r="SY44" s="14"/>
+      <c r="SZ44" s="14"/>
+      <c r="TA44" s="14"/>
+      <c r="TB44" s="14"/>
+      <c r="TC44" s="14"/>
+      <c r="TD44" s="14"/>
+      <c r="TE44" s="14"/>
+      <c r="TF44" s="14"/>
+      <c r="TG44" s="14"/>
+      <c r="TH44" s="14"/>
+      <c r="TI44" s="14"/>
+      <c r="TJ44" s="14"/>
+      <c r="TK44" s="14"/>
+      <c r="TL44" s="14"/>
+      <c r="TM44" s="14"/>
+      <c r="TN44" s="14"/>
+      <c r="TO44" s="14"/>
+      <c r="TP44" s="14"/>
+      <c r="TQ44" s="14"/>
+      <c r="TR44" s="14"/>
+      <c r="TS44" s="14"/>
+      <c r="TT44" s="14"/>
+      <c r="TU44" s="14"/>
+      <c r="TV44" s="14"/>
+      <c r="TW44" s="14"/>
+      <c r="TX44" s="14"/>
+      <c r="TY44" s="14"/>
+      <c r="TZ44" s="14"/>
+      <c r="UA44" s="14"/>
+      <c r="UB44" s="14"/>
+      <c r="UC44" s="14"/>
+      <c r="UD44" s="14"/>
+      <c r="UE44" s="14"/>
+      <c r="UF44" s="14"/>
+      <c r="UG44" s="14"/>
+      <c r="UH44" s="14"/>
+      <c r="UI44" s="14"/>
+      <c r="UJ44" s="14"/>
+      <c r="UK44" s="14"/>
+      <c r="UL44" s="14"/>
+      <c r="UM44" s="14"/>
+      <c r="UN44" s="14"/>
+      <c r="UO44" s="14"/>
+      <c r="UP44" s="14"/>
+      <c r="UQ44" s="14"/>
+      <c r="UR44" s="14"/>
+      <c r="US44" s="14"/>
+      <c r="UT44" s="14"/>
+      <c r="UU44" s="14"/>
+      <c r="UV44" s="14"/>
+      <c r="UW44" s="14"/>
+      <c r="UX44" s="14"/>
+      <c r="UY44" s="14"/>
+      <c r="UZ44" s="14"/>
+      <c r="VA44" s="14"/>
+      <c r="VB44" s="14"/>
+      <c r="VC44" s="14"/>
+      <c r="VD44" s="14"/>
+      <c r="VE44" s="14"/>
+      <c r="VF44" s="14"/>
+      <c r="VG44" s="14"/>
+      <c r="VH44" s="14"/>
+      <c r="VI44" s="14"/>
+      <c r="VJ44" s="14"/>
+      <c r="VK44" s="14"/>
+      <c r="VL44" s="14"/>
+      <c r="VM44" s="14"/>
+      <c r="VN44" s="14"/>
+      <c r="VO44" s="14"/>
+      <c r="VP44" s="14"/>
+      <c r="VQ44" s="14"/>
+      <c r="VR44" s="14"/>
+      <c r="VS44" s="14"/>
+      <c r="VT44" s="14"/>
+      <c r="VU44" s="14"/>
+      <c r="VV44" s="14"/>
+      <c r="VW44" s="14"/>
+      <c r="VX44" s="14"/>
+      <c r="VY44" s="14"/>
+      <c r="VZ44" s="14"/>
+      <c r="WA44" s="14"/>
+      <c r="WB44" s="14"/>
+      <c r="WC44" s="14"/>
+      <c r="WD44" s="14"/>
+      <c r="WE44" s="14"/>
+      <c r="WF44" s="14"/>
+      <c r="WG44" s="14"/>
+      <c r="WH44" s="14"/>
+      <c r="WI44" s="14"/>
+      <c r="WJ44" s="14"/>
+      <c r="WK44" s="14"/>
+      <c r="WL44" s="14"/>
+      <c r="WM44" s="14"/>
+      <c r="WN44" s="14"/>
+      <c r="WO44" s="14"/>
+      <c r="WP44" s="14"/>
+      <c r="WQ44" s="14"/>
+      <c r="WR44" s="14"/>
+      <c r="WS44" s="14"/>
+      <c r="WT44" s="14"/>
+      <c r="WU44" s="14"/>
+      <c r="WV44" s="14"/>
+      <c r="WW44" s="14"/>
+      <c r="WX44" s="14"/>
+      <c r="WY44" s="14"/>
+      <c r="WZ44" s="14"/>
+      <c r="XA44" s="14"/>
+      <c r="XB44" s="14"/>
+      <c r="XC44" s="14"/>
+      <c r="XD44" s="14"/>
+      <c r="XE44" s="14"/>
+      <c r="XF44" s="14"/>
+      <c r="XG44" s="14"/>
+      <c r="XH44" s="14"/>
+      <c r="XI44" s="14"/>
+      <c r="XJ44" s="14"/>
+      <c r="XK44" s="14"/>
+      <c r="XL44" s="14"/>
+      <c r="XM44" s="14"/>
+      <c r="XN44" s="14"/>
+      <c r="XO44" s="14"/>
+      <c r="XP44" s="14"/>
+      <c r="XQ44" s="14"/>
+      <c r="XR44" s="14"/>
+      <c r="XS44" s="14"/>
+      <c r="XT44" s="14"/>
+      <c r="XU44" s="14"/>
+      <c r="XV44" s="14"/>
+      <c r="XW44" s="14"/>
+      <c r="XX44" s="14"/>
+      <c r="XY44" s="14"/>
+      <c r="XZ44" s="14"/>
+      <c r="YA44" s="14"/>
+      <c r="YB44" s="14"/>
+      <c r="YC44" s="14"/>
+      <c r="YD44" s="14"/>
+      <c r="YE44" s="14"/>
+      <c r="YF44" s="14"/>
+      <c r="YG44" s="14"/>
+      <c r="YH44" s="14"/>
+      <c r="YI44" s="14"/>
+      <c r="YJ44" s="14"/>
+      <c r="YK44" s="14"/>
+      <c r="YL44" s="14"/>
+      <c r="YM44" s="14"/>
+      <c r="YN44" s="14"/>
+      <c r="YO44" s="14"/>
+      <c r="YP44" s="14"/>
+      <c r="YQ44" s="14"/>
+      <c r="YR44" s="14"/>
+      <c r="YS44" s="14"/>
+      <c r="YT44" s="14"/>
+      <c r="YU44" s="14"/>
+      <c r="YV44" s="14"/>
+      <c r="YW44" s="14"/>
+      <c r="YX44" s="14"/>
+      <c r="YY44" s="14"/>
+      <c r="YZ44" s="14"/>
+      <c r="ZA44" s="14"/>
+      <c r="ZB44" s="14"/>
+      <c r="ZC44" s="14"/>
+      <c r="ZD44" s="14"/>
+      <c r="ZE44" s="14"/>
+      <c r="ZF44" s="14"/>
+      <c r="ZG44" s="14"/>
+      <c r="ZH44" s="14"/>
+      <c r="ZI44" s="14"/>
+      <c r="ZJ44" s="14"/>
+      <c r="ZK44" s="14"/>
+      <c r="ZL44" s="14"/>
+      <c r="ZM44" s="14"/>
+      <c r="ZN44" s="14"/>
+      <c r="ZO44" s="14"/>
+      <c r="ZP44" s="14"/>
+      <c r="ZQ44" s="14"/>
+      <c r="ZR44" s="14"/>
+      <c r="ZS44" s="14"/>
+      <c r="ZT44" s="14"/>
+      <c r="ZU44" s="14"/>
+      <c r="ZV44" s="14"/>
+      <c r="ZW44" s="14"/>
+      <c r="ZX44" s="14"/>
+      <c r="ZY44" s="14"/>
+      <c r="ZZ44" s="14"/>
+      <c r="AAA44" s="14"/>
+      <c r="AAB44" s="14"/>
+      <c r="AAC44" s="14"/>
+      <c r="AAD44" s="14"/>
+      <c r="AAE44" s="14"/>
+      <c r="AAF44" s="14"/>
+      <c r="AAG44" s="14"/>
+      <c r="AAH44" s="14"/>
+      <c r="AAI44" s="14"/>
+      <c r="AAJ44" s="14"/>
+      <c r="AAK44" s="14"/>
+      <c r="AAL44" s="14"/>
+      <c r="AAM44" s="14"/>
+      <c r="AAN44" s="14"/>
+      <c r="AAO44" s="14"/>
+      <c r="AAP44" s="14"/>
+      <c r="AAQ44" s="14"/>
+      <c r="AAR44" s="14"/>
+      <c r="AAS44" s="14"/>
+      <c r="AAT44" s="14"/>
+      <c r="AAU44" s="14"/>
+      <c r="AAV44" s="14"/>
+      <c r="AAW44" s="14"/>
+      <c r="AAX44" s="14"/>
+      <c r="AAY44" s="14"/>
+      <c r="AAZ44" s="14"/>
+      <c r="ABA44" s="14"/>
+      <c r="ABB44" s="14"/>
+      <c r="ABC44" s="14"/>
+      <c r="ABD44" s="14"/>
+      <c r="ABE44" s="14"/>
+      <c r="ABF44" s="14"/>
+      <c r="ABG44" s="14"/>
+      <c r="ABH44" s="14"/>
+      <c r="ABI44" s="14"/>
+      <c r="ABJ44" s="14"/>
+      <c r="ABK44" s="14"/>
+      <c r="ABL44" s="14"/>
+      <c r="ABM44" s="14"/>
+      <c r="ABN44" s="14"/>
+      <c r="ABO44" s="14"/>
+      <c r="ABP44" s="14"/>
+      <c r="ABQ44" s="14"/>
+      <c r="ABR44" s="14"/>
+      <c r="ABS44" s="14"/>
+      <c r="ABT44" s="14"/>
+      <c r="ABU44" s="14"/>
+      <c r="ABV44" s="14"/>
+      <c r="ABW44" s="14"/>
+      <c r="ABX44" s="14"/>
+      <c r="ABY44" s="14"/>
+      <c r="ABZ44" s="14"/>
+      <c r="ACA44" s="14"/>
+      <c r="ACB44" s="14"/>
+      <c r="ACC44" s="14"/>
+      <c r="ACD44" s="14"/>
+      <c r="ACE44" s="14"/>
+      <c r="ACF44" s="14"/>
+      <c r="ACG44" s="14"/>
+      <c r="ACH44" s="14"/>
+      <c r="ACI44" s="14"/>
+      <c r="ACJ44" s="14"/>
+      <c r="ACK44" s="14"/>
+      <c r="ACL44" s="14"/>
+      <c r="ACM44" s="14"/>
+      <c r="ACN44" s="14"/>
+      <c r="ACO44" s="14"/>
+      <c r="ACP44" s="14"/>
+      <c r="ACQ44" s="14"/>
+      <c r="ACR44" s="14"/>
+      <c r="ACS44" s="14"/>
+      <c r="ACT44" s="14"/>
+      <c r="ACU44" s="14"/>
+      <c r="ACV44" s="14"/>
+      <c r="ACW44" s="14"/>
+      <c r="ACX44" s="14"/>
+      <c r="ACY44" s="14"/>
+      <c r="ACZ44" s="14"/>
+      <c r="ADA44" s="14"/>
+      <c r="ADB44" s="14"/>
+      <c r="ADC44" s="14"/>
+      <c r="ADD44" s="14"/>
+      <c r="ADE44" s="14"/>
+      <c r="ADF44" s="14"/>
+      <c r="ADG44" s="14"/>
+      <c r="ADH44" s="14"/>
+      <c r="ADI44" s="14"/>
+      <c r="ADJ44" s="14"/>
+      <c r="ADK44" s="14"/>
+      <c r="ADL44" s="14"/>
+      <c r="ADM44" s="14"/>
+      <c r="ADN44" s="14"/>
+      <c r="ADO44" s="14"/>
+      <c r="ADP44" s="14"/>
+      <c r="ADQ44" s="14"/>
+      <c r="ADR44" s="14"/>
+      <c r="ADS44" s="14"/>
+      <c r="ADT44" s="14"/>
+      <c r="ADU44" s="14"/>
+      <c r="ADV44" s="14"/>
+      <c r="ADW44" s="14"/>
+      <c r="ADX44" s="14"/>
+      <c r="ADY44" s="14"/>
+      <c r="ADZ44" s="14"/>
+      <c r="AEA44" s="14"/>
+      <c r="AEB44" s="14"/>
+      <c r="AEC44" s="14"/>
+      <c r="AED44" s="14"/>
+      <c r="AEE44" s="14"/>
+      <c r="AEF44" s="14"/>
+      <c r="AEG44" s="14"/>
+      <c r="AEH44" s="14"/>
+      <c r="AEI44" s="14"/>
+      <c r="AEJ44" s="14"/>
+      <c r="AEK44" s="14"/>
+      <c r="AEL44" s="14"/>
+      <c r="AEM44" s="14"/>
+      <c r="AEN44" s="14"/>
+      <c r="AEO44" s="14"/>
+      <c r="AEP44" s="14"/>
+      <c r="AEQ44" s="14"/>
+      <c r="AER44" s="14"/>
+      <c r="AES44" s="14"/>
+      <c r="AET44" s="14"/>
+      <c r="AEU44" s="14"/>
+      <c r="AEV44" s="14"/>
+      <c r="AEW44" s="14"/>
+      <c r="AEX44" s="14"/>
+      <c r="AEY44" s="14"/>
+      <c r="AEZ44" s="14"/>
+      <c r="AFA44" s="14"/>
+      <c r="AFB44" s="14"/>
+      <c r="AFC44" s="14"/>
+      <c r="AFD44" s="14"/>
+      <c r="AFE44" s="14"/>
+      <c r="AFF44" s="14"/>
+      <c r="AFG44" s="14"/>
+      <c r="AFH44" s="14"/>
+      <c r="AFI44" s="14"/>
+      <c r="AFJ44" s="14"/>
+      <c r="AFK44" s="14"/>
+      <c r="AFL44" s="14"/>
+      <c r="AFM44" s="14"/>
+      <c r="AFN44" s="14"/>
+      <c r="AFO44" s="14"/>
+      <c r="AFP44" s="14"/>
+      <c r="AFQ44" s="14"/>
+      <c r="AFR44" s="14"/>
+      <c r="AFS44" s="14"/>
+      <c r="AFT44" s="14"/>
+      <c r="AFU44" s="14"/>
+      <c r="AFV44" s="14"/>
+      <c r="AFW44" s="14"/>
+      <c r="AFX44" s="14"/>
+      <c r="AFY44" s="14"/>
+      <c r="AFZ44" s="14"/>
+      <c r="AGA44" s="14"/>
+      <c r="AGB44" s="14"/>
+      <c r="AGC44" s="14"/>
+      <c r="AGD44" s="14"/>
+      <c r="AGE44" s="14"/>
+      <c r="AGF44" s="14"/>
+      <c r="AGG44" s="14"/>
+      <c r="AGH44" s="14"/>
+      <c r="AGI44" s="14"/>
+      <c r="AGJ44" s="14"/>
+      <c r="AGK44" s="14"/>
+      <c r="AGL44" s="14"/>
+      <c r="AGM44" s="14"/>
+      <c r="AGN44" s="14"/>
+      <c r="AGO44" s="14"/>
+      <c r="AGP44" s="14"/>
+      <c r="AGQ44" s="14"/>
+      <c r="AGR44" s="14"/>
+      <c r="AGS44" s="14"/>
+      <c r="AGT44" s="14"/>
+      <c r="AGU44" s="14"/>
+      <c r="AGV44" s="14"/>
+      <c r="AGW44" s="14"/>
+      <c r="AGX44" s="14"/>
+      <c r="AGY44" s="14"/>
+      <c r="AGZ44" s="14"/>
+      <c r="AHA44" s="14"/>
+      <c r="AHB44" s="14"/>
+      <c r="AHC44" s="14"/>
+      <c r="AHD44" s="14"/>
+      <c r="AHE44" s="14"/>
+      <c r="AHF44" s="14"/>
+      <c r="AHG44" s="14"/>
+      <c r="AHH44" s="14"/>
+      <c r="AHI44" s="14"/>
+      <c r="AHJ44" s="14"/>
+      <c r="AHK44" s="14"/>
+      <c r="AHL44" s="14"/>
+      <c r="AHM44" s="14"/>
+      <c r="AHN44" s="14"/>
+      <c r="AHO44" s="14"/>
+      <c r="AHP44" s="14"/>
+      <c r="AHQ44" s="14"/>
+      <c r="AHR44" s="14"/>
+      <c r="AHS44" s="14"/>
+      <c r="AHT44" s="14"/>
+      <c r="AHU44" s="14"/>
+      <c r="AHV44" s="14"/>
+      <c r="AHW44" s="14"/>
+      <c r="AHX44" s="14"/>
+      <c r="AHY44" s="14"/>
+      <c r="AHZ44" s="14"/>
+      <c r="AIA44" s="14"/>
+      <c r="AIB44" s="14"/>
+      <c r="AIC44" s="14"/>
+      <c r="AID44" s="14"/>
+      <c r="AIE44" s="14"/>
+      <c r="AIF44" s="14"/>
+      <c r="AIG44" s="14"/>
+      <c r="AIH44" s="14"/>
+      <c r="AII44" s="14"/>
+      <c r="AIJ44" s="14"/>
+      <c r="AIK44" s="14"/>
+      <c r="AIL44" s="14"/>
+      <c r="AIM44" s="14"/>
+      <c r="AIN44" s="14"/>
+      <c r="AIO44" s="14"/>
+      <c r="AIP44" s="14"/>
+      <c r="AIQ44" s="14"/>
+      <c r="AIR44" s="14"/>
+      <c r="AIS44" s="14"/>
+      <c r="AIT44" s="14"/>
+      <c r="AIU44" s="14"/>
+      <c r="AIV44" s="14"/>
+      <c r="AIW44" s="14"/>
+      <c r="AIX44" s="14"/>
+      <c r="AIY44" s="14"/>
+      <c r="AIZ44" s="14"/>
+      <c r="AJA44" s="14"/>
+      <c r="AJB44" s="14"/>
+      <c r="AJC44" s="14"/>
+      <c r="AJD44" s="14"/>
+      <c r="AJE44" s="14"/>
+      <c r="AJF44" s="14"/>
+      <c r="AJG44" s="14"/>
+      <c r="AJH44" s="14"/>
+      <c r="AJI44" s="14"/>
+      <c r="AJJ44" s="14"/>
+      <c r="AJK44" s="14"/>
+      <c r="AJL44" s="14"/>
+      <c r="AJM44" s="14"/>
+      <c r="AJN44" s="14"/>
+      <c r="AJO44" s="14"/>
+      <c r="AJP44" s="14"/>
+      <c r="AJQ44" s="14"/>
+      <c r="AJR44" s="14"/>
+      <c r="AJS44" s="14"/>
+      <c r="AJT44" s="14"/>
+      <c r="AJU44" s="14"/>
+      <c r="AJV44" s="14"/>
+      <c r="AJW44" s="14"/>
+      <c r="AJX44" s="14"/>
+      <c r="AJY44" s="14"/>
+      <c r="AJZ44" s="14"/>
+      <c r="AKA44" s="14"/>
+      <c r="AKB44" s="14"/>
+      <c r="AKC44" s="14"/>
+      <c r="AKD44" s="14"/>
+      <c r="AKE44" s="14"/>
+      <c r="AKF44" s="14"/>
+      <c r="AKG44" s="14"/>
+      <c r="AKH44" s="14"/>
+      <c r="AKI44" s="14"/>
+      <c r="AKJ44" s="14"/>
+      <c r="AKK44" s="14"/>
+      <c r="AKL44" s="14"/>
+      <c r="AKM44" s="14"/>
+      <c r="AKN44" s="14"/>
+      <c r="AKO44" s="14"/>
+      <c r="AKP44" s="14"/>
+      <c r="AKQ44" s="14"/>
+      <c r="AKR44" s="14"/>
+      <c r="AKS44" s="14"/>
+      <c r="AKT44" s="14"/>
+      <c r="AKU44" s="14"/>
+      <c r="AKV44" s="14"/>
+      <c r="AKW44" s="14"/>
+      <c r="AKX44" s="14"/>
+      <c r="AKY44" s="14"/>
+      <c r="AKZ44" s="14"/>
+      <c r="ALA44" s="14"/>
+      <c r="ALB44" s="14"/>
+      <c r="ALC44" s="14"/>
+      <c r="ALD44" s="14"/>
+      <c r="ALE44" s="14"/>
+      <c r="ALF44" s="14"/>
+      <c r="ALG44" s="14"/>
+      <c r="ALH44" s="14"/>
+      <c r="ALI44" s="14"/>
+      <c r="ALJ44" s="14"/>
+      <c r="ALK44" s="14"/>
+      <c r="ALL44" s="14"/>
+      <c r="ALM44" s="14"/>
+      <c r="ALN44" s="14"/>
+      <c r="ALO44" s="14"/>
+      <c r="ALP44" s="14"/>
+      <c r="ALQ44" s="14"/>
+      <c r="ALR44" s="14"/>
+      <c r="ALS44" s="14"/>
+      <c r="ALT44" s="14"/>
+      <c r="ALU44" s="14"/>
+      <c r="ALV44" s="14"/>
+      <c r="ALW44" s="14"/>
+      <c r="ALX44" s="14"/>
+      <c r="ALY44" s="14"/>
+      <c r="ALZ44" s="14"/>
+      <c r="AMA44" s="14"/>
+      <c r="AMB44" s="14"/>
+      <c r="AMC44" s="14"/>
+      <c r="AMD44" s="14"/>
+      <c r="AME44" s="14"/>
+      <c r="AMF44" s="14"/>
+      <c r="AMG44" s="14"/>
+      <c r="AMH44" s="14"/>
+      <c r="AMI44" s="14"/>
+      <c r="AMJ44" s="14"/>
     </row>
     <row r="45" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45" s="2">
+        <v>420</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H45" s="10"/>
+    </row>
+    <row r="46" spans="1:1024" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B46" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C46" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D46" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E46" s="2">
         <v>2</v>
       </c>
-      <c r="F45" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="G45" s="2" t="s">
+      <c r="F46" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H45" s="10"/>
+      <c r="H46" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
@@ -13879,7 +13958,7 @@
     <mergeCell ref="B30:F30"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B25:F25"/>
@@ -13888,6 +13967,7 @@
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B42:F42"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -13900,7 +13980,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:AMJ50"/>
+  <dimension ref="A1:AMJ51"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="12" customWidth="1"/>
@@ -13927,27 +14007,27 @@
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="F2" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
@@ -14014,10 +14094,10 @@
       <c r="D6" s="7"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="26"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
@@ -14026,10 +14106,10 @@
       <c r="D7" s="7"/>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="26"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -14038,10 +14118,10 @@
       <c r="D8" s="7"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="26"/>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
@@ -14050,22 +14130,22 @@
       <c r="D9" s="7"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="26"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -14094,14 +14174,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>83</v>
+        <v>222</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -14140,14 +14220,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>146</v>
-      </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="20"/>
+        <v>198</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="21"/>
       <c r="G15" s="9" t="s">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -14156,7 +14236,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -14208,10 +14288,10 @@
         <v>500</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -14232,10 +14312,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -14256,10 +14336,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -14280,10 +14360,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -14292,7 +14372,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -14304,10 +14384,10 @@
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -14316,22 +14396,22 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="2">
-        <v>0.2</v>
+        <v>91</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -14346,16 +14426,16 @@
         <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="F24" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -14363,13 +14443,13 @@
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="21"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
       <c r="G25" s="1" t="s">
         <v>6</v>
       </c>
@@ -14382,7 +14462,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
@@ -14396,14 +14476,14 @@
         <v>2</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -14412,7 +14492,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
@@ -14426,14 +14506,14 @@
         <v>2</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
       <c r="E29" s="18"/>
       <c r="F29" s="18"/>
       <c r="G29" s="9" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="H29" s="10"/>
     </row>
@@ -14480,10 +14560,10 @@
         <v>500</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -14576,7 +14656,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>68</v>
@@ -14635,13 +14715,13 @@
       <c r="A38" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="21"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
       <c r="G38" s="1" t="s">
         <v>6</v>
       </c>
@@ -14654,7 +14734,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="C39" s="18"/>
       <c r="D39" s="18"/>
@@ -14675,7 +14755,7 @@
       <c r="E40" s="18"/>
       <c r="F40" s="18"/>
       <c r="G40" s="9" t="s">
-        <v>191</v>
+        <v>169</v>
       </c>
       <c r="H40" s="10"/>
     </row>
@@ -14684,116 +14764,106 @@
         <v>3</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="C41" s="18"/>
       <c r="D41" s="18"/>
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
       <c r="G41" s="9" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>3</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>87</v>
+        <v>188</v>
       </c>
       <c r="C42" s="18"/>
       <c r="D42" s="18"/>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
       <c r="G42" s="9"/>
-      <c r="H42" s="10"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
+      <c r="H42" s="9"/>
+    </row>
+    <row r="43" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="8">
+        <v>3</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="10"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B44" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C44" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F43" s="6" t="s">
+      <c r="F44" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H43" s="15" t="s">
+      <c r="H44" s="15" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E44" s="2">
-        <v>500</v>
-      </c>
-      <c r="F44" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H44" s="10"/>
     </row>
     <row r="45" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E45" s="2">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G45" s="13" t="s">
-        <v>64</v>
+        <v>86</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="H45" s="10"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>46</v>
@@ -14805,7 +14875,7 @@
         <v>32</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H46" s="10"/>
     </row>
@@ -14814,7 +14884,7 @@
         <v>29</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>35</v>
@@ -14833,12 +14903,12 @@
       </c>
       <c r="H47" s="10"/>
     </row>
-    <row r="48" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>35</v>
@@ -14850,34 +14920,34 @@
         <v>2</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>68</v>
+        <v>32</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="H48" s="10"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E49" s="2">
         <v>2</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G49" s="13" t="s">
-        <v>79</v>
+        <v>107</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="H49" s="10"/>
     </row>
@@ -14886,7 +14956,7 @@
         <v>40</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>45</v>
@@ -14901,12 +14971,36 @@
         <v>32</v>
       </c>
       <c r="G50" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H50" s="10"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E51" s="2">
+        <v>2</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G51" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="H50" s="10"/>
+      <c r="H51" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
@@ -14928,7 +15022,7 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B43:F43"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B25:F25"/>
@@ -14938,6 +15032,7 @@
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B42:F42"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -14950,7 +15045,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AMJ44"/>
+  <dimension ref="A1:AMJ45"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="12" customWidth="1"/>
@@ -14977,27 +15072,27 @@
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="F2" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="F2" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
@@ -15064,10 +15159,10 @@
       <c r="D6" s="7"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="26"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
@@ -15076,10 +15171,10 @@
       <c r="D7" s="7"/>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="26"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -15088,10 +15183,10 @@
       <c r="D8" s="7"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="26"/>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
@@ -15100,22 +15195,22 @@
       <c r="D9" s="7"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="26"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -15144,14 +15239,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>84</v>
+        <v>212</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -15174,14 +15269,14 @@
         <v>1</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="20"/>
+        <v>200</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="21"/>
       <c r="G14" s="9" t="s">
-        <v>142</v>
+        <v>199</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -15190,7 +15285,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -15242,10 +15337,10 @@
         <v>376</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H17" s="10"/>
     </row>
@@ -15266,10 +15361,10 @@
         <v>12</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -15290,10 +15385,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -15314,10 +15409,10 @@
         <v>35</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -15326,7 +15421,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>30</v>
@@ -15338,10 +15433,10 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -15350,22 +15445,22 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0.3</v>
+        <v>91</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>219</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -15380,16 +15475,16 @@
         <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -15397,13 +15492,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -15416,7 +15511,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
@@ -15437,7 +15532,7 @@
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="H26" s="10"/>
     </row>
@@ -15446,7 +15541,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -15460,14 +15555,14 @@
         <v>2</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -15514,10 +15609,10 @@
         <v>376</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -15562,7 +15657,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>68</v>
@@ -15621,13 +15716,13 @@
       <c r="A35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="21"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
       <c r="G35" s="1" t="s">
         <v>6</v>
       </c>
@@ -15640,7 +15735,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
@@ -15665,103 +15760,93 @@
       </c>
       <c r="H37" s="10"/>
     </row>
-    <row r="38" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>3</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>87</v>
+        <v>189</v>
       </c>
       <c r="C38" s="18"/>
       <c r="D38" s="18"/>
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
       <c r="G38" s="9"/>
-      <c r="H38" s="10"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="6" t="s">
+      <c r="H38" s="9"/>
+    </row>
+    <row r="39" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="8">
+        <v>3</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="10"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B40" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C40" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F40" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H39" s="15" t="s">
+      <c r="H40" s="15" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E40" s="2">
-        <v>376</v>
-      </c>
-      <c r="F40" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H40" s="10"/>
     </row>
     <row r="41" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E41" s="2">
-        <v>2</v>
+        <v>376</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G41" s="13" t="s">
-        <v>64</v>
+        <v>86</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="H41" s="10"/>
     </row>
     <row r="42" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>46</v>
@@ -15770,34 +15855,34 @@
         <v>2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>68</v>
+        <v>32</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="H42" s="10"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E43" s="2">
         <v>2</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="G43" s="13" t="s">
-        <v>79</v>
+        <v>107</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="H43" s="10"/>
     </row>
@@ -15806,7 +15891,7 @@
         <v>40</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>45</v>
@@ -15821,12 +15906,36 @@
         <v>32</v>
       </c>
       <c r="G44" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H44" s="10"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" s="2">
+        <v>2</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G45" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="H44" s="10"/>
+      <c r="H45" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
@@ -15847,7 +15956,7 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B35:F35"/>
     <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B39:F39"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B24:F24"/>
@@ -15856,6 +15965,7 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B38:F38"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -15868,7 +15978,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:AMJ40"/>
+  <dimension ref="A1:AMJ41"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="12" customWidth="1"/>
@@ -15895,27 +16005,27 @@
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="160.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F2" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="F2" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
@@ -15982,10 +16092,10 @@
       <c r="D6" s="7"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="26"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
@@ -15994,10 +16104,10 @@
       <c r="D7" s="7"/>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="26"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -16006,10 +16116,10 @@
       <c r="D8" s="7"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="26"/>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
@@ -16018,22 +16128,22 @@
       <c r="D9" s="7"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="26"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -16062,14 +16172,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -16091,15 +16201,15 @@
       <c r="A14" s="8">
         <v>1</v>
       </c>
-      <c r="B14" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="20"/>
+      <c r="B14" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="21"/>
       <c r="G14" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -16108,7 +16218,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -16160,10 +16270,10 @@
         <v>583</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H17" s="10"/>
     </row>
@@ -16184,10 +16294,10 @@
         <v>12</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -16208,10 +16318,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -16232,10 +16342,10 @@
         <v>35</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -16244,7 +16354,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>30</v>
@@ -16256,10 +16366,10 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -16268,22 +16378,22 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0.3</v>
+        <v>91</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>219</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -16298,16 +16408,16 @@
         <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>94</v>
+        <v>224</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -16315,13 +16425,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -16334,7 +16444,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
@@ -16355,7 +16465,7 @@
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="H26" s="10"/>
     </row>
@@ -16364,7 +16474,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -16378,14 +16488,14 @@
         <v>2</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -16432,10 +16542,10 @@
         <v>1</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -16491,13 +16601,13 @@
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
       <c r="G33" s="1" t="s">
         <v>6</v>
       </c>
@@ -16510,7 +16620,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="C34" s="18"/>
       <c r="D34" s="18"/>
@@ -16531,97 +16641,87 @@
       <c r="E35" s="18"/>
       <c r="F35" s="18"/>
       <c r="G35" s="9" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="1:8" ht="120" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>3</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>87</v>
+        <v>190</v>
       </c>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
-      <c r="G36" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="H36" s="10"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+    </row>
+    <row r="37" spans="1:8" ht="105" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <v>3</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="H37" s="10"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C38" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F38" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H37" s="15" t="s">
+      <c r="H38" s="15" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E38" s="2">
-        <v>520</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E39" s="2">
         <v>2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>62</v>
+        <v>86</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="H39" s="10"/>
     </row>
@@ -16630,7 +16730,7 @@
         <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>42</v>
@@ -16645,12 +16745,36 @@
         <v>82</v>
       </c>
       <c r="G40" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H40" s="10"/>
+    </row>
+    <row r="41" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" s="2">
+        <v>2</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="H40" s="10"/>
+      <c r="H41" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
@@ -16671,7 +16795,7 @@
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B26:F26"/>
@@ -16680,6 +16804,7 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -16692,7 +16817,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:AMJ40"/>
+  <dimension ref="A1:AMJ41"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.85546875" style="12" customWidth="1"/>
@@ -16719,27 +16844,27 @@
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="129" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F2" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="F2" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
@@ -16806,10 +16931,10 @@
       <c r="D6" s="7"/>
       <c r="E6" s="22"/>
       <c r="F6" s="22"/>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="26"/>
+      <c r="H6" s="27"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
@@ -16818,10 +16943,10 @@
       <c r="D7" s="7"/>
       <c r="E7" s="22"/>
       <c r="F7" s="22"/>
-      <c r="G7" s="26" t="s">
+      <c r="G7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="26"/>
+      <c r="H7" s="27"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
@@ -16830,10 +16955,10 @@
       <c r="D8" s="7"/>
       <c r="E8" s="22"/>
       <c r="F8" s="22"/>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="26"/>
+      <c r="H8" s="27"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
@@ -16842,22 +16967,22 @@
       <c r="D9" s="7"/>
       <c r="E9" s="22"/>
       <c r="F9" s="22"/>
-      <c r="G9" s="26" t="s">
+      <c r="G9" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="26"/>
+      <c r="H9" s="27"/>
     </row>
     <row r="10" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
       <c r="G10" s="1" t="s">
         <v>6</v>
       </c>
@@ -16886,14 +17011,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -16916,14 +17041,14 @@
         <v>1</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
       <c r="F14" s="18"/>
       <c r="G14" s="9" t="s">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -16932,7 +17057,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -16984,10 +17109,10 @@
         <v>460</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H17" s="10"/>
     </row>
@@ -17008,10 +17133,10 @@
         <v>12</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -17032,10 +17157,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -17056,10 +17181,10 @@
         <v>40</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -17068,7 +17193,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>30</v>
@@ -17080,10 +17205,10 @@
         <v>0.54</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -17092,22 +17217,22 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0.2</v>
+        <v>91</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>220</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -17122,16 +17247,16 @@
         <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="F23" s="11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -17139,13 +17264,13 @@
       <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="21"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
       <c r="G24" s="1" t="s">
         <v>6</v>
       </c>
@@ -17158,7 +17283,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
@@ -17172,14 +17297,14 @@
         <v>2</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="H26" s="10"/>
     </row>
@@ -17188,7 +17313,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -17202,14 +17327,14 @@
         <v>2</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -17256,10 +17381,10 @@
         <v>1</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -17315,13 +17440,13 @@
       <c r="A33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
       <c r="G33" s="1" t="s">
         <v>6</v>
       </c>
@@ -17334,7 +17459,7 @@
         <v>3</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="C34" s="18"/>
       <c r="D34" s="18"/>
@@ -17355,97 +17480,87 @@
       <c r="E35" s="18"/>
       <c r="F35" s="18"/>
       <c r="G35" s="9" t="s">
-        <v>204</v>
+        <v>179</v>
       </c>
       <c r="H35" s="10"/>
     </row>
-    <row r="36" spans="1:8" ht="105" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>3</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>87</v>
+        <v>191</v>
       </c>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
-      <c r="G36" s="9" t="s">
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+    </row>
+    <row r="37" spans="1:8" ht="105" x14ac:dyDescent="0.2">
+      <c r="A37" s="8">
+        <v>3</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="H36" s="10"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
+      <c r="H37" s="10"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B38" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C38" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D38" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F38" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H37" s="15" t="s">
+      <c r="H38" s="15" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E38" s="2">
-        <v>460</v>
-      </c>
-      <c r="F38" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H38" s="10"/>
     </row>
     <row r="39" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="E39" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G39" s="13" t="s">
-        <v>62</v>
+        <v>86</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="H39" s="10"/>
     </row>
@@ -17454,7 +17569,7 @@
         <v>29</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>42</v>
@@ -17469,12 +17584,36 @@
         <v>82</v>
       </c>
       <c r="G40" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H40" s="10"/>
+    </row>
+    <row r="41" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" s="2">
+        <v>2</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="H40" s="10"/>
+      <c r="H41" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F1:H1"/>
@@ -17496,7 +17635,7 @@
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B33:F33"/>
     <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B26:F26"/>
@@ -17504,6 +17643,7 @@
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
   <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/data/human/adult/validation/Scenarios/CSTARS.xlsx
+++ b/data/human/adult/validation/Scenarios/CSTARS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\Source\Pulse\ventilator_scenarios\source\data\human\adult\validation\Scenarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E5337F-4DBF-4129-9835-7C898CD8F9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB8D67E-47A9-4C82-894A-4EEA1BD4479D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27570" yWindow="3675" windowWidth="29880" windowHeight="26985" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2070" yWindow="4125" windowWidth="25590" windowHeight="22080" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1334" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="236">
   <si>
     <t>Scenario Name</t>
   </si>
@@ -307,9 +307,6 @@
     <t>ExpiratoryRespiratoryResistance</t>
   </si>
   <si>
-    <t>Right mainstem resolution.</t>
-  </si>
-  <si>
     <t>PIP</t>
   </si>
   <si>
@@ -447,17 +444,6 @@
   </si>
   <si>
     <t>lessThanValue</t>
-  </si>
-  <si>
-    <t>Patient suctioned and albuterol administered.
-Learning Objectives:
- - Recognize that treatment reduced airway resistance (lower difference PIP - Pplat)
- - AutoPEEP reduced
- - Failed trigger efforts disappeared
- - Recognize that now discordance problem is early cycle
-Recommended Actions:
- - Goal shifts to Comfort (imprive synchrony) due to cycle dyssychrony
- - Consider switching mode to PC-CSV (ie Pressure Support)</t>
   </si>
   <si>
     <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
@@ -467,14 +453,6 @@
       { "Compartment": "RightLung", "Severity": { "Scalar0To1": { "Value": 0.27 }}}]
   }}
 }</t>
-  </si>
-  <si>
-    <t>Learning Objectives:
- - Recognize mild ARDS
- - Recognize acceptable ventilator settings
-Recommended Actions:
- - None
-&lt;br /&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Learning Objectives:
@@ -605,14 +583,6 @@
   </si>
   <si>
     <t xml:space="preserve">Two hours later the patient is agitated. Both PIP and Pplat have increased. The SpO2 has fallen, and etCO2 has decreased. </t>
-  </si>
-  <si>
-    <t>Learning Objectives:
- - Recognize right mainstem intubation and recommend repositioning of endotracheal tube
-Recommended Actions:
- - Greatly increased DP, absence of breath sounds on the left side but normal sound to palpation indicate right mainstem intubation
- - Reposition endotracheal tube and re-assess 
-&lt;br /&gt;</t>
   </si>
   <si>
     <t>Learning Objectives:
@@ -741,13 +711,6 @@
   </si>
   <si>
     <t>Learning Objectives:
- - Recognize resolution of pneumothorax.
-Recommended Actions:
- - SpO2, breath sounds, plateau pressure indicate pneumothorax resolved
-&lt;br /&gt;</t>
-  </si>
-  <si>
-    <t>Learning Objectives:
  - Assess baseline status
  - Recognize moderate ARDS
 Recommended Actions:
@@ -981,24 +944,7 @@
 }</t>
   </si>
   <si>
-    <t>&lt;br /&gt;
-Ventilator settings are (VT delivered = 6.9 mL/kg (ideal)):
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| PC-CMV | NA     | 20          | NA           | NA  | 0.6    | 10       | 10            | 0.60 |</t>
-  </si>
-  <si>
     <t>{ "PatientAction": { "AcuteStress": { "Severity": { "Scalar0To1": { "Value": 0.8 } } } } }</t>
-  </si>
-  <si>
-    <t>{ "PatientAction": {
-      "AirwayObstruction": {
-        "Severity": {
-          "Scalar0To1": {
-            "Value": 0.35
-          } } } }
-  }</t>
   </si>
   <si>
     <t>Patient transport continues.
@@ -1082,43 +1028,6 @@
 }</t>
   </si>
   <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 42, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.52, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 27, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 350, "Unit": "mL" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
-    <t>Ventilator settings are:
-&lt;br /&gt;
-| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
-| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.450  | NA          | 53           | NA  | 0.53  | 27       | 8            | 0.40 |</t>
-  </si>
-  <si>
-    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
-  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
-  "Mode": "AssistedControl", 
-  "InspirationWaveform": "Square",
-  "Flow": { "ScalarVolumePerTime": { "Value": 53, "Unit": "L/min" } },
-  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.4 } },
-  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.53, "Unit": "s" } },
-  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
-  "RespirationRate": { "ScalarFrequency": { "Value": 27, "Unit": "1/min" } },
-  "TidalVolume": { "ScalarVolume": { "Value": 450, "Unit": "mL" } },
-   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
-  }}
-}</t>
-  </si>
-  <si>
     <t>{ "PatientAction": { "AcuteRespiratoryDistressSyndromeExacerbation":
   {
     "Severity": [ 
@@ -1141,16 +1050,116 @@
 | VC-CMV | 0.350   | NA          | 42           | NA  | 0.52  | 27       | 12            | 1.00 |</t>
   </si>
   <si>
+    <t>Learning Objectives:
+ - Identify severity of ARDS
+ - Recognize acceptable ventilator settings
+Recommended Actions:
+ - None
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>Patient suctioned and albuterol administered.
+Learning Objectives:
+ - Recognize that treatment reduced airway resistance (lower difference PIP - Pplat)
+ - AutoPEEP reduced
+ - Failed trigger efforts disappeared
+ - Recognize that now discordance problem is early cycle
+Recommended Actions:
+ - Goal shifts to Comfort (imprive synchrony) due to cycle dyssychrony
+ - Decrease FiO2
+ - Consider switching mode to PC-CSV (ie Pressure Support)</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Recognize resolution of pneumothorax.
+Recommended Actions:
+ - SpO2, breath sounds, plateau pressure indicate pneumothorax resolved
+ - Increase FiO2 to get SpO2 88-95%
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>Ventilator settings are:
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| VC-CMV | 0.450  | NA          | 53           | NA  | 0.53  | 27       | 8            | 0.21 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 53, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.21 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.53, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 27, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 450, "Unit": "mL" } },
+   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
     <t>Ventialtor settings are changed. Decrease VT to prevent premature cycling by high-pressure alarm.
 Learning Objectives:
  - Evaluate effects of changes
 Recommended Actions:
- - None
+ - Increase PEEP to improve oxygenation
+ - Increase FiO2 to get SpO2 88-95%
 Ventilator settings are updated to:
  - TV = 450 mL -&gt; 350 mL
 | Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
 | ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
-| VC-CMV | 0.350  | NA          | 42           | NA  | 0.52  | 27       | 8            | 0.40 |</t>
+| VC-CMV | 0.350  | NA          | 42           | NA  | 0.52  | 27       | 8            | 0.21 |</t>
+  </si>
+  <si>
+    <t>{ "EquipmentAction": { "MechanicalVentilatorVolumeControl": { "MechanicalVentilatorMode": 
+  { "MechanicalVentilatorAction": { "EquipmentAction": { "Action": {} } }, "Connection": "On" },
+  "Mode": "AssistedControl", 
+  "InspirationWaveform": "Square",
+  "Flow": { "ScalarVolumePerTime": { "Value": 42, "Unit": "L/min" } },
+  "FractionInspiredOxygen": { "Scalar0To1": { "Value": 0.21 } },
+  "InspiratoryPeriod": { "ScalarTime": { "Value": 0.52, "Unit": "s" } },
+  "PositiveEndExpiratoryPressure": { "ScalarPressure": { "Value": 8, "Unit": "cmH2O" } },
+  "RespirationRate": { "ScalarFrequency": { "Value": 27, "Unit": "1/min" } },
+  "TidalVolume": { "ScalarVolume": { "Value": 350, "Unit": "mL" } },
+   "InspirationPatientTriggerPressure": { "ScalarPressure": { "Value": -1.0, "Unit": "cmH2O"  } }
+  }}
+}</t>
+  </si>
+  <si>
+    <t>&lt;br /&gt;
+Ventilator settings are:
+&lt;br /&gt;
+| Mode   | VT (L) | PIP (cmH2O) | Flow (L/min) | I:E | TI (s) | RR (bpm) | PEEP (cmH2O) | FiO2 |
+| ------ | ------ | ----------- | ------------ | --- | ------ | -------- | ------------ | ---- |
+| PC-CMV | NA     | 20          | NA           | NA  | 0.6    | 10       | 10            | 0.60 |</t>
+  </si>
+  <si>
+    <t>{ "PatientAction": {
+      "AirwayObstruction": {
+        "Severity": {
+          "Scalar0To1": {
+            "Value": 0.3
+          } } } }
+  }</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Recognize right mainstem intubation and recommend repositioning of endotracheal tube
+Recommended Actions:
+ - Decreased etCO2, plus greatly increased Pplat and DP, absence of breath sounds on the left side but normal sound to palpation indicate right mainstem intubation
+ - Reposition endotracheal tube and re-assess 
+&lt;br /&gt;</t>
+  </si>
+  <si>
+    <t>Endotracheal tube repositioned.</t>
+  </si>
+  <si>
+    <t>Learning Objectives:
+ - Assess effects of tube reposition
+Recommended Actions:
+ - None</t>
   </si>
 </sst>
 </file>
@@ -1848,7 +1857,7 @@
     </row>
     <row r="2" spans="1:1024" ht="105.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -1857,7 +1866,7 @@
         <v>68</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G2" s="26"/>
       <c r="H2" s="26"/>
@@ -1950,7 +1959,7 @@
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
       <c r="G8" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H8" s="27"/>
     </row>
@@ -2005,14 +2014,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>126</v>
+        <v>224</v>
       </c>
       <c r="H12" s="9"/>
     </row>
@@ -2051,14 +2060,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="20"/>
       <c r="E15" s="20"/>
       <c r="F15" s="21"/>
       <c r="G15" s="9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="H15" s="9"/>
     </row>
@@ -2067,7 +2076,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -2118,11 +2127,9 @@
       <c r="E18" s="2">
         <v>567</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F18" s="11"/>
       <c r="G18" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -2143,10 +2150,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -2167,10 +2174,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -2191,10 +2198,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -2203,7 +2210,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -2215,10 +2222,10 @@
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -2227,22 +2234,22 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -2257,16 +2264,16 @@
         <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>93</v>
-      </c>
       <c r="G24" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -2293,7 +2300,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
@@ -2314,7 +2321,7 @@
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H27" s="9"/>
     </row>
@@ -2323,14 +2330,14 @@
         <v>2</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H28" s="9"/>
     </row>
@@ -2339,7 +2346,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -2353,7 +2360,7 @@
         <v>2</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
@@ -2404,11 +2411,9 @@
       <c r="E32" s="2">
         <v>567</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F32" s="11"/>
       <c r="G32" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -2429,10 +2434,10 @@
         <v>12</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -2453,10 +2458,10 @@
         <v>12</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -2477,10 +2482,10 @@
         <v>35</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -2489,7 +2494,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>30</v>
@@ -2501,10 +2506,10 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -2513,22 +2518,22 @@
         <v>29</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -2543,16 +2548,16 @@
         <v>35</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -2579,7 +2584,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C40" s="18"/>
       <c r="D40" s="18"/>
@@ -2593,14 +2598,14 @@
         <v>3</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="20"/>
       <c r="E41" s="20"/>
       <c r="F41" s="21"/>
       <c r="G41" s="9" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -2609,7 +2614,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C42" s="18"/>
       <c r="D42" s="18"/>
@@ -2660,11 +2665,9 @@
       <c r="E44" s="2">
         <v>490</v>
       </c>
-      <c r="F44" s="11" t="s">
-        <v>106</v>
-      </c>
+      <c r="F44" s="11"/>
       <c r="G44" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -2685,7 +2688,7 @@
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>67</v>
@@ -2697,22 +2700,22 @@
         <v>29</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E46" s="2">
         <v>2</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H46" s="10"/>
     </row>
@@ -2739,14 +2742,14 @@
         <v>4</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="C48" s="20"/>
       <c r="D48" s="20"/>
       <c r="E48" s="20"/>
       <c r="F48" s="21"/>
       <c r="G48" s="9" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="H48" s="10"/>
     </row>
@@ -2755,7 +2758,7 @@
         <v>4</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C49" s="18"/>
       <c r="D49" s="18"/>
@@ -2769,7 +2772,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="20"/>
@@ -2820,11 +2823,9 @@
       <c r="E52" s="2">
         <v>490</v>
       </c>
-      <c r="F52" s="11" t="s">
-        <v>106</v>
-      </c>
+      <c r="F52" s="11"/>
       <c r="G52" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H52" s="10"/>
     </row>
@@ -2845,7 +2846,7 @@
         <v>3</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G53" s="13" t="s">
         <v>63</v>
@@ -2863,13 +2864,13 @@
         <v>35</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E54" s="2">
         <v>3</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>66</v>
@@ -2893,7 +2894,7 @@
         <v>3</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>67</v>
@@ -2917,10 +2918,10 @@
         <v>3</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H56" s="10"/>
     </row>
@@ -2929,7 +2930,7 @@
         <v>29</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>30</v>
@@ -2941,10 +2942,10 @@
         <v>3</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H57" s="10"/>
     </row>
@@ -3043,7 +3044,7 @@
         <v>69</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G2" s="26"/>
       <c r="H2" s="26"/>
@@ -3140,7 +3141,7 @@
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
       <c r="G8" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H8" s="27"/>
     </row>
@@ -3195,14 +3196,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -3239,14 +3240,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="9" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -3255,7 +3256,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -3306,11 +3307,9 @@
       <c r="E18" s="2">
         <v>650</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F18" s="11"/>
       <c r="G18" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -3331,10 +3330,10 @@
         <v>24</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -3355,10 +3354,10 @@
         <v>36</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -3379,10 +3378,10 @@
         <v>68</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -3391,7 +3390,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -3403,10 +3402,10 @@
         <v>0.49</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -3415,7 +3414,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
@@ -3427,10 +3426,10 @@
         <v>0.19</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -3457,7 +3456,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
@@ -3471,14 +3470,14 @@
         <v>2</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="H26" s="9"/>
     </row>
@@ -3501,7 +3500,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
@@ -3515,7 +3514,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -3566,11 +3565,9 @@
       <c r="E31" s="2">
         <v>650</v>
       </c>
-      <c r="F31" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F31" s="11"/>
       <c r="G31" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -3591,7 +3588,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>61</v>
@@ -3615,7 +3612,7 @@
         <v>1</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>62</v>
@@ -3639,10 +3636,10 @@
         <v>1</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -3663,10 +3660,10 @@
         <v>1</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -3693,7 +3690,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
@@ -3714,7 +3711,7 @@
       <c r="E38" s="20"/>
       <c r="F38" s="21"/>
       <c r="G38" s="9" t="s">
-        <v>124</v>
+        <v>225</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -3723,7 +3720,7 @@
         <v>3</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C39" s="18"/>
       <c r="D39" s="18"/>
@@ -3737,7 +3734,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C40" s="18"/>
       <c r="D40" s="18"/>
@@ -3788,11 +3785,9 @@
       <c r="E42" s="2">
         <v>650</v>
       </c>
-      <c r="F42" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F42" s="11"/>
       <c r="G42" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H42" s="10"/>
     </row>
@@ -3813,7 +3808,7 @@
         <v>2</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G43" s="13" t="s">
         <v>61</v>
@@ -3837,7 +3832,7 @@
         <v>2</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G44" s="13" t="s">
         <v>62</v>
@@ -3861,10 +3856,10 @@
         <v>2</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H45" s="10"/>
     </row>
@@ -3885,10 +3880,10 @@
         <v>2</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H46" s="10"/>
     </row>
@@ -3982,7 +3977,7 @@
         <v>70</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G2" s="26"/>
       <c r="H2" s="26"/>
@@ -4077,7 +4072,7 @@
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
       <c r="G8" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H8" s="27"/>
     </row>
@@ -4132,7 +4127,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
@@ -4140,7 +4135,7 @@
       <c r="F12" s="21"/>
       <c r="G12" s="9"/>
       <c r="H12" s="10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="147.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4148,14 +4143,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
       <c r="G13" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H13" s="10"/>
     </row>
@@ -4194,14 +4189,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
       <c r="E16" s="18"/>
       <c r="F16" s="18"/>
       <c r="G16" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H16" s="10"/>
     </row>
@@ -4210,7 +4205,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
@@ -4261,11 +4256,9 @@
       <c r="E19" s="2">
         <v>450</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F19" s="11"/>
       <c r="G19" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -4286,10 +4279,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -4310,10 +4303,10 @@
         <v>12</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -4334,10 +4327,10 @@
         <v>40</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -4346,7 +4339,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
@@ -4358,10 +4351,10 @@
         <v>0.54</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -4370,22 +4363,22 @@
         <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -4400,16 +4393,16 @@
         <v>35</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>93</v>
-      </c>
       <c r="G25" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H25" s="10"/>
     </row>
@@ -5452,7 +5445,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -5473,7 +5466,7 @@
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="14"/>
@@ -6498,7 +6491,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -6506,7 +6499,7 @@
       <c r="F29" s="18"/>
       <c r="G29" s="9"/>
       <c r="H29" s="10" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14"/>
@@ -7530,14 +7523,14 @@
         <v>2</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
       <c r="G30" s="9" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="H30" s="10"/>
       <c r="I30" s="14"/>
@@ -8562,7 +8555,7 @@
         <v>2</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
@@ -8576,7 +8569,7 @@
         <v>2</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C32" s="18"/>
       <c r="D32" s="18"/>
@@ -10658,11 +10651,9 @@
       <c r="E34" s="2">
         <v>450</v>
       </c>
-      <c r="F34" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F34" s="11"/>
       <c r="G34" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -10682,9 +10673,11 @@
       <c r="E35" s="2">
         <v>1</v>
       </c>
-      <c r="F35" s="11"/>
+      <c r="F35" s="11" t="s">
+        <v>84</v>
+      </c>
       <c r="G35" s="13" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="H35" s="10"/>
     </row>
@@ -10704,9 +10697,11 @@
       <c r="E36" s="2">
         <v>1</v>
       </c>
-      <c r="F36" s="11"/>
+      <c r="F36" s="11" t="s">
+        <v>84</v>
+      </c>
       <c r="G36" s="13" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -10727,10 +10722,10 @@
         <v>33</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -10739,7 +10734,7 @@
         <v>29</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>30</v>
@@ -10751,10 +10746,10 @@
         <v>0.65</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -10763,22 +10758,22 @@
         <v>29</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E39" s="2">
         <v>0.4</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H39" s="10"/>
     </row>
@@ -10793,16 +10788,16 @@
         <v>35</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E40" s="2">
         <v>100</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H40" s="10"/>
     </row>
@@ -11845,7 +11840,7 @@
         <v>3</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C42" s="18"/>
       <c r="D42" s="18"/>
@@ -11859,14 +11854,14 @@
         <v>3</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C43" s="18"/>
       <c r="D43" s="18"/>
       <c r="E43" s="18"/>
       <c r="F43" s="18"/>
       <c r="G43" s="9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H43" s="10"/>
       <c r="I43" s="14"/>
@@ -12891,7 +12886,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="C44" s="18"/>
       <c r="D44" s="18"/>
@@ -14974,11 +14969,9 @@
       <c r="E46" s="2">
         <v>350</v>
       </c>
-      <c r="F46" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F46" s="11"/>
       <c r="G46" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H46" s="10"/>
     </row>
@@ -14999,7 +14992,7 @@
         <v>2</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>67</v>
@@ -16045,14 +16038,14 @@
         <v>4</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C49" s="18"/>
       <c r="D49" s="18"/>
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
       <c r="G49" s="9" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="H49" s="10"/>
       <c r="I49" s="14"/>
@@ -17077,7 +17070,7 @@
         <v>4</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C50" s="18"/>
       <c r="D50" s="18"/>
@@ -17091,7 +17084,7 @@
         <v>4</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C51" s="18"/>
       <c r="D51" s="18"/>
@@ -19174,11 +19167,9 @@
       <c r="E53" s="2">
         <v>350</v>
       </c>
-      <c r="F53" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F53" s="11"/>
       <c r="G53" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H53" s="10"/>
     </row>
@@ -19199,7 +19190,7 @@
         <v>2</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>67</v>
@@ -19208,10 +19199,6 @@
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B48:F48"/>
     <mergeCell ref="B49:F49"/>
     <mergeCell ref="B51:F51"/>
     <mergeCell ref="B16:F16"/>
@@ -19225,6 +19212,10 @@
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B48:F48"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B13:F13"/>
@@ -19292,7 +19283,7 @@
     </row>
     <row r="2" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="25" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -19301,7 +19292,7 @@
         <v>71</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G2" s="26"/>
       <c r="H2" s="26"/>
@@ -19396,7 +19387,7 @@
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
       <c r="G8" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H8" s="27"/>
     </row>
@@ -19451,7 +19442,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
@@ -19459,7 +19450,7 @@
       <c r="F12" s="21"/>
       <c r="G12" s="9"/>
       <c r="H12" s="10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="127.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -19467,14 +19458,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
       <c r="G13" s="9" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H13" s="10"/>
     </row>
@@ -19513,14 +19504,14 @@
         <v>1</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="20"/>
       <c r="E16" s="20"/>
       <c r="F16" s="21"/>
       <c r="G16" s="9" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="H16" s="10"/>
     </row>
@@ -19529,7 +19520,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
@@ -19580,11 +19571,9 @@
       <c r="E19" s="2">
         <v>488</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F19" s="11"/>
       <c r="G19" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -19605,10 +19594,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -19629,10 +19618,10 @@
         <v>12</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -19653,10 +19642,10 @@
         <v>35</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -19665,7 +19654,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
@@ -19677,10 +19666,10 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -19689,22 +19678,22 @@
         <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -19719,16 +19708,16 @@
         <v>35</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="H25" s="10"/>
     </row>
@@ -19755,7 +19744,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -19769,14 +19758,14 @@
         <v>2</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -19785,7 +19774,7 @@
         <v>2</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -19799,14 +19788,14 @@
         <v>2</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
       <c r="E30" s="18"/>
       <c r="F30" s="18"/>
       <c r="G30" s="9" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -19852,11 +19841,9 @@
       <c r="E32" s="2">
         <v>488</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F32" s="11"/>
       <c r="G32" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H32" s="10"/>
     </row>
@@ -19949,7 +19936,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>67</v>
@@ -19976,7 +19963,7 @@
         <v>32</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -20000,7 +19987,7 @@
         <v>32</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -20027,7 +20014,7 @@
         <v>3</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C40" s="18"/>
       <c r="D40" s="18"/>
@@ -20048,7 +20035,7 @@
       <c r="E41" s="18"/>
       <c r="F41" s="18"/>
       <c r="G41" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -20057,17 +20044,17 @@
         <v>3</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C42" s="18"/>
       <c r="D42" s="18"/>
       <c r="E42" s="18"/>
       <c r="F42" s="18"/>
       <c r="G42" s="9" t="s">
-        <v>184</v>
+        <v>226</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
@@ -20075,7 +20062,7 @@
         <v>3</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C43" s="18"/>
       <c r="D43" s="18"/>
@@ -20089,7 +20076,7 @@
         <v>3</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C44" s="18"/>
       <c r="D44" s="18"/>
@@ -20140,11 +20127,9 @@
       <c r="E46" s="2">
         <v>488</v>
       </c>
-      <c r="F46" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F46" s="11"/>
       <c r="G46" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H46" s="10"/>
     </row>
@@ -20237,7 +20222,7 @@
         <v>2</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>67</v>
@@ -20264,7 +20249,7 @@
         <v>32</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H51" s="10"/>
     </row>
@@ -20288,7 +20273,7 @@
         <v>32</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H52" s="10"/>
     </row>
@@ -20383,7 +20368,7 @@
         <v>72</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G2" s="26"/>
       <c r="H2" s="26"/>
@@ -20478,7 +20463,7 @@
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
       <c r="G8" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H8" s="27"/>
     </row>
@@ -20533,14 +20518,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -20563,14 +20548,14 @@
         <v>1</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
       <c r="F14" s="21"/>
       <c r="G14" s="9" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -20579,7 +20564,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -20630,11 +20615,9 @@
       <c r="E17" s="2">
         <v>376</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F17" s="11"/>
       <c r="G17" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H17" s="10"/>
     </row>
@@ -20655,10 +20638,10 @@
         <v>12</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -20679,10 +20662,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -20703,10 +20686,10 @@
         <v>35</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -20715,7 +20698,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>30</v>
@@ -20727,10 +20710,10 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -20739,22 +20722,22 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -20769,16 +20752,16 @@
         <v>35</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -20805,7 +20788,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
@@ -20826,7 +20809,7 @@
       <c r="E26" s="18"/>
       <c r="F26" s="18"/>
       <c r="G26" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H26" s="10"/>
     </row>
@@ -20835,7 +20818,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -20849,14 +20832,14 @@
         <v>2</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
       <c r="E28" s="18"/>
       <c r="F28" s="18"/>
       <c r="G28" s="9" t="s">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="H28" s="10"/>
     </row>
@@ -20902,11 +20885,9 @@
       <c r="E30" s="2">
         <v>376</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F30" s="11"/>
       <c r="G30" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H30" s="10"/>
     </row>
@@ -20951,7 +20932,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>67</v>
@@ -20978,7 +20959,7 @@
         <v>32</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H33" s="10"/>
     </row>
@@ -21002,7 +20983,7 @@
         <v>32</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -21029,7 +21010,7 @@
         <v>3</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
@@ -21050,7 +21031,7 @@
       <c r="E37" s="18"/>
       <c r="F37" s="18"/>
       <c r="G37" s="9" t="s">
-        <v>77</v>
+        <v>234</v>
       </c>
       <c r="H37" s="10"/>
     </row>
@@ -21059,7 +21040,7 @@
         <v>3</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C38" s="18"/>
       <c r="D38" s="18"/>
@@ -21068,18 +21049,20 @@
       <c r="G38" s="9"/>
       <c r="H38" s="9"/>
     </row>
-    <row r="39" spans="1:8" ht="14.85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" ht="75" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>3</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C39" s="18"/>
       <c r="D39" s="18"/>
       <c r="E39" s="18"/>
       <c r="F39" s="18"/>
-      <c r="G39" s="9"/>
+      <c r="G39" s="9" t="s">
+        <v>235</v>
+      </c>
       <c r="H39" s="10"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
@@ -21124,11 +21107,9 @@
       <c r="E41" s="2">
         <v>376</v>
       </c>
-      <c r="F41" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F41" s="11"/>
       <c r="G41" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H41" s="10"/>
     </row>
@@ -21173,7 +21154,7 @@
         <v>2</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>67</v>
@@ -21200,7 +21181,7 @@
         <v>32</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H44" s="10"/>
     </row>
@@ -21224,7 +21205,7 @@
         <v>32</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H45" s="10"/>
     </row>
@@ -21316,7 +21297,7 @@
         <v>73</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G2" s="26"/>
       <c r="H2" s="26"/>
@@ -21411,7 +21392,7 @@
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
       <c r="G8" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H8" s="27"/>
     </row>
@@ -21466,14 +21447,14 @@
         <v>1</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
       <c r="F12" s="18"/>
       <c r="G12" s="9" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -21496,14 +21477,14 @@
         <v>1</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
       <c r="E14" s="20"/>
       <c r="F14" s="21"/>
       <c r="G14" s="9" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="H14" s="10"/>
     </row>
@@ -21512,7 +21493,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -21564,10 +21545,10 @@
         <v>12</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H17" s="10"/>
     </row>
@@ -21588,10 +21569,10 @@
         <v>12</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -21612,10 +21593,10 @@
         <v>35</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -21624,7 +21605,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>30</v>
@@ -21636,10 +21617,10 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -21648,22 +21629,22 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -21678,16 +21659,16 @@
         <v>35</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -21714,7 +21695,7 @@
         <v>2</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
@@ -21735,7 +21716,7 @@
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
       <c r="G25" s="9" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="H25" s="10"/>
     </row>
@@ -21744,7 +21725,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
@@ -21758,14 +21739,14 @@
         <v>2</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -21811,11 +21792,9 @@
       <c r="E29" s="2">
         <v>1</v>
       </c>
-      <c r="F29" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F29" s="11"/>
       <c r="G29" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H29" s="10"/>
     </row>
@@ -21836,7 +21815,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>61</v>
@@ -21860,7 +21839,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>62</v>
@@ -21890,7 +21869,7 @@
         <v>3</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C33" s="18"/>
       <c r="D33" s="18"/>
@@ -21911,7 +21890,7 @@
       <c r="E34" s="18"/>
       <c r="F34" s="18"/>
       <c r="G34" s="9" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H34" s="10"/>
     </row>
@@ -21920,7 +21899,7 @@
         <v>3</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>
@@ -21933,15 +21912,15 @@
       <c r="A36" s="8">
         <v>3</v>
       </c>
-      <c r="B36" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
+      <c r="B36" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="21"/>
       <c r="G36" s="9" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -21987,11 +21966,9 @@
       <c r="E38" s="2">
         <v>2</v>
       </c>
-      <c r="F38" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F38" s="11"/>
       <c r="G38" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -22012,7 +21989,7 @@
         <v>2</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G39" s="13" t="s">
         <v>61</v>
@@ -22036,7 +22013,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G40" s="13" t="s">
         <v>62</v>
@@ -22131,7 +22108,7 @@
         <v>74</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G2" s="26"/>
       <c r="H2" s="26"/>
@@ -22226,7 +22203,7 @@
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
       <c r="G8" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H8" s="27"/>
     </row>
@@ -22281,7 +22258,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
@@ -22289,7 +22266,7 @@
       <c r="F12" s="21"/>
       <c r="G12" s="9"/>
       <c r="H12" s="10" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -22297,14 +22274,14 @@
         <v>1</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
       <c r="G13" s="9" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H13" s="10"/>
     </row>
@@ -22327,14 +22304,14 @@
         <v>1</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
       <c r="F15" s="18"/>
       <c r="G15" s="9" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H15" s="10"/>
     </row>
@@ -22343,7 +22320,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -22394,11 +22371,9 @@
       <c r="E18" s="2">
         <v>460</v>
       </c>
-      <c r="F18" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F18" s="11"/>
       <c r="G18" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H18" s="10"/>
     </row>
@@ -22419,10 +22394,10 @@
         <v>12</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H19" s="10"/>
     </row>
@@ -22443,10 +22418,10 @@
         <v>12</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H20" s="10"/>
     </row>
@@ -22467,10 +22442,10 @@
         <v>40</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H21" s="10"/>
     </row>
@@ -22479,7 +22454,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>30</v>
@@ -22491,10 +22466,10 @@
         <v>0.54</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H22" s="10"/>
     </row>
@@ -22503,22 +22478,22 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H23" s="10"/>
     </row>
@@ -22533,16 +22508,16 @@
         <v>35</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>93</v>
-      </c>
       <c r="G24" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H24" s="10"/>
     </row>
@@ -22569,7 +22544,7 @@
         <v>2</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
@@ -22583,14 +22558,14 @@
         <v>2</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
       <c r="E27" s="18"/>
       <c r="F27" s="18"/>
       <c r="G27" s="9" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H27" s="10"/>
     </row>
@@ -22599,7 +22574,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
@@ -22613,14 +22588,14 @@
         <v>2</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
       <c r="E29" s="18"/>
       <c r="F29" s="18"/>
       <c r="G29" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H29" s="10"/>
     </row>
@@ -22666,11 +22641,9 @@
       <c r="E31" s="2">
         <v>1</v>
       </c>
-      <c r="F31" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F31" s="11"/>
       <c r="G31" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H31" s="10"/>
     </row>
@@ -22691,7 +22664,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G32" s="13" t="s">
         <v>61</v>
@@ -22715,7 +22688,7 @@
         <v>1</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>62</v>
@@ -22745,7 +22718,7 @@
         <v>3</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>
@@ -22766,7 +22739,7 @@
       <c r="E36" s="18"/>
       <c r="F36" s="18"/>
       <c r="G36" s="9" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="H36" s="10"/>
     </row>
@@ -22775,7 +22748,7 @@
         <v>3</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
@@ -22789,14 +22762,14 @@
         <v>3</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C38" s="18"/>
       <c r="D38" s="18"/>
       <c r="E38" s="18"/>
       <c r="F38" s="18"/>
       <c r="G38" s="9" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H38" s="10"/>
     </row>
@@ -22837,16 +22810,14 @@
         <v>57</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E40" s="2">
         <v>1</v>
       </c>
-      <c r="F40" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="F40" s="11"/>
       <c r="G40" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H40" s="10"/>
     </row>
@@ -22867,7 +22838,7 @@
         <v>2</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G41" s="13" t="s">
         <v>61</v>
@@ -22891,7 +22862,7 @@
         <v>2</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G42" s="13" t="s">
         <v>62</v>
